--- a/sample_data/Knowledge_base_updated.xlsx
+++ b/sample_data/Knowledge_base_updated.xlsx
@@ -1,40 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LongArc\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A2ED9D9B3EA6316A7B6B7162D0533C94B42B91B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
-    <sheet name="Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Recommendations" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Master" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Recommendations" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="KB Tracker" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="731">
   <si>
     <t>module_id</t>
   </si>
@@ -99,14 +81,14 @@
     <t>Appointment Scheduling</t>
   </si>
   <si>
-    <t>&lt;20% of inbound trucks arrive against a pre-booked slot.
+    <t xml:space="preserve">&lt;20% of inbound trucks arrive against a pre-booked slot.
 &gt;50% of daily volume clusters into a single 2-hour window, causing dock queuing beyond 2 hours.
 No designated driver holding area - drivers and helpers congregate at the security gate causing congestion.
 Dock-in time is not captured, so it cannot feed downstream GRN turnaround-time (TAT) SLAs.
 Slot booking, where it exists, is a manual register entry with no QR/Booking-ID confirmation shared with the vendor ahead of arrival.</t>
   </si>
   <si>
-    <t>20-50% slot adherence.
+    <t xml:space="preserve">20-50% slot adherence.
 Peak-hour concentration still exceeds 40% of daily volume.
 Average vehicle wait time 60-120 minutes.
 An informal holding area exists but is not enforced, so congregation at the gate persists.
@@ -114,7 +96,7 @@
 A digital slot booking exists for under 30% of vendors, without a QR/Booking-ID confirmation shared back to the vendor.</t>
   </si>
   <si>
-    <t>50-75% slot adherence via a basic appointment scheduler.
+    <t xml:space="preserve">50-75% slot adherence via a basic appointment scheduler.
 Peak-hour concentration reduced to 25-40%.
 Average wait time 30-60 minutes.
 A designated driver holding area away from the security gate is marked and used for the majority of vehicles.
@@ -122,7 +104,7 @@
 A digital slot booking with a QR/Booking-ID confirmation (D-2 indent leading to a D-1 slot) is shared with 30-60% of vendors ahead of arrival.</t>
   </si>
   <si>
-    <t>75-90% slot adherence with system-enforced windows.
+    <t xml:space="preserve">75-90% slot adherence with system-enforced windows.
 Peak-hour concentration under 25%.
 Average wait time under 30 minutes.
 Adherence tracked daily.
@@ -131,7 +113,7 @@
 Digital slot booking with a QR/Booking-ID confirmation (D-2 indent to D-1 slot) is shared with 60-90% of vendors, scanned at the gate to authenticate arrival.</t>
   </si>
   <si>
-    <t>&gt;90% slot adherence with automated vendor notification.
+    <t xml:space="preserve">&gt;90% slot adherence with automated vendor notification.
 Load spread within +/-10% across all shift hours.
 Average wait time under 15 minutes.
 The holding area is fully marshalled with real-time occupancy visibility and zero congregation at the security gate.
@@ -148,27 +130,27 @@
     <t>Gate Entry &amp; Documentation Verification</t>
   </si>
   <si>
-    <t>&lt;50% of gate entries verified against indent/invoice before unloading starts (across the 70:30 vendor:courier vehicle mix, with no differentiated checklist for vendor vs courier vehicles).
+    <t xml:space="preserve">&lt;50% of gate entries verified against indent/invoice before unloading starts (across the 70:30 vendor:courier vehicle mix, with no differentiated checklist for vendor vs courier vehicles).
 Documentation/invoice mismatch rate above 30%.
 Average gate-in time over 20 min/vehicle.
 There is no driver-ID or vehicle-number authentication against the booked slot, and temperature checks (where done at all) are not scoped to any specific SKU or deviation threshold.</t>
   </si>
   <si>
-    <t>50-70% verified pre-unload, using a single generic checklist applied to both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicles.
+    <t xml:space="preserve">50-70% verified pre-unload, using a single generic checklist applied to both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicles.
 Mismatch rate 20-30%.
 Gate-in time 15-20 min/vehicle.
 Driver-ID and vehicle-number are checked against the slot for under 30% of vehicles.
 A temperature check is performed inconsistently and without a defined deviation threshold, even for 4°C-sensitive SKUs (e.g., mushrooms).</t>
   </si>
   <si>
-    <t>70-85% verified against a defined checklist (vendor, invoice, indented qty, reefer temperature), with separate verification steps for vendor trucks (70% of vehicle mix) and courier vans (30% of vehicle mix).
+    <t xml:space="preserve">70-85% verified against a defined checklist (vendor, invoice, indented qty, reefer temperature), with separate verification steps for vendor trucks (70% of vehicle mix) and courier vans (30% of vehicle mix).
 Mismatch rate 10-20%.
 Gate-in time 10-15 min.
 Driver-ID and vehicle-number are authenticated against the vendor code, PO, and slot for 30-60% of vehicles.
 Temperature is checked specifically for 4°C-sensitive SKUs (e.g., mushrooms) but the reject threshold (e.g., &gt;3°C deviation) is not consistently applied.</t>
   </si>
   <si>
-    <t>85-95% verified via system-assisted matching (barcode/OCR) across both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicle streams.
+    <t xml:space="preserve">85-95% verified via system-assisted matching (barcode/OCR) across both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicle streams.
 Mismatch rate 5-10%.
 Gate-in time 5-10 min.
 100% of reefer vehicles temperature-logged.
@@ -176,7 +158,7 @@
 A defined temperature-reject rule (&gt;3°C deviation for 4°C-sensitive SKUs such as mushrooms only, not the full FnV range) is applied consistently.</t>
   </si>
   <si>
-    <t>&gt;95% verified end-to-end digitally with zero manual entry, with vendor (70% of vehicle mix) and courier (30% of vehicle mix) streams tracked and matched separately.
+    <t xml:space="preserve">&gt;95% verified end-to-end digitally with zero manual entry, with vendor (70% of vehicle mix) and courier (30% of vehicle mix) streams tracked and matched separately.
 Mismatch rate under 5%.
 Gate-in time under 5 min.
 Full audit trail with automated exception flags.
@@ -190,28 +172,28 @@
     <t>Manpower Entry Management</t>
   </si>
   <si>
-    <t>0% biometric/facial recognition coverage at shift changeovers.
+    <t xml:space="preserve">0% biometric/facial recognition coverage at shift changeovers.
 Manual register only, with no zone-wise capturing of manpower entries (e.g., S&amp;G, packing, put-away, dispatch) against warehouse-sizing-based headcount norms.
 Unauthorized-entry incidents exceed 60 per month.</t>
   </si>
   <si>
-    <t>Under 30% biometric coverage.
+    <t xml:space="preserve">Under 30% biometric coverage.
 Manual plus partial physical checks.
 Zone-wise entry counts recorded ad hoc for under 30% of zones, not benchmarked against a sizing-based manpower plan.
 Unauthorized-entry incidents 30-60 per month.</t>
   </si>
   <si>
-    <t>30-60% facial recognition coverage at main shift changeovers.
+    <t xml:space="preserve">30-60% facial recognition coverage at main shift changeovers.
 Zone-wise manpower entry tracked for 30-60% of zones (e.g., S&amp;G, packing, put-away) against a defined warehouse-sizing-based headcount norm (illustrative only - e.g., ~10 for S&amp;G, ~25 for packing), reviewed periodically rather than daily.
 Unauthorized-entry incidents 10-30 per month.</t>
   </si>
   <si>
-    <t>60-90% coverage across all shifts and gates.
+    <t xml:space="preserve">60-90% coverage across all shifts and gates.
 Zone-wise entry captured and reconciled daily for 60-90% of zones against the warehouse-sizing-based manpower plan, integrated with the attendance system.
 Unauthorized-entry incidents under 10 per month, zero incidents in the last quarter.</t>
   </si>
   <si>
-    <t>100% facial recognition and physical-check coverage across all shifts and gates.
+    <t xml:space="preserve">100% facial recognition and physical-check coverage across all shifts and gates.
 Zone-wise manpower entry captured in real time for 100% of zones, with automated variance alerts against the warehouse-sizing-based headcount plan.
 Zero unauthorized-entry incidents in the last 12 months.
 Real-time anomaly alerts.</t>
@@ -223,27 +205,27 @@
     <t>Dock Management System</t>
   </si>
   <si>
-    <t>No formal dock allocation.
+    <t xml:space="preserve">No formal dock allocation.
 Dock utilization under 50%.
 Docks unnumbered or inconsistently numbered.</t>
   </si>
   <si>
-    <t>Manual dock allocation sheet.
+    <t xml:space="preserve">Manual dock allocation sheet.
 Utilization 50-65%.</t>
   </si>
   <si>
-    <t>Defined dock allocation by vehicle size with numbered docks.
+    <t xml:space="preserve">Defined dock allocation by vehicle size with numbered docks.
 Utilization 65-80%.
 FIFO followed for over 70% of vehicles.</t>
   </si>
   <si>
-    <t>System-based dock scheduling with size-matched allocation.
+    <t xml:space="preserve">System-based dock scheduling with size-matched allocation.
 Utilization 80-90%.
 FIFO adherence above 90%.
 Green-channel vehicles unloaded within 15 minutes.</t>
   </si>
   <si>
-    <t>Fully automated dock-vehicle matching with real-time queuing.
+    <t xml:space="preserve">Fully automated dock-vehicle matching with real-time queuing.
 Utilization above 90%.
 FIFO adherence 100%.
 Green-channel wait time under 10 minutes.</t>
@@ -255,32 +237,32 @@
     <t>Dock Buffers</t>
   </si>
   <si>
-    <t>Under 25% of docks fitted with buffers.
+    <t xml:space="preserve">Under 25% of docks fitted with buffers.
 More than 1 dock-damage incident per week.
 No penalty framework for drivers causing repeat dock damage.
 Physical damage to dock structures (bumpers, levelers, shelters, columns) not tracked or inspected separately from buffer coverage.</t>
   </si>
   <si>
-    <t>25-50% buffer coverage.
+    <t xml:space="preserve">25-50% buffer coverage.
 1 dock-damage incident per week on average.
 Repeat-offender drivers flagged informally but no defined penalty applied.
 Physical dock-structure damage noted only when reported by staff, with no periodic inspection.</t>
   </si>
   <si>
-    <t>50-75% buffer coverage.
+    <t xml:space="preserve">50-75% buffer coverage.
 1 dock-damage incident every 2 weeks.
 A defined penalty (e.g., warning/fine) applied to drivers on a repeat incident.
 Physical dock-structure damage inspected monthly and logged separately from buffer-related damage.</t>
   </si>
   <si>
-    <t>75-95% buffer coverage.
+    <t xml:space="preserve">75-95% buffer coverage.
 Fewer than 1 dock-damage incident every 4 weeks.
 A graded penalty scale (warning, fine, vendor/transporter review) enforced for repeat-offender drivers.
 Periodic buffer-condition audits in place.
 Physical dock-structure damage inspected weekly with defects tracked to closure.</t>
   </si>
   <si>
-    <t>100% dock buffer coverage.
+    <t xml:space="preserve">100% dock buffer coverage.
 Zero damage incidents in the last 12 months.
 Graded penalty scale for repeat-offender drivers strictly enforced with under 2% repeat-offense rate.
 Preventive maintenance schedule tracked.
@@ -293,7 +275,7 @@
     <t>Unloading Operations &amp; Floor Management</t>
   </si>
   <si>
-    <t>No defined/target unloading SLA.
+    <t xml:space="preserve">No defined/target unloading SLA.
 No dock-wise dedicated workforce assigned.
 No defined palletisation zone (material is palletized wherever space is available, creating space constraints at the inbound gate).
 No crate-stacking pattern defined (poor vertical space utilization).
@@ -302,7 +284,7 @@
 No bypass-routing flag exists for vendor pre-packed material, so pre-packed loads are routed through S&amp;G by default regardless of need.</t>
   </si>
   <si>
-    <t>An unloading SLA is defined but tracked for under 30% of docks (benchmark: ~500 units/person/hour for pre-packed material).
+    <t xml:space="preserve">An unloading SLA is defined but tracked for under 30% of docks (benchmark: ~500 units/person/hour for pre-packed material).
 Dock-wise workforce assignment is informal.
 A palletisation zone is nominally marked but frequently encroached upon.
 Crate stacking has no defined SOP.
@@ -310,7 +292,7 @@
 A bypass flag for vendor pre-packed material is used informally for under 30% of eligible loads.</t>
   </si>
   <si>
-    <t>Unloading SLA (~500 units/person/hour pre-packed) is tracked for 30-60% of docks with a dock-wise supervisor-led team.
+    <t xml:space="preserve">Unloading SLA (~500 units/person/hour pre-packed) is tracked for 30-60% of docks with a dock-wise supervisor-led team.
 A visibly marked palletisation zone and sorting/grading area are maintained on most days.
 A crate-stacking SOP (max stack height, brick/inline pattern) is defined but followed inconsistently.
 A green channel exists for some reliable vendors.
@@ -318,7 +300,7 @@
 A bypass-routing flag for vendor pre-packed material, skipping S&amp;G and routing straight to packing/staging, is applied for 30-60% of eligible loads.</t>
   </si>
   <si>
-    <t>Unloading SLA is tracked for 60-90% of docks against benchmark, with a dock-wise supervisor-led team on every shift.
+    <t xml:space="preserve">Unloading SLA is tracked for 60-90% of docks against benchmark, with a dock-wise supervisor-led team on every shift.
 Palletisation zone, unloading area, and S&amp;G area are marked and adhered to.
 Crate-stacking SOP is followed on 70-95% of pallets.
 A green channel is consistently used for reliable vendors.
@@ -327,7 +309,7 @@
 The bypass-routing flag for vendor pre-packed material is applied for 60-90% of eligible loads, tracked as part of the load-declaration step at gate/weighment.</t>
   </si>
   <si>
-    <t>Unloading SLA is tracked for over 90% of docks and consistently meets/exceeds the ~500 units/person/hour benchmark, with a dock-wise supervisor-led team at all times.
+    <t xml:space="preserve">Unloading SLA is tracked for over 90% of docks and consistently meets/exceeds the ~500 units/person/hour benchmark, with a dock-wise supervisor-led team at all times.
 Palletisation zone, unloading area, and S&amp;G area are marked, audited, and adhered to with zero space-constraint incidents.
 Crate-stacking SOP compliance exceeds 95%.
 Green-channel and dry-category lanes operate with zero cross-flow incidents.
@@ -341,32 +323,32 @@
     <t>Weighment &amp; GRN Digitization</t>
   </si>
   <si>
-    <t>Weighment data is logged manually for GRN/PO creation - error-prone and slow.
+    <t xml:space="preserve">Weighment data is logged manually for GRN/PO creation - error-prone and slow.
 Weighment occurs downstream of S&amp;G, increasing vendor wait time and delaying PO closure.
 The weighment area sits hard against the staging area with no clear aisle, creating a choke point.
 Scale calibration is untracked.</t>
   </si>
   <si>
-    <t>Manual logging accounts for over 70% of weighment transactions.
+    <t xml:space="preserve">Manual logging accounts for over 70% of weighment transactions.
 Weighment is still performed post-S&amp;G for the majority of vehicles.
 The clear aisle between weighment and staging is under 1.5m or undefined.
 Scale calibration is done ad hoc with no fixed schedule.</t>
   </si>
   <si>
-    <t>Digital weighment is integrated with the WMS/GRN system for 30-60% of transactions.
+    <t xml:space="preserve">Digital weighment is integrated with the WMS/GRN system for 30-60% of transactions.
 Weighment has been shifted to the unloading stage for some vendor categories, reducing PO-closure delay.
 A minimum 1.5m clear aisle between weighment and staging is maintained on most days.
 Scales are calibrated on a defined but not strictly daily schedule.</t>
   </si>
   <si>
-    <t>Digital weighment integrated with WMS/GRN covers 60-90% of transactions.
+    <t xml:space="preserve">Digital weighment integrated with WMS/GRN covers 60-90% of transactions.
 Weighment is performed at the unloading stage for the majority of vendors, ahead of S&amp;G.
 The 1.5m clear-aisle buffer between weighment and staging is consistently maintained.
 Calibrated scales with tare memory per packaging type are recalibrated on a defined schedule (daily recommended).
 Digital weight logs are retained as an audit trail.</t>
   </si>
   <si>
-    <t>Over 90% of weighment transactions are digitally integrated with WMS/GRN with zero manual entry.
+    <t xml:space="preserve">Over 90% of weighment transactions are digitally integrated with WMS/GRN with zero manual entry.
 Weighment is performed at the unloading stage for all applicable vendors, enabling same-day PO closure.
 The 1.5m clear-aisle buffer is maintained with zero choke-point incidents.
 Scales are recalibrated daily with tare memory per packaging type.
@@ -379,27 +361,27 @@
     <t>Gate Release Decision &amp; Capacity Gating</t>
   </si>
   <si>
-    <t>Gate operates as a security checkpoint, not a capacity-gated release valve: trucks are waved onto the dock/yard regardless of whether a dock bay or staging space is available, with no reject / temp-reject / hold / bypass decision rule (checks vary guard-to-guard).
+    <t xml:space="preserve">Gate operates as a security checkpoint, not a capacity-gated release valve: trucks are waved onto the dock/yard regardless of whether a dock bay or staging space is available, with no reject / temp-reject / hold / bypass decision rule (checks vary guard-to-guard).
 Gate-out has no exit slip or outbound-seal verification. Vehicles routinely block the dock and back up into S&amp;G congestion.</t>
   </si>
   <si>
-    <t>A capacity check is attempted informally for under 30% of gate-ins (e.g., a phone call to the dock supervisor) with no defined time window, so vehicles sent to hold still cause dock-blocking regularly.
+    <t xml:space="preserve">A capacity check is attempted informally for under 30% of gate-ins (e.g., a phone call to the dock supervisor) with no defined time window, so vehicles sent to hold still cause dock-blocking regularly.
 Reject/hold decisions depend on individual guard judgment.
 Gate-out has no formal exit slip or seal check.</t>
   </si>
   <si>
-    <t>A defined capacity check (dock bay + staging pallet positions available within a stated window, e.g., 15 minutes) gates 30-60% of gate-ins, routing 'no' decisions to the holding area.
+    <t xml:space="preserve">A defined capacity check (dock bay + staging pallet positions available within a stated window, e.g., 15 minutes) gates 30-60% of gate-ins, routing 'no' decisions to the holding area.
 A basic reject-vs-hold rule exists, but temp-reject (scoped to 4°C SKUs) and bypass-routing (pre-packed vendors) are not yet part of the same decision rule.
 Gate-out issues an exit slip for the majority of dispatches but outbound-seal verification is inconsistent.</t>
   </si>
   <si>
-    <t>Capacity-gated release (dock bay + staging space confirmed within 15 minutes) governs 60-90% of gate-ins.
+    <t xml:space="preserve">Capacity-gated release (dock bay + staging space confirmed within 15 minutes) governs 60-90% of gate-ins.
 The full reject / temp-reject / hold / bypass decision taxonomy is defined and applied consistently, with 'hold' vehicles routed to the designated holding area.
 Gate-out issues an exit slip and verifies the outbound vehicle seal for the majority of dispatches.
 Physical enablers (multi-lane entry, boom barrier, CCTV/tablet at the gate) are in place.</t>
   </si>
   <si>
-    <t>Over 90% of gate-ins are capacity-gated in real time (dock bay + staging space confirmed within 15 minutes, tied live to the dock-management and staging systems), with zero blind releases and zero dock-blocking incidents.
+    <t xml:space="preserve">Over 90% of gate-ins are capacity-gated in real time (dock bay + staging space confirmed within 15 minutes, tied live to the dock-management and staging systems), with zero blind releases and zero dock-blocking incidents.
 The full reject / temp-reject / hold / bypass decision taxonomy is applied with a complete audit trail.
 Gate-out is fully controlled (exit slip plus outbound-seal verification on 100% of dispatches).
 Physical enablers (multi-lane entry with boom barrier, CCTV/tablet, and weighbridge where applicable) are fully deployed.</t>
@@ -483,11 +465,11 @@
     <t>0-2 of the 9 core QMS elements (policy, objectives, SOPs, exception handling, responsibility matrix, escalation matrix, risk analysis, complaints/feedback loop, documentation control) are documented.</t>
   </si>
   <si>
-    <t>3-4 elements documented.
+    <t xml:space="preserve">3-4 elements documented.
 No formal review cycle in place.</t>
   </si>
   <si>
-    <t>5-6 elements documented and in active use.
+    <t xml:space="preserve">5-6 elements documented and in active use.
 Reviewed annually.</t>
   </si>
   <si>
@@ -503,32 +485,32 @@
     <t>Inbound Quality Check Norms</t>
   </si>
   <si>
-    <t>No defined sampling percentage or rejection threshold.
+    <t xml:space="preserve">No defined sampling percentage or rejection threshold.
 Inspection is ad hoc, covering under 5% of inbound lots.
 GRN is raised and approved without any dependency on a quality-check procedure or quality-team clearance.
 Acceptance/rejection is based purely on visual inspection with no structured Arrival Quality Report (AQR) or fixed cutoff defined before unloading begins, and QC/vehicle rejection rates are not tracked by vendor or SKU.</t>
   </si>
   <si>
-    <t>Sampling done on 5-10% of lots, but rejection threshold undefined or inconsistently applied.
+    <t xml:space="preserve">Sampling done on 5-10% of lots, but rejection threshold undefined or inconsistently applied.
 GRN approval nominally requires quality-team sign-off, but this is often obtained after goods are already put away, not before GRN posting.
 A written AQR format exists but fixed sampling/defect cutoffs are not consistently applied before unloading starts.
 Rejection data is recorded but not segmented by vendor or SKU.</t>
   </si>
   <si>
-    <t>Sampling fixed at approximately 10% of received quantity.
+    <t xml:space="preserve">Sampling fixed at approximately 10% of received quantity.
 Rejection threshold set at 20% defect rate for full-lot rejection, but not segmented by SKU/category.
 GRN approval is procedurally linked to quality-team clearance, but clearance is manual/paper-based and not enforced as a system hold.
 A defined AQR is used for the majority of lots (e.g., 10% sampling, reject lot if defect &gt;20%), completed before unloading begins.
 QC reject % and vehicle rejection % are tracked in aggregate but not yet split by vendor/SKU for a supplier scorecard.</t>
   </si>
   <si>
-    <t>10% sampling and 20% rejection threshold applied and segmented by category (FnV vs dry), with batch/expiry and 70-80% shelf-life checks enforced.
+    <t xml:space="preserve">10% sampling and 20% rejection threshold applied and segmented by category (FnV vs dry), with batch/expiry and 70-80% shelf-life checks enforced.
 GRN cannot be posted until the quality team records clearance against the defined inspection procedure.
 AQR with fixed sampling/defect cutoffs is completed before unloading starts for 85-95% of lots.
 QC reject % and vehicle rejection % are tracked by vendor and SKU and feed a periodic supplier scorecard.</t>
   </si>
   <si>
-    <t>Sampling and rejection norms (10%/20%) defined per SKU category, digitally logged, with under 2% inspection-error rate and monthly trend analysis on rejection causes.
+    <t xml:space="preserve">Sampling and rejection norms (10%/20%) defined per SKU category, digitally logged, with under 2% inspection-error rate and monthly trend analysis on rejection causes.
 GRN approval is system-enforced with zero exceptions, released only on digital quality-team clearance against the defined procedure, with a full audit trail of inspector sign-off.
 AQR is completed before unloading begins for over 95% of lots with zero exceptions.
 QC reject % and vehicle rejection % by vendor and SKU are tracked in real time and drive an automated, continuously updated supplier scorecard used in vendor review.</t>
@@ -540,24 +522,24 @@
     <t>Return to Vendor Policy</t>
   </si>
   <si>
-    <t>No defined return-to-vendor (RTV) policy.
+    <t xml:space="preserve">No defined return-to-vendor (RTV) policy.
 Under 30% of returns closed same-day.</t>
   </si>
   <si>
-    <t>Informal RTV process.
+    <t xml:space="preserve">Informal RTV process.
 30-50% same-day closure.</t>
   </si>
   <si>
-    <t>RTV policy defined by SKU category (hard/soft).
+    <t xml:space="preserve">RTV policy defined by SKU category (hard/soft).
 50-75% same-day closure.</t>
   </si>
   <si>
-    <t>RTV policy defined and tracked.
+    <t xml:space="preserve">RTV policy defined and tracked.
 75-95% same-day closure.
 Space occupied by pending returns reviewed weekly.</t>
   </si>
   <si>
-    <t>RTV fully systemized.
+    <t xml:space="preserve">RTV fully systemized.
 Over 95% same-day closure.
 Zero aged-return inventory beyond 24 hours.</t>
   </si>
@@ -568,23 +550,23 @@
     <t>Customer Complaint Tracking</t>
   </si>
   <si>
-    <t>Complaint rate exceeds 3% of FnV volume handled, or is not tracked at all.
+    <t xml:space="preserve">Complaint rate exceeds 3% of FnV volume handled, or is not tracked at all.
 Complaint density is not tracked in PPM at all, or exceeds 500 PPM where estimated, so order-level density cannot be benchmarked against a quick-commerce/dark-store standard.</t>
   </si>
   <si>
-    <t>Complaint rate tracked at 2.5-3%, with no root-cause analysis.
+    <t xml:space="preserve">Complaint rate tracked at 2.5-3%, with no root-cause analysis.
 Complaints PPM runs at 200-500, calculated only occasionally/retrospectively.</t>
   </si>
   <si>
-    <t>Complaint rate at the typical industry band of 2-2.5%, tracked monthly with basic categorization.
+    <t xml:space="preserve">Complaint rate at the typical industry band of 2-2.5%, tracked monthly with basic categorization.
 Complaints PPM runs at 100-200, tracked monthly alongside the %-of-volume metric.</t>
   </si>
   <si>
-    <t>Complaint rate reduced to 1-2%, with root-cause analysis and corrective actions closed within 7 days.
+    <t xml:space="preserve">Complaint rate reduced to 1-2%, with root-cause analysis and corrective actions closed within 7 days.
 Complaints PPM runs at 50-100, tracked weekly against a defined benchmark band.</t>
   </si>
   <si>
-    <t>Complaint rate under 1% (best-in-class), with real-time tracking, root-cause analysis, and closed-loop resolution within 48 hours.
+    <t xml:space="preserve">Complaint rate under 1% (best-in-class), with real-time tracking, root-cause analysis, and closed-loop resolution within 48 hours.
 Complaints PPM is held under 50 (best-in-class), tracked daily against benchmark, giving both a wholesale (volume-based) and dark-store/quick-commerce (order-based) view of complaint density.</t>
   </si>
   <si>
@@ -642,33 +624,33 @@
     <t>5S Implementation</t>
   </si>
   <si>
-    <t>No formal 5S audit.
+    <t xml:space="preserve">No formal 5S audit.
 Audit score under 40% where measured at all.
 No physical demarcation of aisles, S&amp;G/packing areas, storage space, buffer-pallet staging, packaging-material storage, or tools/machinery locations - floor markings, if any, are inconsistent or absent.
 No designated area/zone name signage, fire extinguisher position signage, or fire exit signage is installed anywhere in the facility.</t>
   </si>
   <si>
-    <t>5S introduced in a pilot area only.
+    <t xml:space="preserve">5S introduced in a pilot area only.
 Audit score 40-55%.
 Floor marking/demarcation done for under 30% of the required zones (aisles, S&amp;G/packing spaces, storage, buffer-pallet staging, packaging material, tools/machinery), and only in the pilot area.
 Signage exists for a few zones and fire extinguisher points only, limited to the pilot area; fire exits are marked but not consistently visible or illuminated.</t>
   </si>
   <si>
-    <t>Sort/Set/Shine implemented facility-wide.
+    <t xml:space="preserve">Sort/Set/Shine implemented facility-wide.
 Audit score 55-70%.
 Audits conducted quarterly.
 Demarcation in place for 30-60% of required zones - e.g., aisles and storage racking are marked, but S&amp;G/packing space, buffer-pallet staging, packaging-material, and tools/machinery locations are only partially marked.
 Designated area signage and fire extinguisher position signage are installed for 30-60% of required zones/points; fire exits are signed and illuminated for the main escape routes only.</t>
   </si>
   <si>
-    <t>Standardized across all zones with monthly audits.
+    <t xml:space="preserve">Standardized across all zones with monthly audits.
 Score 70-85%.
 Training conducted at least twice a year.
 Demarcation covers 60-90% of required zones, including aisles, S&amp;G and packing space boundaries, storage space marking, buffer-pallet staging area, and packaging-material storage, with tools/machinery locations marked but not yet audited on a fixed schedule.
 Area signage, fire extinguisher signage, and fire exit signage cover 60-90% of required zones/points/routes, checked alongside the periodic 5S review.</t>
   </si>
   <si>
-    <t>5S sustained for over 12 months.
+    <t xml:space="preserve">5S sustained for over 12 months.
 Audit score above 85%.
 Daily checks, biannual training, and a documented continuous-improvement (Kaizen) count.
 100% of zones demarcated and colour-coded - aisles, S&amp;G and packing spaces, storage space, buffer-pallet staging, packaging-material storage, and tools/machinery locations - with demarcation adherence audited as part of the daily 5S check.
@@ -681,25 +663,25 @@
     <t>Lean Principles Implementation</t>
   </si>
   <si>
-    <t>0-1 of the 5 lean principles (value definition, value stream mapping, flow, pull, continuous improvement) deployed.
+    <t xml:space="preserve">0-1 of the 5 lean principles (value definition, value stream mapping, flow, pull, continuous improvement) deployed.
 No PDCA or waste tracking.</t>
   </si>
   <si>
-    <t>2 principles deployed (e.g., value stream mapping started).
+    <t xml:space="preserve">2 principles deployed (e.g., value stream mapping started).
 PDCA used in under 20% of processes.</t>
   </si>
   <si>
-    <t>3 principles deployed.
+    <t xml:space="preserve">3 principles deployed.
 PDCA embedded in 20-50% of processes.
 2-3 of the 8 waste types tracked.</t>
   </si>
   <si>
-    <t>4 principles deployed with pull/JIT replenishment active.
+    <t xml:space="preserve">4 principles deployed with pull/JIT replenishment active.
 PDCA in 50-80% of processes.
 5-6 of the 8 waste types tracked with quarterly reduction targets.</t>
   </si>
   <si>
-    <t>All 5 principles fully embedded.
+    <t xml:space="preserve">All 5 principles fully embedded.
 PDCA in over 80% of processes.
 All 8 waste types tracked with measurable year-on-year reduction of over 10%.</t>
   </si>
@@ -713,7 +695,7 @@
     <t>Under 30% of standard and exception scenarios documented in SOPs.</t>
   </si>
   <si>
-    <t>30-50% documented.
+    <t xml:space="preserve">30-50% documented.
 Exception flows largely undocumented.</t>
   </si>
   <si>
@@ -738,28 +720,28 @@
     <t>Sorting &amp; Grading Norms</t>
   </si>
   <si>
-    <t>No defined size or quality standards (blemish-free, rot-free, infestation-free) for sorting/grading.
+    <t xml:space="preserve">No defined size or quality standards (blemish-free, rot-free, infestation-free) for sorting/grading.
 Criteria applied on 0% of SKUs.
 No S&amp;G throughput SLA is defined (benchmark: ~70 units/person/hour for general S&amp;G, 400-500 units/person/shift for leafy cutting).
 Piece-category SKUs (e.g., coconut, watermelon) are staffed randomly, causing significant throughput slowdown.</t>
   </si>
   <si>
-    <t>Standards defined for under 30% of SKUs.
+    <t xml:space="preserve">Standards defined for under 30% of SKUs.
 A throughput SLA is defined but tracked for under 30% of stations, with wide variance against the ~70 units/person/hour / 400-500 units/person/shift benchmarks.
 Piece-category SKUs are not assigned to experienced manpower.</t>
   </si>
   <si>
-    <t>Standards defined for 30-60% of SKUs, covering blemish, rot, infestation, and size checks.
+    <t xml:space="preserve">Standards defined for 30-60% of SKUs, covering blemish, rot, infestation, and size checks.
 Throughput SLA (~70 units/person/hour, 400-500/shift for leafy) is tracked for 30-60% of stations.
 Experienced manpower is assigned to piece-category SKUs (coconut, watermelon) only inconsistently.</t>
   </si>
   <si>
-    <t>Standards defined for 60-90% of SKUs, with grading accuracy audited monthly at over 90% accuracy.
+    <t xml:space="preserve">Standards defined for 60-90% of SKUs, with grading accuracy audited monthly at over 90% accuracy.
 Throughput SLA is tracked for 60-90% of stations, mostly within benchmark.
 Experienced manpower is consistently assigned to piece-category SKUs, limiting their drag on overall S&amp;G throughput.</t>
   </si>
   <si>
-    <t>Standards defined for 100% of SKUs.
+    <t xml:space="preserve">Standards defined for 100% of SKUs.
 Grading accuracy above 95%, audited weekly with a corrective feedback loop.
 Throughput SLA is tracked for 100% of stations and consistently meets or exceeds benchmark (~70 units/person/hour, 400-500/shift leafy).
 Piece-category SKUs are always staffed with experienced manpower, with throughput impact monitored and minimized.</t>
@@ -771,7 +753,7 @@
     <t>Packing Norms &amp; Productivity</t>
   </si>
   <si>
-    <t>Packing productivity under 60 units/person/hour.
+    <t xml:space="preserve">Packing productivity under 60 units/person/hour.
 Packaging material (nets/boxes/LDP) not defined by SKU.
 No shift-level SLA is tracked against the net/box/shrink packing benchmarks (~900-1,000 net, ~1,100-1,200 box, ~1,000-1,100 shrink units/person/shift).
 Formed boxes are stacked directly on the worktop causing clutter.
@@ -779,7 +761,7 @@
 Chilled-category SKUs (e.g., apples, pears) are packed under ambient conditions with no dedicated chilled station.</t>
   </si>
   <si>
-    <t>Productivity 60-80 units/person/hour.
+    <t xml:space="preserve">Productivity 60-80 units/person/hour.
 Packaging material defined for under 50% of SKUs.
 Shift-level SLA is tracked for under 30% of lines against the net/box/shrink benchmarks.
 A formed-box staging shelf is used on under 30% of lines.
@@ -787,7 +769,7 @@
 Chilled SKUs are packed ambient on over 70% of shifts.</t>
   </si>
   <si>
-    <t>Productivity at the 80-100 units/person/hour benchmark band.
+    <t xml:space="preserve">Productivity at the 80-100 units/person/hour benchmark band.
 Packaging material defined per SKU.
 Shift-level SLA is tracked for 30-60% of lines and trending toward the net/box/shrink benchmarks.
 A formed-box staging shelf decongests the worktop on 30-60% of lines.
@@ -795,7 +777,7 @@
 A dedicated chilled packing station is used for 30-60% of chilled-SKU shifts.</t>
   </si>
   <si>
-    <t>Productivity 100-120 units/person/hour, matching category benchmarks (net roll ~90/hr, pannet ~100/hr, LDP ~100/hr).
+    <t xml:space="preserve">Productivity 100-120 units/person/hour, matching category benchmarks (net roll ~90/hr, pannet ~100/hr, LDP ~100/hr).
 Gang output tracked daily against a 400-500 packets/person/day target.
 Shift-level SLA is tracked for 60-90% of lines and mostly at benchmark (~900-1,200 units/person/shift by pack type).
 Formed-box staging shelf standard is followed on 60-90% of lines.
@@ -803,7 +785,7 @@
 A dedicated chilled packing station is used for 60-90% of chilled-SKU shifts.</t>
   </si>
   <si>
-    <t>Productivity above 120 units/person/hour or consistently at the top of the category benchmark.
+    <t xml:space="preserve">Productivity above 120 units/person/hour or consistently at the top of the category benchmark.
 A 4-cutter + 6-packer gang achieving 4,000+ packets/day, tracked and improved monthly.
 Shift-level SLA is tracked for over 90% of lines and consistently at or above benchmark.
 Formed-box staging shelf standard is followed on all lines.
@@ -817,28 +799,28 @@
     <t>Manpower Planning for Processing</t>
   </si>
   <si>
-    <t>No standard manpower norm for processing tables.
+    <t xml:space="preserve">No standard manpower norm for processing tables.
 Occupancy varies randomly (under 2 or over 6 people per 8ft x 4ft table).
 No defined ratio of S&amp;G tables to packaging tables - S&amp;G tables are frequently fewer than packing tables, bottlenecking downstream packaging input.
 No cleaning step is enforced between vendors' S&amp;G batches, causing clutter and cross-contamination risk.</t>
   </si>
   <si>
-    <t>Norm defined (4 people per 8ft x 4ft table) but followed on under 40% of tables.
+    <t xml:space="preserve">Norm defined (4 people per 8ft x 4ft table) but followed on under 40% of tables.
 An S&amp;G-to-packing table ratio is loosely followed for under 40% of shifts, with S&amp;G output frequently under-matched to packing input.
 Inter-vendor cleaning is ad hoc.</t>
   </si>
   <si>
-    <t>4-person-per-table norm followed on 40-70% of tables.
+    <t xml:space="preserve">4-person-per-table norm followed on 40-70% of tables.
 S&amp;G-to-packing table ratio is matched to keep S&amp;G output aligned with packing input on 40-70% of shifts.
 Cleaning between vendors' S&amp;G batches is performed inconsistently.</t>
   </si>
   <si>
-    <t>Norm followed on 70-95% of tables, monitored via regular floor walks.
+    <t xml:space="preserve">Norm followed on 70-95% of tables, monitored via regular floor walks.
 S&amp;G-to-packing table ratio and output-input matching is maintained on 70-95% of shifts, monitored via floor walks.
 Cleaning after each vendor's S&amp;G batch is standard practice.</t>
   </si>
   <si>
-    <t>Norm followed on over 95% of tables at all times, with real-time floor supervision preventing congestion or under-utilization.
+    <t xml:space="preserve">Norm followed on over 95% of tables at all times, with real-time floor supervision preventing congestion or under-utilization.
 S&amp;G-to-packing table ratio and output-input matching is maintained on over 95% of shifts with real-time supervision.
 Cleaning after every vendor's S&amp;G batch is enforced with zero cross-contamination incidents.</t>
   </si>
@@ -849,23 +831,23 @@
     <t>Shrinkage &amp; Seasonal Loss Management</t>
   </si>
   <si>
-    <t>Shrinkage not tracked by SKU category.
+    <t xml:space="preserve">Shrinkage not tracked by SKU category.
 Overall loss exceeds 5% with no seasonal breakup.</t>
   </si>
   <si>
-    <t>Shrinkage tracked in aggregate only.
+    <t xml:space="preserve">Shrinkage tracked in aggregate only.
 No category-specific targets (e.g., leafy items vs vegetables like brinjal).</t>
   </si>
   <si>
-    <t>Shrinkage tracked by category against benchmark ranges (up to 30-35% for leafy items, 1-2% for vegetables like brinjal).
+    <t xml:space="preserve">Shrinkage tracked by category against benchmark ranges (up to 30-35% for leafy items, 1-2% for vegetables like brinjal).
 Seasonal RTV loss tracked at a 1.5-3% band (winter to monsoon).</t>
   </si>
   <si>
-    <t>Shrinkage within benchmark for over 80% of SKU categories.
+    <t xml:space="preserve">Shrinkage within benchmark for over 80% of SKU categories.
 Seasonal loss trend reviewed monthly with corrective action for outliers.</t>
   </si>
   <si>
-    <t>Shrinkage consistently at or below benchmark for all categories.
+    <t xml:space="preserve">Shrinkage consistently at or below benchmark for all categories.
 Seasonal loss held at 1.5% or below even during monsoon.
 Monthly root-cause review with documented reduction actions.</t>
   </si>
@@ -876,26 +858,26 @@
     <t>Repacking Reduction Targets</t>
   </si>
   <si>
-    <t>Repacking/re-stickering rate not measured.
+    <t xml:space="preserve">Repacking/re-stickering rate not measured.
 Anecdotally exceeds 8% of units reworked.
 Cause coding does not distinguish avoidable rework such as re-sorting already vendor-packed bananas at the packing stage, ripeness-based segregation (e.g., mango, avocado) being performed late at the packing stage instead of at S&amp;G, or idle organic-table capacity - all of which inflate the repack rate.</t>
   </si>
   <si>
-    <t>Measured but no target set.
+    <t xml:space="preserve">Measured but no target set.
 Rate at 5-8%.
 Rate is measured in aggregate without cause coding for these specific drivers (banana re-sort, late ripeness segregation, idle organic-table capacity).</t>
   </si>
   <si>
-    <t>Target set at 5% or below.
+    <t xml:space="preserve">Target set at 5% or below.
 Actual performance running at 5-6%.
 Cause coding identifies banana re-sort, late ripeness segregation, and idle organic-table time as contributors, but corrective action (stopping banana re-sort, moving ripeness segregation to the S&amp;G stage, converting the organic table to multi-use) is applied inconsistently.</t>
   </si>
   <si>
-    <t>Actual rate 2-5%, tracked weekly with cause coding.
+    <t xml:space="preserve">Actual rate 2-5%, tracked weekly with cause coding.
 Banana re-sort at packing is eliminated, ripeness-based segregation is performed at the S&amp;G stage, and the organic table is run as a time-clustered multi-use table on 70-95% of shifts, reflected in the weekly cause-coded repack trend.</t>
   </si>
   <si>
-    <t>Rate under 2%, tracked daily, root cause eliminated at source (labeling/QC), sustained for 2+ consecutive quarters.
+    <t xml:space="preserve">Rate under 2%, tracked daily, root cause eliminated at source (labeling/QC), sustained for 2+ consecutive quarters.
 Banana re-sort at packing is fully eliminated, ripeness-based segregation is performed at the S&amp;G stage on 100% of shifts, and the organic table is consistently run as a multi-use table in downtime, sustained for 2+ consecutive quarters as a root-cause-eliminated driver of the sub-2% repack rate.</t>
   </si>
   <si>
@@ -932,32 +914,32 @@
     <t>Demand Planning</t>
   </si>
   <si>
-    <t>0-1 of the 5 demand-planning layers (baseline/historical, seasonal &amp; festive, event-based/sales, time-of-day, area/hyperlocal behavior) in use.
+    <t xml:space="preserve">0-1 of the 5 demand-planning layers (baseline/historical, seasonal &amp; festive, event-based/sales, time-of-day, area/hyperlocal behavior) in use.
 Forecast accuracy under 60%.
 Hourly-volatility and SKU-level inaccuracy are not analyzed, and new-store locations run on no meaningful demand data (pure guesswork).</t>
   </si>
   <si>
-    <t>2 layers active.
+    <t xml:space="preserve">2 layers active.
 Forecast accuracy 60-75%.
 Hourly volatility and hyperlocal (area-level) variation are acknowledged but not modeled.
 New stores use a flat citywide/category average with no ramp-up curve.</t>
   </si>
   <si>
-    <t>3 layers active (e.g., baseline + seasonal/festive + event-based).
+    <t xml:space="preserve">3 layers active (e.g., baseline + seasonal/festive + event-based).
 Forecast accuracy 75-85%.
 Time-of-day demand curves are tracked for under 50% of SKUs/stores.
 Hyperlocal (area-behavior) variation is factored in for high-volume stores only.
 New stores follow a defined but generic ramp-up curve.</t>
   </si>
   <si>
-    <t>4 of the 5 layers active (typically missing time-of-day or area-behavior).
+    <t xml:space="preserve">4 of the 5 layers active (typically missing time-of-day or area-behavior).
 Forecast accuracy 85-95%.
 Time-of-day and hyperlocal demand patterns are modeled for 70-90% of stores.
 SKU-level forecast error is tracked and root-caused monthly.
 New-store data gaps are bridged with a comparable-store proxy model for the first 4-6 weeks.</t>
   </si>
   <si>
-    <t>All 5 layers active and continuously calibrated against actuals (baseline, seasonal/festive, event-based, time-of-day, hyperlocal/area-behavior).
+    <t xml:space="preserve">All 5 layers active and continuously calibrated against actuals (baseline, seasonal/festive, event-based, time-of-day, hyperlocal/area-behavior).
 Forecast accuracy above 95%, directly driving the fill-rate KPI.
 Hourly volatility and SKU-level accuracy are tracked in real time with automated recalibration.
 New-store demand gaps are closed within 2-4 weeks via a proxy-to-actual transition model.</t>
@@ -969,29 +951,29 @@
     <t>Inventory Planning</t>
   </si>
   <si>
-    <t>0-1 of the 5 inventory-planning components (regular+buffer stock, seasonal buffer of +15-20%, festive buffer of +50-100%, FEFO discipline for fresh/perishable SKUs, SKU assortment) defined.
+    <t xml:space="preserve">0-1 of the 5 inventory-planning components (regular+buffer stock, seasonal buffer of +15-20%, festive buffer of +50-100%, FEFO discipline for fresh/perishable SKUs, SKU assortment) defined.
 Stockout/excess (waste) incidents affect over 20% of SKUs monthly.
 Batch/expiry tracking is manual or absent, and shelf-life-driven markdowns/write-offs are not visible until after the fact.</t>
   </si>
   <si>
-    <t>2 components defined.
+    <t xml:space="preserve">2 components defined.
 Incidents affect 10-20% of SKUs monthly.
 FEFO is followed inconsistently, with batch mismanagement (wrong batch picked/dispatched) as a regular occurrence.
 Inventory visibility lags actual stock by more than a day.</t>
   </si>
   <si>
-    <t>3 components defined (e.g., regular+buffer stock, one of seasonal/festive buffer, and a defined SKU assortment).
+    <t xml:space="preserve">3 components defined (e.g., regular+buffer stock, one of seasonal/festive buffer, and a defined SKU assortment).
 Incidents affect 5-10% of SKUs monthly.
 FEFO is enforced for the majority of fresh SKUs.
 Batch-level visibility exists but is not real-time, creating an occasional stockout-vs-waste trade-off at the shelf-life boundary.</t>
   </si>
   <si>
-    <t>4 of the 5 components defined and reviewed monthly (seasonal +15-20% and festive +50-100% buffers both applied, FEFO enforced for fresh).
+    <t xml:space="preserve">4 of the 5 components defined and reviewed monthly (seasonal +15-20% and festive +50-100% buffers both applied, FEFO enforced for fresh).
 Incidents affect under 5% of SKUs monthly.
 Batch/expiry data is visible near-real-time, keeping the stockout-vs-waste trade-off and batch mismanagement to isolated exceptions.</t>
   </si>
   <si>
-    <t>All 5 components defined, automated, and reviewed weekly (regular+buffer stock, seasonal +15-20% buffer, festive +50-100% buffer, FEFO for fresh, SKU assortment).
+    <t xml:space="preserve">All 5 components defined, automated, and reviewed weekly (regular+buffer stock, seasonal +15-20% buffer, festive +50-100% buffer, FEFO for fresh, SKU assortment).
 Incidents affect under 2% of SKUs monthly.
 Batch/expiry visibility is real-time and system-enforced, eliminating batch mismanagement and holding the stockout-vs-waste trade-off within a defined tolerance.</t>
   </si>
@@ -1002,13 +984,13 @@
     <t>Replenishment Planning</t>
   </si>
   <si>
-    <t>Replenishment triggered manually and irregularly.
+    <t xml:space="preserve">Replenishment triggered manually and irregularly.
 No defined formula (Forecast Demand + Safety Stock - Current Inventory) or wave structure.
 No min-max or reorder-point model is defined, no emergency top-up process exists for stockout risk, and days-of-inventory (DoI) is not tracked.
 Partial fulfillment, dock congestion at replenishment receipt, and storage overflow are common and unmanaged.</t>
   </si>
   <si>
-    <t>Formula-based replenishment defined but run less than once a day.
+    <t xml:space="preserve">Formula-based replenishment defined but run less than once a day.
 Wave split ad hoc.
 A min-max or reorder-point trigger is defined for under 30% of SKUs.
 Emergency top-up is handled ad hoc with no defined SLA.
@@ -1016,7 +998,7 @@
 Partial fulfillment and storage overflow incidents are frequent.</t>
   </si>
   <si>
-    <t>Replenishment run once a day using the standard formula.
+    <t xml:space="preserve">Replenishment run once a day using the standard formula.
 Wave timing not optimized.
 Min-max/reorder-point triggers cover 30-60% of SKUs.
 A defined but manually-invoked emergency top-up process exists.
@@ -1024,14 +1006,14 @@
 Dock congestion from replenishment receipts is reviewed but not systematically avoided.</t>
   </si>
   <si>
-    <t>Replenishment run twice a day with a defined wave split (e.g., 70% first wave / 30% second wave).
+    <t xml:space="preserve">Replenishment run twice a day with a defined wave split (e.g., 70% first wave / 30% second wave).
 Lead time and buffer capacity factored in.
 Min-max/reorder-point triggers cover 60-90% of SKUs with an SLA-bound emergency top-up process.
 DoI is tracked by SKU against a target band.
 Dock-congestion and storage-overflow incidents from replenishment receipt are reduced to isolated exceptions.</t>
   </si>
   <si>
-    <t>Fully automated twice-daily (or more frequent) replenishment cycle with an optimized wave split (e.g., 70/30), lead-time-adjusted safety stock, and under 2% stockout rate at dark stores.
+    <t xml:space="preserve">Fully automated twice-daily (or more frequent) replenishment cycle with an optimized wave split (e.g., 70/30), lead-time-adjusted safety stock, and under 2% stockout rate at dark stores.
 Min-max/reorder-point triggers cover over 90% of SKUs, integrated with an automated, SLA-bound emergency top-up process (ARS).
 DoI is tracked by SKU in real time against target bands.
 Dock congestion and storage overflow from replenishment receipts are eliminated through slotted receiving.
@@ -1044,13 +1026,13 @@
     <t>Manpower &amp; Capacity Planning</t>
   </si>
   <si>
-    <t>0-2 of 6 roles (inbound, outbound/picking, packing, put-away, supervisory, security) have defined manpower planning.
+    <t xml:space="preserve">0-2 of 6 roles (inbound, outbound/picking, packing, put-away, supervisory, security) have defined manpower planning.
 Staffing variance exceeds 20%.
 No surge-planning mechanism for demand spikes and no defined gig-workforce flexibility strategy.
 Staffing decisions ignore diurnal (hour-of-day) demand variability, and attrition/gig-supply risk are not tracked.</t>
   </si>
   <si>
-    <t>3 roles planned.
+    <t xml:space="preserve">3 roles planned.
 Staffing variance 15-20%.
 Surge planning is reactive (arranged only after a spike is already underway).
 Gig-workforce usage is ad hoc with no defined flex ratio.
@@ -1058,20 +1040,20 @@
 Attrition is tracked but not analyzed.</t>
   </si>
   <si>
-    <t>4 roles planned.
+    <t xml:space="preserve">4 roles planned.
 Variance 10-15%.
 A surge-planning trigger and a defined gig-to-permanent flex ratio exist for under 60% of shifts.
 Shift design accounts for diurnal variability for the main peak window only.
 Attrition and gig-supply risk are tracked monthly without a mitigation plan.</t>
   </si>
   <si>
-    <t>5 roles planned with shift-level granularity.
+    <t xml:space="preserve">5 roles planned with shift-level granularity.
 Variance 5-10%.
 Surge planning and a defined gig-flex ratio are applied on 60-90% of shifts, with shift design built around the full diurnal demand curve.
 Attrition and gig-supply risk are tracked with an active mitigation/backup-pool plan.</t>
   </si>
   <si>
-    <t>All 6 roles planned with daily granularity and capacity buffers.
+    <t xml:space="preserve">All 6 roles planned with daily granularity and capacity buffers.
 Variance under 5%.
 Surge planning and gig-flex ratio are applied on over 90% of shifts with capacity buffers pre-built into the roster.
 Shift design is fully diurnal-curve-driven.
@@ -1084,7 +1066,7 @@
     <t>Network Planning</t>
   </si>
   <si>
-    <t>Fewer than 1 planned warehouse-to-dark-store replenishment cycle per day.
+    <t xml:space="preserve">Fewer than 1 planned warehouse-to-dark-store replenishment cycle per day.
 Dispatch is ad hoc.
 No route optimization or truck-load optimization is applied (vehicles dispatched part-full or on unoptimized routes).
 No formal pick-path design exists, causing inefficient in-warehouse travel.
@@ -1092,7 +1074,7 @@
 Inbound to not-yet-live (pre-live) dark stores is unplanned and causes downstream issues.</t>
   </si>
   <si>
-    <t>1 cycle per day.
+    <t xml:space="preserve">1 cycle per day.
 Wave split not defined.
 Route/truck-load optimization is applied to under 30% of dispatch routes.
 Pick-path design is undefined, with operators walking ad hoc.
@@ -1100,14 +1082,14 @@
 Pre-live-store inward is handled the same as live-store inward with no distinction.</t>
   </si>
   <si>
-    <t>1-2 cycles per day with a defined split (approximately 70/30), but adherence under 70%.
+    <t xml:space="preserve">1-2 cycles per day with a defined split (approximately 70/30), but adherence under 70%.
 Route/truck-load optimization covers 30-60% of dispatch routes.
 A basic pick-path layout exists but is not distance-optimized.
 Freezer/cold-chain capacity is checked before dispatch for temperature-sensitive SKUs only.
 Pre-live dark-store inward follows a separate but informal process.</t>
   </si>
   <si>
-    <t>2 cycles per day with a 70/30 (or optimized) split.
+    <t xml:space="preserve">2 cycles per day with a 70/30 (or optimized) split.
 Adherence 70-90%.
 Route/truck-load optimization covers 60-90% of dispatch routes, holding OPH (orders-per-hour) close to target.
 Pick-path design is distance-optimized and reviewed periodically.
@@ -1115,7 +1097,7 @@
 Pre-live dark-store inward follows a defined, separate SOP.</t>
   </si>
   <si>
-    <t>2 or more cycles per day, wave-split adherence above 90%, dynamically adjusted to dark-store stock positions in real time.
+    <t xml:space="preserve">2 or more cycles per day, wave-split adherence above 90%, dynamically adjusted to dark-store stock positions in real time.
 Route/truck-load optimization covers over 90% of dispatch routes with OPH consistently at or above target.
 Pick-path design is continuously optimized using movement data.
 Freezer/cold-chain capacity is dynamically planned with zero temperature-zone breaches.
@@ -1128,19 +1110,19 @@
     <t>Planning Cycle &amp; Fill Rate Monitoring</t>
   </si>
   <si>
-    <t>Fill rate under 70%.
+    <t xml:space="preserve">Fill rate under 70%.
 No defined D-minus planning day.</t>
   </si>
   <si>
-    <t>Fill rate 70-80%.
+    <t xml:space="preserve">Fill rate 70-80%.
 D-minus planning cycle used inconsistently.</t>
   </si>
   <si>
-    <t>Fill rate 80-90%.
+    <t xml:space="preserve">Fill rate 80-90%.
 D-minus planning day formally defined and followed for FnV/dry categories.</t>
   </si>
   <si>
-    <t>Fill rate 90-95%.
+    <t xml:space="preserve">Fill rate 90-95%.
 D-minus cycle followed consistently, with variance root-caused monthly.</t>
   </si>
   <si>
@@ -1153,25 +1135,25 @@
     <t>Supplier Planning &amp; Risk Management</t>
   </si>
   <si>
-    <t>Supplier performance (quality variability, lead-time risk, price volatility, OTIF - on-time-in-full) is not tracked in any structured way.
+    <t xml:space="preserve">Supplier performance (quality variability, lead-time risk, price volatility, OTIF - on-time-in-full) is not tracked in any structured way.
 Sourcing decisions are made without visibility into any of these four dimensions.
 OTIF is neither defined nor measured.</t>
   </si>
   <si>
-    <t>One of the four dimensions (typically OTIF or price) is tracked in aggregate, with no vendor-level or SKU-level breakdown.
+    <t xml:space="preserve">One of the four dimensions (typically OTIF or price) is tracked in aggregate, with no vendor-level or SKU-level breakdown.
 Quality variability and lead-time risk are known anecdotally but not measured.</t>
   </si>
   <si>
-    <t>2-3 of the four dimensions are tracked by vendor (e.g., OTIF % and lead-time variance), reviewed periodically (e.g., quarterly), but not yet linked to sourcing/allocation decisions.
+    <t xml:space="preserve">2-3 of the four dimensions are tracked by vendor (e.g., OTIF % and lead-time variance), reviewed periodically (e.g., quarterly), but not yet linked to sourcing/allocation decisions.
 Price volatility is monitored but not hedged or contracted against.</t>
   </si>
   <si>
-    <t>All four dimensions (quality variability, lead-time risk, price volatility, OTIF) are tracked by vendor and reviewed monthly, feeding a basic supplier scorecard.
+    <t xml:space="preserve">All four dimensions (quality variability, lead-time risk, price volatility, OTIF) are tracked by vendor and reviewed monthly, feeding a basic supplier scorecard.
 Sourcing allocation is adjusted for chronic OTIF/quality underperformers.
 Price volatility is partially managed via defined contracting/hedging for key SKUs.</t>
   </si>
   <si>
-    <t>All four dimensions are tracked by vendor and SKU in real time via an automated supplier scorecard, directly driving sourcing/allocation decisions and vendor tiering.
+    <t xml:space="preserve">All four dimensions are tracked by vendor and SKU in real time via an automated supplier scorecard, directly driving sourcing/allocation decisions and vendor tiering.
 OTIF is held above a defined benchmark (e.g., 95%+).
 Price volatility is actively hedged/contracted for the majority of high-value categories, with quarterly vendor business reviews closing the loop on quality and lead-time risk.</t>
   </si>
@@ -1407,11 +1389,11 @@
     <t>Throughput at 75-90% of benchmark (approximately 3-3.6 units/sq ft FnV, 17-20 units/sq ft dry).</t>
   </si>
   <si>
-    <t>Throughput at 90-100% of benchmark (4 units/sq ft FnV, 22.5-25 units/sq ft dry).
+    <t xml:space="preserve">Throughput at 90-100% of benchmark (4 units/sq ft FnV, 22.5-25 units/sq ft dry).
 Outbound dispatch capacity validated at approximately 4x warehouse area.</t>
   </si>
   <si>
-    <t>Throughput consistently at or above benchmark.
+    <t xml:space="preserve">Throughput consistently at or above benchmark.
 Dispatch capacity engineered and validated at exactly 4x warehouse area (e.g., a 50,000 sq ft facility supporting 200,000-unit dispatch capacity), reviewed quarterly.</t>
   </si>
   <si>
@@ -1421,19 +1403,19 @@
     <t>Warehouse Layout Design</t>
   </si>
   <si>
-    <t>Layout not benchmarked against SPR/MTR design standards.
+    <t xml:space="preserve">Layout not benchmarked against SPR/MTR design standards.
 Storage-area ratio undefined or deviates over 70% from the 50-60% norm.</t>
   </si>
   <si>
-    <t>Partial benchmarking.
+    <t xml:space="preserve">Partial benchmarking.
 Storage ratio in the 60-70% band (too high, indicating processing-area shortfall) or below 40%.</t>
   </si>
   <si>
-    <t>Storage area at 50-60% of total footprint per design norm.
+    <t xml:space="preserve">Storage area at 50-60% of total footprint per design norm.
 Aisle widths (~10 ft) and beam lengths (~2.4m) mostly conform to standard.</t>
   </si>
   <si>
-    <t>Full conformance to SPR/MTR specifications (aisle width, 100mm overhang, 3-4 ft sprinkler clearance) with storage ratio at 50-55%, or up to 60% for high-inventory/smaller-city sites.
+    <t xml:space="preserve">Full conformance to SPR/MTR specifications (aisle width, 100mm overhang, 3-4 ft sprinkler clearance) with storage ratio at 50-55%, or up to 60% for high-inventory/smaller-city sites.
 Density near 22.5 units/sq ft.</t>
   </si>
   <si>
@@ -1446,19 +1428,19 @@
     <t>Cost per Unit Tracking</t>
   </si>
   <si>
-    <t>0-2 of the 6 cost components (manpower, material supply, packaging, electricity, depreciation, rent) tracked.
+    <t xml:space="preserve">0-2 of the 6 cost components (manpower, material supply, packaging, electricity, depreciation, rent) tracked.
 No periodic review.</t>
   </si>
   <si>
-    <t>3 components tracked.
+    <t xml:space="preserve">3 components tracked.
 Reviewed annually.</t>
   </si>
   <si>
-    <t>4 components tracked.
+    <t xml:space="preserve">4 components tracked.
 Reviewed quarterly.</t>
   </si>
   <si>
-    <t>5 components tracked.
+    <t xml:space="preserve">5 components tracked.
 Reviewed monthly, feeding into cost-per-unit optimization actions.</t>
   </si>
   <si>
@@ -1471,27 +1453,27 @@
     <t>Project Planning &amp; Governance (Charter, Timeline, Cost Control)</t>
   </si>
   <si>
-    <t>No formal project charter, scope definition, or Gantt chart is used for planning/execution.
+    <t xml:space="preserve">No formal project charter, scope definition, or Gantt chart is used for planning/execution.
 Timelines and budgets are not documented.
 Delivery is tracked informally, with over 50% of projects (of any type - warehouse design/expansion, systems rollout, process change, etc.) running behind schedule or over budget with no visibility into the cause.</t>
   </si>
   <si>
-    <t>A basic project charter (scope/objective) is drafted for under 40% of projects.
+    <t xml:space="preserve">A basic project charter (scope/objective) is drafted for under 40% of projects.
 No Gantt chart or formal milestone timeline is maintained.
 Schedule or cost overrun exceeds 30% on the majority of tracked projects.</t>
   </si>
   <si>
-    <t>A project charter (scope, objective, stakeholders, budget) and a Gantt chart with defined milestones are used for 40-70% of projects.
+    <t xml:space="preserve">A project charter (scope, objective, stakeholders, budget) and a Gantt chart with defined milestones are used for 40-70% of projects.
 Milestone/timeline adherence is reviewed periodically (e.g., monthly), but cost tracking against budget is inconsistent.
 Schedule or cost overrun is in the 15-30% band.</t>
   </si>
   <si>
-    <t>A project charter and Gantt chart with milestone-level timelines are mandatory and used for 70-95% of projects.
+    <t xml:space="preserve">A project charter and Gantt chart with milestone-level timelines are mandatory and used for 70-95% of projects.
 Progress and cost are reviewed on a defined cadence (e.g., weekly) against the charter baseline.
 Schedule/cost overrun held under 15%, with variances root-caused.</t>
   </si>
   <si>
-    <t>Over 95% of projects (irrespective of type) are governed by a formal charter and Gantt chart with baselined milestones, tracked in real time against a defined ownership/RACI matrix.
+    <t xml:space="preserve">Over 95% of projects (irrespective of type) are governed by a formal charter and Gantt chart with baselined milestones, tracked in real time against a defined ownership/RACI matrix.
 Over 90% of projects are delivered on time and within the approved budget (schedule/cost overrun under 5%), with lessons-learned closed out post-project.</t>
   </si>
   <si>
@@ -1570,7 +1552,7 @@
     <t>Collection Center Setup &amp; Purpose</t>
   </si>
   <si>
-    <t>0% of inbound FnV volume routed through a collection center.
+    <t xml:space="preserve">0% of inbound FnV volume routed through a collection center.
 All sourcing goes direct to the main warehouse.</t>
   </si>
   <si>
@@ -1583,7 +1565,7 @@
     <t>50-80% of volume via a collection center, with a defined sorting/grading/packing split.</t>
   </si>
   <si>
-    <t>Over 80% of volume via a collection center.
+    <t xml:space="preserve">Over 80% of volume via a collection center.
 A fully optimized first-mile network measurably reducing cost-per-unit quarter-on-quarter.</t>
   </si>
   <si>
@@ -1593,18 +1575,18 @@
     <t>Collection Center Timing &amp; Dispatch Cutoffs</t>
   </si>
   <si>
-    <t>Under 50% of collection-center dispatches meet the 3:00 PM cutoff.
+    <t xml:space="preserve">Under 50% of collection-center dispatches meet the 3:00 PM cutoff.
 Frequent arrivals past 9:00 PM.</t>
   </si>
   <si>
     <t>50-70% adherence to the 3:00 PM dispatch / 9:00 PM arrival cutoffs.</t>
   </si>
   <si>
-    <t>70-85% adherence.
+    <t xml:space="preserve">70-85% adherence.
 Material typically arrives by 8-9 PM, packing completed by 11:30 PM.</t>
   </si>
   <si>
-    <t>85-95% adherence.
+    <t xml:space="preserve">85-95% adherence.
 Arrival consistently by 7-8 PM, enabling processing completion by 12:00 AM and FnV dispatch by 1:00 PM.</t>
   </si>
   <si>
@@ -1617,7 +1599,7 @@
     <t>Collection Center Processing Split</t>
   </si>
   <si>
-    <t>No defined processing split between collection center and warehouse.
+    <t xml:space="preserve">No defined processing split between collection center and warehouse.
 Allocation decided ad hoc daily.</t>
   </si>
   <si>
@@ -1639,18 +1621,18 @@
     <t>Unloading Productivity Norms</t>
   </si>
   <si>
-    <t>Unloading productivity not benchmarked by load type (packed vs bulk).
+    <t xml:space="preserve">Unloading productivity not benchmarked by load type (packed vs bulk).
 No target set.</t>
   </si>
   <si>
-    <t>Productivity tracked in aggregate only, below benchmark (under 400 units/person/hour packed.
+    <t xml:space="preserve">Productivity tracked in aggregate only, below benchmark (under 400 units/person/hour packed.
 Under 4 pallets/person/hour bulk).</t>
   </si>
   <si>
     <t>Productivity at benchmark for one load type only: 500 units/person/hour for packed material, or 5 pallets (125 crates)/person/hour for bulk - not both.</t>
   </si>
   <si>
-    <t>Productivity at benchmark for both load types (500 units/person/hour packed.
+    <t xml:space="preserve">Productivity at benchmark for both load types (500 units/person/hour packed.
 5 pallets or 125 crates/person/hour bulk), tracked daily.</t>
   </si>
   <si>
@@ -1669,32 +1651,32 @@
     <t>Staging &amp; Holding Zone Management</t>
   </si>
   <si>
-    <t>No defined/target SLA for picking and allocation (benchmark: ~600 units/person/hour).
+    <t xml:space="preserve">No defined/target SLA for picking and allocation (benchmark: ~600 units/person/hour).
 No defined physical staging zones, leading to congestion.
 Allocation and holding material share the same physical zone with no clear demarcation.
 No structured stacking/arrangement method for crates.
 No defined dump/reject area within the staging zone.</t>
   </si>
   <si>
-    <t>Picking SLA is tracked for under 30% of shifts against the ~600 units/person/hour benchmark.
+    <t xml:space="preserve">Picking SLA is tracked for under 30% of shifts against the ~600 units/person/hour benchmark.
 Wave Staging, Holding, and Reject/Dump zones are informally identified but frequently overlap.
 Crate stacking in staging has no defined method.
 A dump/reject corner exists but has no clearance routine.</t>
   </si>
   <si>
-    <t>Picking SLA is tracked for 30-60% of shifts.
+    <t xml:space="preserve">Picking SLA is tracked for 30-60% of shifts.
 Wave Staging, Holding, and Reject/Dump zones are marked with reduced but still occasional overlap.
 A dump/reject corner has a clearance routine that is followed inconsistently.
 A maximum days-of-holding (DoH) target for held material is defined but not consistently tracked.</t>
   </si>
   <si>
-    <t>Picking SLA is tracked for 60-90% of shifts and mostly at benchmark.
+    <t xml:space="preserve">Picking SLA is tracked for 60-90% of shifts and mostly at benchmark.
 Wave Staging, Holding, and Reject/Dump zones are distinctly marked with no overlap on 70-95% of days.
 The dump/reject corner follows a timed clearance SOP.
 DoH SLA for holding material is tracked and mostly met.</t>
   </si>
   <si>
-    <t>Picking SLA is tracked for over 90% of shifts and consistently meets/exceeds the ~600 units/person/hour benchmark.
+    <t xml:space="preserve">Picking SLA is tracked for over 90% of shifts and consistently meets/exceeds the ~600 units/person/hour benchmark.
 Wave Staging, Holding, and Reject/Dump zones are distinctly marked with zero overlap.
 The dump/reject corner's timed clearance SOP is followed with zero aged-waste incidents.
 DoH SLA for holding material is met on over 95% of days, reviewed as part of routine floor governance.</t>
@@ -1706,23 +1688,23 @@
     <t>Dispatch &amp; Loading Operations</t>
   </si>
   <si>
-    <t>No defined SLA for dispatch/loading.
+    <t xml:space="preserve">No defined SLA for dispatch/loading.
 System allocation and physical allocation happen independently and out of sync, resulting in inventory mismatches at receiving hubs.</t>
   </si>
   <si>
-    <t>A loading SLA is defined (benchmark: ~2,500 units/person/hour) but tracked for under 30% of dispatches.
+    <t xml:space="preserve">A loading SLA is defined (benchmark: ~2,500 units/person/hour) but tracked for under 30% of dispatches.
 System and physical allocation are reconciled only after the fact, with inventory mismatches at hubs still common.</t>
   </si>
   <si>
-    <t>Loading SLA is tracked for 30-60% of dispatches against the ~2,500 units/person/hour benchmark.
+    <t xml:space="preserve">Loading SLA is tracked for 30-60% of dispatches against the ~2,500 units/person/hour benchmark.
 Scanner-based allocation is used for some dispatches, but system and physical completion are not always simultaneous, leaving residual hub-level mismatches.</t>
   </si>
   <si>
-    <t>Loading SLA is tracked for 60-90% of dispatches and mostly at benchmark.
+    <t xml:space="preserve">Loading SLA is tracked for 60-90% of dispatches and mostly at benchmark.
 Scanner-based allocation with simultaneous system and physical completion is standard for the majority of dispatches, reducing hub-level inventory mismatches to occasional exceptions.</t>
   </si>
   <si>
-    <t>Loading SLA is tracked for over 90% of dispatches and consistently meets/exceeds the ~2,500 units/person/hour benchmark.
+    <t xml:space="preserve">Loading SLA is tracked for over 90% of dispatches and consistently meets/exceeds the ~2,500 units/person/hour benchmark.
 100% of allocations are scanner-based with simultaneous system and physical completion, eliminating hub-level inventory mismatches.
 Evaluated as a standing criterion in every facility diagnostic, not a one-off, site-specific observation.</t>
   </si>
@@ -1892,7 +1874,7 @@
     <t>Standardized</t>
   </si>
   <si>
-    <t>Deploy a digital appointment scheduler with defined slot windows.
+    <t xml:space="preserve">Deploy a digital appointment scheduler with defined slot windows.
  Mark and start enforcing a driver holding area away from the gate.
  Begin manually logging dock-in time.</t>
   </si>
@@ -1900,7 +1882,7 @@
     <t>Managed</t>
   </si>
   <si>
-    <t>Enforce system-generated slot windows with daily adherence tracking.
+    <t xml:space="preserve">Enforce system-generated slot windows with daily adherence tracking.
  Formalize and signpost the holding area.
  Start using dock-in time as the official SLA start-point for GRN TAT.
  Roll out QR/Booking-ID confirmations to the majority of vendors.</t>
@@ -1909,44 +1891,44 @@
     <t>Best-in-class</t>
   </si>
   <si>
-    <t>Automate vendor slot notifications and load-spread balancing across shift hours.
+    <t xml:space="preserve">Automate vendor slot notifications and load-spread balancing across shift hours.
  Give the holding area real-time occupancy visibility.
  Make dock-in time system-captured with automated GRN-TAT breach alerts.
  Push QR/Booking-ID scanning above 90% of vendors with zero manual slot entries.</t>
   </si>
   <si>
-    <t>Introduce a single documentation checklist (vendor, invoice, indent qty) applied before unloading, even generic across vendor/courier.
+    <t xml:space="preserve">Introduce a single documentation checklist (vendor, invoice, indent qty) applied before unloading, even generic across vendor/courier.
  Start logging driver-ID and vehicle-number at the gate.</t>
   </si>
   <si>
-    <t>Split the checklist by vehicle type (vendor vs. courier).
+    <t xml:space="preserve">Split the checklist by vehicle type (vendor vs. courier).
  Check driver-ID/vehicle-number against the slot for a defined share of vehicles.
  Start temperature checks scoped specifically to 4°C SKUs (mushrooms etc.).</t>
   </si>
   <si>
-    <t>Introduce barcode/OCR-assisted matching to raise pre-unload verification coverage.
+    <t xml:space="preserve">Introduce barcode/OCR-assisted matching to raise pre-unload verification coverage.
  Apply the &gt;3°C-deviation temp-reject rule consistently for 4°C SKUs.
  Push driver-ID/vehicle authentication to the majority of vehicles.
  Log 100% of reefer vehicle temperatures.</t>
   </si>
   <si>
-    <t>Fully digitize gate verification end-to-end with an automated exception-flagging audit trail.
+    <t xml:space="preserve">Fully digitize gate verification end-to-end with an automated exception-flagging audit trail.
  Extend driver-ID/vehicle authentication and the temp-reject rule to over 90% of vehicles with zero exceptions.</t>
   </si>
   <si>
-    <t>Start rolling out biometric/facial-recognition coverage at main shift changeovers.
+    <t xml:space="preserve">Start rolling out biometric/facial-recognition coverage at main shift changeovers.
  Begin ad hoc zone-wise entry counts for at least the highest-risk zones (S&amp;G, packing).</t>
   </si>
   <si>
-    <t>Extend facial-recognition coverage to the main changeover shifts.
+    <t xml:space="preserve">Extend facial-recognition coverage to the main changeover shifts.
  Define a warehouse-sizing-based headcount norm per zone and track actuals against it periodically.</t>
   </si>
   <si>
-    <t>Extend biometric coverage to all shifts and gates.
+    <t xml:space="preserve">Extend biometric coverage to all shifts and gates.
  Integrate zone-wise entry capture with the attendance system and reconcile daily against the sizing-based plan.</t>
   </si>
   <si>
-    <t>Push to 100% biometric plus physical-check coverage across all shifts/gates.
+    <t xml:space="preserve">Push to 100% biometric plus physical-check coverage across all shifts/gates.
  Move zone-wise capture to real time with automated variance alerts against the sizing-based headcount plan.</t>
   </si>
   <si>
@@ -1956,88 +1938,88 @@
     <t>Define dock allocation rules by vehicle size and start enforcing FIFO sequencing at the dock.</t>
   </si>
   <si>
-    <t>Move to system-based dock scheduling with size-matched allocation.
+    <t xml:space="preserve">Move to system-based dock scheduling with size-matched allocation.
  Push FIFO adherence above 90% and guarantee green-channel vehicles unload within 15 minutes.</t>
   </si>
   <si>
     <t>Automate dock-vehicle matching with real-time queuing to push utilization above 90%, FIFO adherence to 100%, and green-channel wait time under 10 minutes.</t>
   </si>
   <si>
-    <t>Fit buffers on at least a quarter of docks, prioritizing the highest-traffic ones.
+    <t xml:space="preserve">Fit buffers on at least a quarter of docks, prioritizing the highest-traffic ones.
  Start logging dock-damage incidents (even informally) as they happen.</t>
   </si>
   <si>
-    <t>Expand buffer coverage toward the halfway mark.
+    <t xml:space="preserve">Expand buffer coverage toward the halfway mark.
  Introduce a formal, if basic, penalty (warning/fine) for a driver's repeat dock-damage incident.
  Begin monthly physical dock-structure inspections logged separately from buffer damage.</t>
   </si>
   <si>
-    <t>Push buffer coverage into the 75-95% range.
+    <t xml:space="preserve">Push buffer coverage into the 75-95% range.
  Formalize a graded penalty scale (warning to fine to vendor/transporter review) for repeat offenders.
  Move dock-structure inspection to weekly with defects tracked to closure.</t>
   </si>
   <si>
-    <t>Complete buffer coverage to 100%.
+    <t xml:space="preserve">Complete buffer coverage to 100%.
  Enforce the graded penalty scale strictly to hold repeat-offense rate under 2%.
  Run a preventive maintenance schedule and verify zero unresolved structural damage via weekly inspection.</t>
   </si>
   <si>
-    <t>Define a target unloading SLA (~500 units/person/hour for pre-packed material) and start marking a palletisation zone, even loosely.
+    <t xml:space="preserve">Define a target unloading SLA (~500 units/person/hour for pre-packed material) and start marking a palletisation zone, even loosely.
  Introduce an informal pre-packed bypass flag for known vendors.</t>
   </si>
   <si>
-    <t>Assign dock-wise supervisor-led unloading teams.
+    <t xml:space="preserve">Assign dock-wise supervisor-led unloading teams.
  Enforce the crate-stacking SOP and keep the palletisation/S&amp;G zones marked.
  Relocate waste disposal away from the inbound gate.
  Extend the bypass flag to 30-60% of eligible pre-packed loads.</t>
   </si>
   <si>
-    <t>Push supervisor-led teams to every shift.
+    <t xml:space="preserve">Push supervisor-led teams to every shift.
  Mark FIFO lanes for S&amp;G and a separate dry-category lane.
  Raise crate-stacking SOP compliance and bypass-flag usage into the 60-90% range.</t>
   </si>
   <si>
-    <t>Drive unloading SLA, crate-stacking, and bypass-flag compliance above 90% with zero space-constraint or cross-flow incidents.
+    <t xml:space="preserve">Drive unloading SLA, crate-stacking, and bypass-flag compliance above 90% with zero space-constraint or cross-flow incidents.
  Fully integrate the bypass flag into the load-declaration/GRN step.</t>
   </si>
   <si>
-    <t>Start piloting digital weighment integration with the WMS/GRN system on a subset of lanes.
+    <t xml:space="preserve">Start piloting digital weighment integration with the WMS/GRN system on a subset of lanes.
  Establish a minimum 1.5m clear aisle between weighment and staging.
  Put scale calibration on a defined (even if not daily) schedule.</t>
   </si>
   <si>
-    <t>Extend digital weighment integration to 30-60% of transactions.
+    <t xml:space="preserve">Extend digital weighment integration to 30-60% of transactions.
  Begin shifting weighment to the unloading stage (ahead of S&amp;G) for some vendor categories to cut PO-closure delay.</t>
   </si>
   <si>
-    <t>Push digital weighment coverage to 60-90%.
+    <t xml:space="preserve">Push digital weighment coverage to 60-90%.
  Make weighment-at-unloading-stage the default for the majority of vendors.
  Move scale recalibration to daily with tare memory per packaging type.
  Retain digital weight logs as an audit trail.</t>
   </si>
   <si>
-    <t>Complete digital weighment integration above 90% with zero manual entry.
+    <t xml:space="preserve">Complete digital weighment integration above 90% with zero manual entry.
  Make same-day PO closure the norm.
  Use the digital weight log routinely for supplier invoice reconciliation and shrinkage analysis.</t>
   </si>
   <si>
-    <t>Introduce an informal capacity check (even a phone call to the dock supervisor) before releasing any vehicle.
+    <t xml:space="preserve">Introduce an informal capacity check (even a phone call to the dock supervisor) before releasing any vehicle.
  Designate (even if unenforced) a waiting/parking zone for held vehicles.
  Start issuing an exit slip on gate-out.</t>
   </si>
   <si>
-    <t>Define a formal capacity check with a stated time window (e.g., 15 minutes for dock bay plus staging space) and route 'no' decisions to the holding area.
+    <t xml:space="preserve">Define a formal capacity check with a stated time window (e.g., 15 minutes for dock bay plus staging space) and route 'no' decisions to the holding area.
  Introduce a basic reject-vs-hold rule.
  Make exit-slip issuance standard.</t>
   </si>
   <si>
-    <t>Extend capacity-gated release to the majority of gate-ins.
+    <t xml:space="preserve">Extend capacity-gated release to the majority of gate-ins.
  Formalize the full reject/temp-reject/hold/bypass decision taxonomy.
  Add outbound-seal verification to gate-out.
  Install physical enablers (multi-lane entry, boom barrier, CCTV/tablet).</t>
   </si>
   <si>
-    <t>Push capacity-gated release above 90% in real time, tied live to the dock-management and staging systems.
+    <t xml:space="preserve">Push capacity-gated release above 90% in real time, tied live to the dock-management and staging systems.
  Apply the full decision taxonomy with a complete audit trail.
  Make gate-out fully controlled (exit slip plus seal verification on 100% of dispatches).
  Add a weighbridge where applicable.</t>
@@ -2091,21 +2073,21 @@
     <t>Complete all 9 elements, version-control them, and link them to a closed-loop CAPA process with under 5-day average closure time.</t>
   </si>
   <si>
-    <t>Define a sampling percentage and a written AQR format, even if not yet consistently applied.
+    <t xml:space="preserve">Define a sampling percentage and a written AQR format, even if not yet consistently applied.
  Require quality-team sign-off before GRN posting (even if it currently happens late).</t>
   </si>
   <si>
-    <t>Fix sampling at ~10% with a 20% defect-rejection threshold.
+    <t xml:space="preserve">Fix sampling at ~10% with a 20% defect-rejection threshold.
  Make GRN approval procedurally dependent on quality clearance (even if still manual/paper-based).
  Apply the AQR before unloading for the majority of lots.</t>
   </si>
   <si>
-    <t>Segment sampling/rejection by category (FnV vs. dry) with batch/expiry and shelf-life checks.
+    <t xml:space="preserve">Segment sampling/rejection by category (FnV vs. dry) with batch/expiry and shelf-life checks.
  Make GRN posting a hard system hold pending quality clearance.
  Start tracking QC/vehicle rejection by vendor and SKU into a periodic supplier scorecard.</t>
   </si>
   <si>
-    <t>Digitize sampling/rejection norms per SKU category with under 2% inspection error.
+    <t xml:space="preserve">Digitize sampling/rejection norms per SKU category with under 2% inspection error.
  Make GRN release fully system-enforced with zero exceptions and a full sign-off audit trail.
  Run the AQR and supplier scorecard in real time, feeding vendor reviews.</t>
   </si>
@@ -2128,7 +2110,7 @@
     <t>Categorize complaints monthly and benchmark PPM against the industry band.</t>
   </si>
   <si>
-    <t>Add root-cause analysis with a 7-day corrective-action closure target.
+    <t xml:space="preserve">Add root-cause analysis with a 7-day corrective-action closure target.
  Track PPM weekly against a defined benchmark.</t>
   </si>
   <si>
@@ -2162,30 +2144,30 @@
     <t>Run a 5S pilot in one area and start basic floor demarcation there (aisles, storage) to lift the audit score above 40%.</t>
   </si>
   <si>
-    <t>Extend Sort/Set/Shine facility-wide with quarterly audits.
+    <t xml:space="preserve">Extend Sort/Set/Shine facility-wide with quarterly audits.
  Expand demarcation to include S&amp;G/packing space and storage marking.</t>
   </si>
   <si>
-    <t>Standardize 5S across all zones with monthly audits and biannual training.
+    <t xml:space="preserve">Standardize 5S across all zones with monthly audits and biannual training.
  Extend demarcation to buffer-pallet staging and packaging-material storage.</t>
   </si>
   <si>
-    <t>Sustain 5S with daily checks and a documented Kaizen count.
+    <t xml:space="preserve">Sustain 5S with daily checks and a documented Kaizen count.
  Complete 100% zone demarcation (including tools/machinery) with colour-coding, auditing demarcation adherence as part of the daily check.</t>
   </si>
   <si>
     <t>Deploy a second lean principle (e.g., start value-stream mapping) and introduce PDCA on at least a few processes.</t>
   </si>
   <si>
-    <t>Deploy a third principle and embed PDCA in 20-50% of processes.
+    <t xml:space="preserve">Deploy a third principle and embed PDCA in 20-50% of processes.
  Start tracking 2-3 of the 8 waste types.</t>
   </si>
   <si>
-    <t>Add pull/JIT replenishment as a fourth principle.
+    <t xml:space="preserve">Add pull/JIT replenishment as a fourth principle.
  Push PDCA to 50-80% of processes and track 5-6 waste types with quarterly reduction targets.</t>
   </si>
   <si>
-    <t>Fully embed all 5 lean principles with PDCA in over 80% of processes.
+    <t xml:space="preserve">Fully embed all 5 lean principles with PDCA in over 80% of processes.
  Track all 8 waste types with measurable year-on-year reduction above 10%.</t>
   </si>
   <si>
@@ -2204,11 +2186,11 @@
     <t>Define size/quality standards and a throughput SLA (~70 units/person/hour) for the first 30% of SKUs/stations, even if compliance is uneven.</t>
   </si>
   <si>
-    <t>Extend standards and throughput-SLA tracking to 30-60% of SKUs/stations.
+    <t xml:space="preserve">Extend standards and throughput-SLA tracking to 30-60% of SKUs/stations.
  Start assigning experienced manpower to piece-category SKUs, even if inconsistently.</t>
   </si>
   <si>
-    <t>Extend to 60-90% of SKUs/stations with monthly grading-accuracy audits above 90%.
+    <t xml:space="preserve">Extend to 60-90% of SKUs/stations with monthly grading-accuracy audits above 90%.
  Make experienced-manpower assignment for piece-category SKUs consistent.</t>
   </si>
   <si>
@@ -2218,41 +2200,41 @@
     <t>Define packaging material by SKU for the first half of SKUs and start tracking a shift-level SLA on a subset of lines.</t>
   </si>
   <si>
-    <t>Define packaging material for all SKUs.
+    <t xml:space="preserve">Define packaging material for all SKUs.
  Introduce a formed-box staging shelf and begin aligning some vendors to FC pack standards to remove re-packing.</t>
   </si>
   <si>
-    <t>Push productivity toward the 100-120 units/person/hour band with daily gang-output tracking.
+    <t xml:space="preserve">Push productivity toward the 100-120 units/person/hour band with daily gang-output tracking.
  Extend FC-standard vendor alignment and dedicated chilled packing to 60-90% of applicable lines/shifts.</t>
   </si>
   <si>
-    <t>Sustain productivity above 120 units/person/hour.
+    <t xml:space="preserve">Sustain productivity above 120 units/person/hour.
  Eliminate the re-pack sub-process for over 90% of applicable vendors and route 100% of chilled SKUs through a dedicated chilled station, tracked and improved monthly.</t>
   </si>
   <si>
     <t>Set the 4-person-per-table norm and start applying an S&amp;G-to-packing table ratio, even if compliance is under 40%.</t>
   </si>
   <si>
-    <t>Push table-norm and ratio compliance into the 40-70% range.
+    <t xml:space="preserve">Push table-norm and ratio compliance into the 40-70% range.
  Begin an inter-vendor cleaning step, even if inconsistent.</t>
   </si>
   <si>
-    <t>Monitor table norm and ratio adherence via regular floor walks to reach 70-95%.
+    <t xml:space="preserve">Monitor table norm and ratio adherence via regular floor walks to reach 70-95%.
  Make inter-vendor cleaning standard practice.</t>
   </si>
   <si>
-    <t>Maintain over 95% adherence with real-time floor supervision.
+    <t xml:space="preserve">Maintain over 95% adherence with real-time floor supervision.
  Enforce inter-vendor cleaning with zero cross-contamination incidents.</t>
   </si>
   <si>
     <t>Start tracking shrinkage in aggregate (even without category splits) to establish a baseline against the 5% ceiling.</t>
   </si>
   <si>
-    <t>Split shrinkage tracking by SKU category against benchmark ranges.
+    <t xml:space="preserve">Split shrinkage tracking by SKU category against benchmark ranges.
  Start tracking seasonal RTV loss by season.</t>
   </si>
   <si>
-    <t>Push category-level shrinkage within benchmark for over 80% of categories.
+    <t xml:space="preserve">Push category-level shrinkage within benchmark for over 80% of categories.
  Review the seasonal-loss trend monthly with corrective action for outliers.</t>
   </si>
   <si>
@@ -2286,16 +2268,16 @@
     <t>Add a second forecasting layer (e.g., seasonal on top of baseline) to lift forecast accuracy above 60%.</t>
   </si>
   <si>
-    <t>Add a third layer (event-based) and start tracking time-of-day demand curves for at least half of SKUs/stores.
+    <t xml:space="preserve">Add a third layer (event-based) and start tracking time-of-day demand curves for at least half of SKUs/stores.
  Give new stores a defined generic ramp-up curve instead of guesswork.</t>
   </si>
   <si>
-    <t>Add the fourth layer (typically time-of-day or hyperlocal) and extend it to 70-90% of stores.
+    <t xml:space="preserve">Add the fourth layer (typically time-of-day or hyperlocal) and extend it to 70-90% of stores.
  Root-cause SKU-level forecast error monthly.
  Bridge new-store gaps with a comparable-store proxy model.</t>
   </si>
   <si>
-    <t>Activate and continuously calibrate all 5 layers against actuals.
+    <t xml:space="preserve">Activate and continuously calibrate all 5 layers against actuals.
  Automate recalibration for hourly volatility and SKU-level accuracy.
  Cut the new-store proxy-to-actual transition to 2-4 weeks.</t>
   </si>
@@ -2312,21 +2294,21 @@
     <t>Automate all 5 components with weekly review and real-time, system-enforced batch/expiry visibility to hold incidents under 2% of SKUs monthly.</t>
   </si>
   <si>
-    <t>Define the replenishment formula (Forecast Demand + Safety Stock - Current Inventory) and run it at least once a day.
+    <t xml:space="preserve">Define the replenishment formula (Forecast Demand + Safety Stock - Current Inventory) and run it at least once a day.
  Introduce a basic reorder-point trigger for a subset of SKUs.</t>
   </si>
   <si>
-    <t>Run replenishment daily on the standard formula.
+    <t xml:space="preserve">Run replenishment daily on the standard formula.
  Extend the reorder-point trigger to 30-60% of SKUs with a manually-invoked emergency top-up process.
  Start tracking DoI by category.</t>
   </si>
   <si>
-    <t>Move to twice-daily replenishment with a defined wave split and lead-time/buffer-capacity factored in.
+    <t xml:space="preserve">Move to twice-daily replenishment with a defined wave split and lead-time/buffer-capacity factored in.
  Extend reorder-point coverage to 60-90% of SKUs with an SLA-bound emergency top-up.
  Track DoI by SKU against a target band.</t>
   </si>
   <si>
-    <t>Fully automate the twice-daily-plus cycle with an optimized wave split and lead-time-adjusted safety stock.
+    <t xml:space="preserve">Fully automate the twice-daily-plus cycle with an optimized wave split and lead-time-adjusted safety stock.
  Extend reorder-point/ARS coverage above 90%.
  Eliminate replenishment-receipt dock congestion and storage overflow via slotted receiving.</t>
   </si>
@@ -2334,33 +2316,33 @@
     <t>Extend defined manpower planning to a third role and start tracking (even without acting on) attrition.</t>
   </si>
   <si>
-    <t>Cover a fourth role.
+    <t xml:space="preserve">Cover a fourth role.
  Introduce a surge-planning trigger and a gig-flex ratio for at least some shifts, even if reactive.</t>
   </si>
   <si>
-    <t>Cover a fifth role with shift-level granularity.
+    <t xml:space="preserve">Cover a fifth role with shift-level granularity.
  Build shift design around the full diurnal demand curve and put an active attrition/gig-supply mitigation plan in place.</t>
   </si>
   <si>
-    <t>Cover all 6 roles with daily granularity and pre-built capacity buffers.
+    <t xml:space="preserve">Cover all 6 roles with daily granularity and pre-built capacity buffers.
  Make surge planning and gig-flex proactive on over 90% of shifts, with attrition and gig-supply risk mitigated via a pre-qualified backup pool.</t>
   </si>
   <si>
-    <t>Move to at least 1 planned warehouse-to-dark-store cycle per day (from ad hoc dispatch).
+    <t xml:space="preserve">Move to at least 1 planned warehouse-to-dark-store cycle per day (from ad hoc dispatch).
  Start applying route/truck-load optimization to at least some routes.</t>
   </si>
   <si>
-    <t>Run 1-2 cycles per day with a defined (e.g., 70/30) wave split.
+    <t xml:space="preserve">Run 1-2 cycles per day with a defined (e.g., 70/30) wave split.
  Extend route/truck-load optimization to 30-60% of routes.
  Check freezer/cold-chain capacity before dispatch for temperature-sensitive SKUs.</t>
   </si>
   <si>
-    <t>Push to 2 cycles per day with 70-90% wave-split adherence.
+    <t xml:space="preserve">Push to 2 cycles per day with 70-90% wave-split adherence.
  Extend route optimization to 60-90% of routes.
  Give pre-live dark stores a defined, separate inward SOP.</t>
   </si>
   <si>
-    <t>Run 2+ cycles per day with wave-split adherence above 90%, dynamically adjusted to dark-store stock in real time.
+    <t xml:space="preserve">Run 2+ cycles per day with wave-split adherence above 90%, dynamically adjusted to dark-store stock in real time.
  Extend route optimization above 90% with OPH at/above target.
  Plan freezer capacity dynamically with zero breaches.</t>
   </si>
@@ -2383,11 +2365,11 @@
     <t>Track 2-3 dimensions by vendor on a periodic (e.g., quarterly) cadence, even without linking to sourcing decisions yet.</t>
   </si>
   <si>
-    <t>Track all four dimensions by vendor monthly, feeding a basic scorecard.
+    <t xml:space="preserve">Track all four dimensions by vendor monthly, feeding a basic scorecard.
  Start adjusting sourcing allocation for chronic underperformers and defining contracting/hedging for key SKUs.</t>
   </si>
   <si>
-    <t>Move to real-time, vendor-and-SKU-level tracking via an automated scorecard driving sourcing/tiering decisions.
+    <t xml:space="preserve">Move to real-time, vendor-and-SKU-level tracking via an automated scorecard driving sourcing/tiering decisions.
  Hold OTIF above 95% and hedge/contract price volatility for the majority of high-value categories.</t>
   </si>
   <si>
@@ -2538,15 +2520,15 @@
     <t>Introduce a basic project charter (scope/objective) for the next project, even without a Gantt chart yet.</t>
   </si>
   <si>
-    <t>Add a Gantt chart with milestones and a defined budget to the charter.
+    <t xml:space="preserve">Add a Gantt chart with milestones and a defined budget to the charter.
  Review milestone/timeline adherence monthly.</t>
   </si>
   <si>
-    <t>Make the charter and Gantt chart mandatory for all projects.
+    <t xml:space="preserve">Make the charter and Gantt chart mandatory for all projects.
  Review progress and cost weekly against the baseline, root-causing variances.</t>
   </si>
   <si>
-    <t>Track projects in real time against a defined ownership/RACI matrix.
+    <t xml:space="preserve">Track projects in real time against a defined ownership/RACI matrix.
  Close out lessons-learned post-project to sustain over 90% on-time, in-budget delivery.</t>
   </si>
   <si>
@@ -2631,15 +2613,15 @@
     <t>Mark rough Wave Staging, Holding, and Reject/Dump zones (even with overlap) and start tracking picking SLA against the 600 units/person/hour benchmark for at least some shifts.</t>
   </si>
   <si>
-    <t>Reduce zone overlap and introduce a (even inconsistent) clearance routine for the dump/reject corner.
+    <t xml:space="preserve">Reduce zone overlap and introduce a (even inconsistent) clearance routine for the dump/reject corner.
  Define a maximum DoH target for held material.</t>
   </si>
   <si>
-    <t>Eliminate zone overlap on 70-95% of days with a timed clearance SOP for the dump/reject corner.
+    <t xml:space="preserve">Eliminate zone overlap on 70-95% of days with a timed clearance SOP for the dump/reject corner.
  Track and mostly meet the DoH SLA.</t>
   </si>
   <si>
-    <t>Sustain zero zone overlap and a fully followed clearance SOP with zero aged-waste incidents.
+    <t xml:space="preserve">Sustain zero zone overlap and a fully followed clearance SOP with zero aged-waste incidents.
  Meet the DoH SLA on over 95% of days as part of routine floor governance.</t>
   </si>
   <si>
@@ -2734,38 +2716,53 @@
   </si>
   <si>
     <t>Move to real-time tracking across the pack-to-dispatch-to-handover chain to sustain it above 98%.</t>
+  </si>
+  <si>
+    <t>review_status</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Needs review</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color theme="1"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -2791,117 +2788,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3091,343 +3016,342 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.6328125" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="5" customWidth="1"/>
-    <col min="2" max="2" width="30" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8" style="5" customWidth="1"/>
-    <col min="4" max="4" width="30" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10" style="5" customWidth="1"/>
-    <col min="7" max="7" width="32" style="5" customWidth="1"/>
-    <col min="8" max="8" width="14" style="8" customWidth="1"/>
-    <col min="9" max="13" width="42" style="5" customWidth="1"/>
-    <col min="14" max="14" width="9" style="5" customWidth="1"/>
-    <col min="15" max="15" width="10" style="5" customWidth="1"/>
-    <col min="16" max="18" width="8.6328125" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="8.6328125" style="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="2" customWidth="1"/>
+    <col min="9" max="13" width="42" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.6328125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f t="shared" ref="E2:E33" si="0">1/8</f>
         <v>0.125</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H2" s="7">
         <f t="shared" ref="H2:H12" si="1">1/11</f>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="I2" s="10" t="s">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="6">
         <v>1</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H3" s="7">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="I3" s="10" t="s">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="6">
         <v>1</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="100" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H4" s="7">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="I4" s="10" t="s">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="6">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="I5" s="10" t="s">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="6">
         <v>1</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="87.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="7">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="I6" s="10" t="s">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="6">
         <v>1</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="7" ht="217.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>57</v>
@@ -3444,39 +3368,39 @@
       <c r="M7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="1">
         <v>1</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="145" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="8" ht="145" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>64</v>
@@ -3493,39 +3417,39 @@
       <c r="M8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="1">
         <v>1</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="174" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
+    <row r="9" ht="174" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>71</v>
@@ -3542,39 +3466,39 @@
       <c r="M9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="1">
         <v>1</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5" t="s">
+    <row r="10" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>78</v>
@@ -3591,39 +3515,39 @@
       <c r="M10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="1">
         <v>1</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="11" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>85</v>
@@ -3640,39 +3564,39 @@
       <c r="M11" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="1">
         <v>1</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="12" ht="72.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="2">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>92</v>
@@ -3689,233 +3613,233 @@
       <c r="M12" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="1">
         <v>1</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="4" t="s">
+    <row r="13" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" ref="H13:H18" si="2">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="6">
         <v>1</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="162.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    <row r="14" ht="162.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H14" s="7">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="6">
         <v>1</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4" t="s">
+    <row r="15" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>114</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="M15" s="10" t="s">
+      <c r="M15" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="N15" s="4">
+      <c r="N15" s="6">
         <v>1</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="16" ht="87.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="6">
         <v>1</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="s">
+    <row r="17" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="2">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
@@ -3934,37 +3858,37 @@
       <c r="M17" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="1">
         <v>1</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="O17" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="s">
+    <row r="18" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="2">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
@@ -3983,429 +3907,429 @@
       <c r="M18" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="1">
         <v>1</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="O18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
+    <row r="19" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>144</v>
       </c>
       <c r="H19" s="7">
         <f>1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I19" s="10" t="s">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="L19" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="N19" s="4">
+      <c r="N19" s="6">
         <v>1</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="4" t="s">
+    <row r="20" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>151</v>
       </c>
       <c r="H20" s="7">
         <f>1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I20" s="10" t="s">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="M20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="6">
         <v>1</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="21" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>158</v>
       </c>
       <c r="H21" s="7">
         <f>1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I21" s="10" t="s">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="L21" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="M21" s="10" t="s">
+      <c r="M21" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="6">
         <v>1</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="4" t="s">
+    <row r="22" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>167</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" ref="H22:H27" si="3">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="L22" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="M22" s="10" t="s">
+      <c r="M22" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="N22" s="4">
+      <c r="N22" s="6">
         <v>1</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="4" t="s">
+    <row r="23" ht="137.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>174</v>
       </c>
       <c r="H23" s="7">
         <f t="shared" si="3"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="L23" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="M23" s="10" t="s">
+      <c r="M23" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="6">
         <v>1</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="s">
+    <row r="24" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>181</v>
       </c>
       <c r="H24" s="7">
         <f t="shared" si="3"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="M24" s="10" t="s">
+      <c r="M24" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="N24" s="4">
+      <c r="N24" s="6">
         <v>1</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O24" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="4" t="s">
+    <row r="25" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>188</v>
       </c>
       <c r="H25" s="7">
         <f t="shared" si="3"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="L25" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="M25" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="6">
         <v>1</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="4" t="s">
+    <row r="26" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>195</v>
       </c>
       <c r="H26" s="7">
         <f t="shared" si="3"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="L26" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="M26" s="10" t="s">
+      <c r="M26" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="6">
         <v>1</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="5" t="s">
+    <row r="27" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="1">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="2">
         <f t="shared" si="3"/>
         <v>0.16666666666666666</v>
       </c>
@@ -4424,333 +4348,333 @@
       <c r="M27" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="1">
         <v>1</v>
       </c>
-      <c r="O27" s="5" t="s">
+      <c r="O27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="4" t="s">
+    <row r="28" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>211</v>
       </c>
       <c r="H28" s="7">
         <f t="shared" ref="H28:H44" si="4">1/17</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I28" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="L28" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="M28" s="10" t="s">
+      <c r="M28" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="6">
         <v>1</v>
       </c>
-      <c r="O28" s="4" t="s">
+      <c r="O28" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="4" t="s">
+    <row r="29" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>218</v>
       </c>
       <c r="H29" s="7">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I29" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="L29" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M29" s="10" t="s">
+      <c r="M29" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="N29" s="4">
+      <c r="N29" s="6">
         <v>1</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="O29" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="4" t="s">
+    <row r="30" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>225</v>
       </c>
       <c r="H30" s="7">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I30" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="L30" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="M30" s="10" t="s">
+      <c r="M30" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="N30" s="4">
+      <c r="N30" s="6">
         <v>1</v>
       </c>
-      <c r="O30" s="4" t="s">
+      <c r="O30" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="4" t="s">
+    <row r="31" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>232</v>
       </c>
       <c r="H31" s="7">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I31" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="M31" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="6">
         <v>1</v>
       </c>
-      <c r="O31" s="4" t="s">
+      <c r="O31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="4" t="s">
+    <row r="32" ht="100" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>239</v>
       </c>
       <c r="H32" s="7">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I32" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="L32" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="M32" s="10" t="s">
+      <c r="M32" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="N32" s="4">
+      <c r="N32" s="6">
         <v>1</v>
       </c>
-      <c r="O32" s="4" t="s">
+      <c r="O32" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="4" t="s">
+    <row r="33" ht="137.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="7">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>246</v>
       </c>
       <c r="H33" s="7">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="I33" s="10" t="s">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="L33" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="M33" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="N33" s="4">
+      <c r="N33" s="6">
         <v>1</v>
       </c>
-      <c r="O33" s="4" t="s">
+      <c r="O33" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="5" t="s">
+    <row r="34" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="1">
         <f t="shared" ref="E34:E64" si="5">1/8</f>
         <v>0.125</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>254</v>
@@ -4767,39 +4691,39 @@
       <c r="M34" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="N34" s="5">
+      <c r="N34" s="1">
         <v>1</v>
       </c>
-      <c r="O34" s="5" t="s">
+      <c r="O34" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="5" t="s">
+    <row r="35" ht="130.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>261</v>
@@ -4816,39 +4740,39 @@
       <c r="M35" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="O35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="5" t="s">
+    <row r="36" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>268</v>
@@ -4865,39 +4789,39 @@
       <c r="M36" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="N36" s="5">
+      <c r="N36" s="1">
         <v>1</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="5" t="s">
+    <row r="37" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>275</v>
@@ -4914,39 +4838,39 @@
       <c r="M37" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="N37" s="5">
+      <c r="N37" s="1">
         <v>1</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="O37" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="5" t="s">
+    <row r="38" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>282</v>
@@ -4963,39 +4887,39 @@
       <c r="M38" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="N38" s="5">
+      <c r="N38" s="1">
         <v>1</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="O38" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="5" t="s">
+    <row r="39" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>289</v>
@@ -5012,39 +4936,39 @@
       <c r="M39" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="N39" s="5">
+      <c r="N39" s="1">
         <v>1</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="O39" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="5" t="s">
+    <row r="40" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>296</v>
@@ -5061,39 +4985,39 @@
       <c r="M40" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="N40" s="5">
+      <c r="N40" s="1">
         <v>1</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="O40" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="5" t="s">
+    <row r="41" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>303</v>
@@ -5110,39 +5034,39 @@
       <c r="M41" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="N41" s="5">
+      <c r="N41" s="1">
         <v>1</v>
       </c>
-      <c r="O41" s="5" t="s">
+      <c r="O41" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="5" t="s">
+    <row r="42" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>310</v>
@@ -5159,39 +5083,39 @@
       <c r="M42" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="1">
         <v>1</v>
       </c>
-      <c r="O42" s="5" t="s">
+      <c r="O42" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="5" t="s">
+    <row r="43" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>317</v>
@@ -5208,39 +5132,39 @@
       <c r="M43" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="1">
         <v>1</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="O43" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="5" t="s">
+    <row r="44" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="2">
         <f t="shared" si="4"/>
-        <v>5.8823529411764705E-2</v>
+        <v>0.058823529411764705</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>324</v>
@@ -5257,184 +5181,184 @@
       <c r="M44" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="N44" s="5">
+      <c r="N44" s="1">
         <v>1</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="O44" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="4" t="s">
+    <row r="45" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>332</v>
       </c>
       <c r="H45" s="7">
         <f t="shared" ref="H45:H51" si="6">1/7</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="M45" s="10" t="s">
+      <c r="M45" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="N45" s="4">
+      <c r="N45" s="6">
         <v>1</v>
       </c>
-      <c r="O45" s="4" t="s">
+      <c r="O45" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="4" t="s">
+    <row r="46" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>339</v>
       </c>
       <c r="H46" s="7">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="I46" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="K46" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="L46" s="10" t="s">
+      <c r="L46" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="M46" s="10" t="s">
+      <c r="M46" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="6">
         <v>1</v>
       </c>
-      <c r="O46" s="4" t="s">
+      <c r="O46" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="4" t="s">
+    <row r="47" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>346</v>
       </c>
       <c r="H47" s="7">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="M47" s="10" t="s">
+      <c r="M47" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="N47" s="4">
+      <c r="N47" s="6">
         <v>1</v>
       </c>
-      <c r="O47" s="4" t="s">
+      <c r="O47" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="5" t="s">
+    <row r="48" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="2">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
@@ -5453,37 +5377,37 @@
       <c r="M48" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="N48" s="5">
+      <c r="N48" s="1">
         <v>1</v>
       </c>
-      <c r="O48" s="5" t="s">
+      <c r="O48" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="116" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="5" t="s">
+    <row r="49" ht="116" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="2">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
@@ -5502,37 +5426,37 @@
       <c r="M49" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="N49" s="5">
+      <c r="N49" s="1">
         <v>1</v>
       </c>
-      <c r="O49" s="5" t="s">
+      <c r="O49" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="5" t="s">
+    <row r="50" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="2">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
@@ -5551,37 +5475,37 @@
       <c r="M50" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="N50" s="5">
+      <c r="N50" s="1">
         <v>1</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="O50" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" s="5" t="s">
+    <row r="51" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="2">
         <f t="shared" si="6"/>
         <v>0.14285714285714285</v>
       </c>
@@ -5600,233 +5524,233 @@
       <c r="M51" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="1">
         <v>1</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="O51" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="4" t="s">
+    <row r="52" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>383</v>
       </c>
       <c r="H52" s="7">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="I52" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="J52" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="K52" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="L52" s="10" t="s">
+      <c r="L52" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="M52" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="N52" s="4">
+      <c r="N52" s="6">
         <v>1</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="O52" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="4" t="s">
+    <row r="53" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>390</v>
       </c>
       <c r="H53" s="7">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="J53" s="10" t="s">
+      <c r="J53" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="L53" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="M53" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="N53" s="4">
+      <c r="N53" s="6">
         <v>1</v>
       </c>
-      <c r="O53" s="4" t="s">
+      <c r="O53" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="4" t="s">
+    <row r="54" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>397</v>
       </c>
       <c r="H54" s="7">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="J54" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="K54" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="L54" s="10" t="s">
+      <c r="L54" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="N54" s="4">
+      <c r="N54" s="6">
         <v>1</v>
       </c>
-      <c r="O54" s="4" t="s">
+      <c r="O54" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="4" t="s">
+    <row r="55" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="7">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>404</v>
       </c>
       <c r="H55" s="7">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="J55" s="10" t="s">
+      <c r="J55" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="L55" s="10" t="s">
+      <c r="L55" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="N55" s="4">
+      <c r="N55" s="6">
         <v>1</v>
       </c>
-      <c r="O55" s="4" t="s">
+      <c r="O55" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" s="5" t="s">
+    <row r="56" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="2">
         <f t="shared" ref="H56:H64" si="7">1/9</f>
         <v>0.1111111111111111</v>
       </c>
@@ -5845,37 +5769,37 @@
       <c r="M56" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="N56" s="5">
+      <c r="N56" s="1">
         <v>1</v>
       </c>
-      <c r="O56" s="5" t="s">
+      <c r="O56" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" s="5" t="s">
+    <row r="57" ht="130.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -5894,37 +5818,37 @@
       <c r="M57" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="N57" s="5">
+      <c r="N57" s="1">
         <v>1</v>
       </c>
-      <c r="O57" s="5" t="s">
+      <c r="O57" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="116" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="5" t="s">
+    <row r="58" ht="116" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -5943,37 +5867,37 @@
       <c r="M58" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="N58" s="5">
+      <c r="N58" s="1">
         <v>1</v>
       </c>
-      <c r="O58" s="5" t="s">
+      <c r="O58" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="5" t="s">
+    <row r="59" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -5992,37 +5916,37 @@
       <c r="M59" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="N59" s="5">
+      <c r="N59" s="1">
         <v>1</v>
       </c>
-      <c r="O59" s="5" t="s">
+      <c r="O59" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="5" t="s">
+    <row r="60" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -6041,37 +5965,37 @@
       <c r="M60" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="N60" s="5">
+      <c r="N60" s="1">
         <v>1</v>
       </c>
-      <c r="O60" s="5" t="s">
+      <c r="O60" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="5" t="s">
+    <row r="61" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -6090,37 +6014,37 @@
       <c r="M61" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="N61" s="5">
+      <c r="N61" s="1">
         <v>1</v>
       </c>
-      <c r="O61" s="5" t="s">
+      <c r="O61" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" s="5" t="s">
+    <row r="62" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -6139,37 +6063,37 @@
       <c r="M62" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="N62" s="5">
+      <c r="N62" s="1">
         <v>1</v>
       </c>
-      <c r="O62" s="5" t="s">
+      <c r="O62" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" s="5" t="s">
+    <row r="63" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H63" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -6188,37 +6112,37 @@
       <c r="M63" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="N63" s="5">
+      <c r="N63" s="1">
         <v>1</v>
       </c>
-      <c r="O63" s="5" t="s">
+      <c r="O63" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" s="5" t="s">
+    <row r="64" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="1">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="2">
         <f t="shared" si="7"/>
         <v>0.1111111111111111</v>
       </c>
@@ -6237,24 +6161,24 @@
       <c r="M64" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="N64" s="5">
+      <c r="N64" s="1">
         <v>1</v>
       </c>
-      <c r="O64" s="5" t="s">
+      <c r="O64" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" ht="29" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="29" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F253"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6264,7 +6188,7 @@
     <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6284,7 +6208,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -6304,7 +6228,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6324,7 +6248,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -6344,7 +6268,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -6364,7 +6288,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -6384,7 +6308,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -6404,7 +6328,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -6424,7 +6348,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -6444,7 +6368,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -6464,7 +6388,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -6484,7 +6408,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6504,7 +6428,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -6524,7 +6448,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -6544,7 +6468,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -6564,7 +6488,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6584,7 +6508,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -6604,7 +6528,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -6624,7 +6548,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -6644,7 +6568,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -6664,7 +6588,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -6684,7 +6608,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -6704,7 +6628,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -6724,7 +6648,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -6744,7 +6668,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -6764,7 +6688,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -6784,7 +6708,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -6804,7 +6728,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -6824,7 +6748,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -6844,7 +6768,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -6864,7 +6788,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -6884,7 +6808,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -6904,7 +6828,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="72.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -6924,7 +6848,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -6944,7 +6868,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -6964,7 +6888,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -6984,7 +6908,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -7004,7 +6928,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -7024,7 +6948,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -7044,7 +6968,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -7064,7 +6988,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -7084,7 +7008,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -7104,7 +7028,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -7124,7 +7048,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -7144,7 +7068,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -7164,7 +7088,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -7184,7 +7108,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -7204,7 +7128,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -7224,7 +7148,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -7244,7 +7168,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -7264,7 +7188,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -7284,7 +7208,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -7304,7 +7228,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -7324,7 +7248,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -7344,7 +7268,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -7364,7 +7288,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -7384,7 +7308,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -7404,7 +7328,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -7424,7 +7348,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -7444,7 +7368,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -7464,7 +7388,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -7484,7 +7408,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -7504,7 +7428,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -7524,7 +7448,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -7544,7 +7468,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -7564,7 +7488,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -7584,7 +7508,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -7604,7 +7528,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -7624,7 +7548,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -7644,7 +7568,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -7664,7 +7588,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -7684,7 +7608,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -7704,7 +7628,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -7724,7 +7648,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -7744,7 +7668,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -7764,7 +7688,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -7784,7 +7708,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -7804,7 +7728,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -7824,7 +7748,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -7844,7 +7768,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -7864,7 +7788,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -7884,7 +7808,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -7904,7 +7828,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -7924,7 +7848,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -7944,7 +7868,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -7964,7 +7888,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -7984,7 +7908,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -8004,7 +7928,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -8024,7 +7948,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -8044,7 +7968,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -8064,7 +7988,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -8084,7 +8008,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -8104,7 +8028,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -8124,7 +8048,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -8144,7 +8068,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -8164,7 +8088,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -8184,7 +8108,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -8204,7 +8128,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -8224,7 +8148,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -8244,7 +8168,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -8264,7 +8188,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -8284,7 +8208,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -8304,7 +8228,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -8324,7 +8248,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>15</v>
       </c>
@@ -8344,7 +8268,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -8364,7 +8288,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -8384,7 +8308,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -8404,7 +8328,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -8424,7 +8348,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>15</v>
       </c>
@@ -8444,7 +8368,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>15</v>
       </c>
@@ -8464,7 +8388,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>15</v>
       </c>
@@ -8484,7 +8408,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -8504,7 +8428,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -8524,7 +8448,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -8544,7 +8468,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>15</v>
       </c>
@@ -8564,7 +8488,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -8584,7 +8508,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>15</v>
       </c>
@@ -8604,7 +8528,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -8624,7 +8548,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -8644,7 +8568,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -8664,7 +8588,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -8684,7 +8608,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>15</v>
       </c>
@@ -8704,7 +8628,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>15</v>
       </c>
@@ -8724,7 +8648,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -8744,7 +8668,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>15</v>
       </c>
@@ -8764,7 +8688,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -8784,7 +8708,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>15</v>
       </c>
@@ -8804,7 +8728,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>15</v>
       </c>
@@ -8824,7 +8748,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -8844,7 +8768,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -8864,7 +8788,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -8884,7 +8808,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -8904,7 +8828,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -8924,7 +8848,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -8944,7 +8868,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -8964,7 +8888,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -8984,7 +8908,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -9004,7 +8928,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -9024,7 +8948,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -9044,7 +8968,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -9064,7 +8988,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -9084,7 +9008,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -9104,7 +9028,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -9124,7 +9048,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -9144,7 +9068,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>15</v>
       </c>
@@ -9164,7 +9088,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -9184,7 +9108,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -9204,7 +9128,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -9224,7 +9148,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -9244,7 +9168,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -9264,7 +9188,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -9284,7 +9208,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -9304,7 +9228,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -9324,7 +9248,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -9344,7 +9268,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -9364,7 +9288,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -9384,7 +9308,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -9404,7 +9328,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -9424,7 +9348,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -9444,7 +9368,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -9464,7 +9388,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -9484,7 +9408,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -9504,7 +9428,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -9524,7 +9448,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -9544,7 +9468,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -9564,7 +9488,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -9584,7 +9508,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -9604,7 +9528,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -9624,7 +9548,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -9644,7 +9568,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -9664,7 +9588,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -9684,7 +9608,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -9704,7 +9628,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -9724,7 +9648,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -9744,7 +9668,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -9764,7 +9688,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -9784,7 +9708,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -9804,7 +9728,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -9824,7 +9748,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -9844,7 +9768,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -9864,7 +9788,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -9884,7 +9808,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -9904,7 +9828,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -9924,7 +9848,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>15</v>
       </c>
@@ -9944,7 +9868,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -9964,7 +9888,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -9984,7 +9908,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>15</v>
       </c>
@@ -10004,7 +9928,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>15</v>
       </c>
@@ -10024,7 +9948,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>15</v>
       </c>
@@ -10044,7 +9968,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>15</v>
       </c>
@@ -10064,7 +9988,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>15</v>
       </c>
@@ -10084,7 +10008,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>15</v>
       </c>
@@ -10104,7 +10028,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>15</v>
       </c>
@@ -10124,7 +10048,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>15</v>
       </c>
@@ -10144,7 +10068,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>15</v>
       </c>
@@ -10164,7 +10088,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>15</v>
       </c>
@@ -10184,7 +10108,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>15</v>
       </c>
@@ -10204,7 +10128,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>15</v>
       </c>
@@ -10224,7 +10148,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>15</v>
       </c>
@@ -10244,7 +10168,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>15</v>
       </c>
@@ -10264,7 +10188,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -10284,7 +10208,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>15</v>
       </c>
@@ -10304,7 +10228,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>15</v>
       </c>
@@ -10324,7 +10248,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>15</v>
       </c>
@@ -10344,7 +10268,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>15</v>
       </c>
@@ -10364,7 +10288,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>15</v>
       </c>
@@ -10384,7 +10308,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>15</v>
       </c>
@@ -10404,7 +10328,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>15</v>
       </c>
@@ -10424,7 +10348,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>15</v>
       </c>
@@ -10444,7 +10368,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>15</v>
       </c>
@@ -10464,7 +10388,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>15</v>
       </c>
@@ -10484,7 +10408,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -10504,7 +10428,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>15</v>
       </c>
@@ -10524,7 +10448,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>15</v>
       </c>
@@ -10544,7 +10468,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -10564,7 +10488,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>15</v>
       </c>
@@ -10584,7 +10508,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -10604,7 +10528,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>15</v>
       </c>
@@ -10624,7 +10548,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>15</v>
       </c>
@@ -10644,7 +10568,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>15</v>
       </c>
@@ -10664,7 +10588,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>15</v>
       </c>
@@ -10684,7 +10608,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>15</v>
       </c>
@@ -10704,7 +10628,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>15</v>
       </c>
@@ -10724,7 +10648,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>15</v>
       </c>
@@ -10744,7 +10668,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>15</v>
       </c>
@@ -10764,7 +10688,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>15</v>
       </c>
@@ -10784,7 +10708,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>15</v>
       </c>
@@ -10804,7 +10728,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>15</v>
       </c>
@@ -10824,7 +10748,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>15</v>
       </c>
@@ -10844,7 +10768,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>15</v>
       </c>
@@ -10864,7 +10788,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>15</v>
       </c>
@@ -10884,7 +10808,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>15</v>
       </c>
@@ -10904,7 +10828,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>15</v>
       </c>
@@ -10924,7 +10848,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>15</v>
       </c>
@@ -10944,7 +10868,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>15</v>
       </c>
@@ -10964,7 +10888,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>15</v>
       </c>
@@ -10984,7 +10908,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>15</v>
       </c>
@@ -11004,7 +10928,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>15</v>
       </c>
@@ -11024,7 +10948,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>15</v>
       </c>
@@ -11044,7 +10968,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>15</v>
       </c>
@@ -11064,7 +10988,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>15</v>
       </c>
@@ -11084,7 +11008,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>15</v>
       </c>
@@ -11104,7 +11028,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>15</v>
       </c>
@@ -11124,7 +11048,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>15</v>
       </c>
@@ -11144,7 +11068,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>15</v>
       </c>
@@ -11164,7 +11088,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>15</v>
       </c>
@@ -11184,7 +11108,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>15</v>
       </c>
@@ -11204,7 +11128,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>15</v>
       </c>
@@ -11224,7 +11148,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>15</v>
       </c>
@@ -11244,7 +11168,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>15</v>
       </c>
@@ -11264,7 +11188,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>15</v>
       </c>
@@ -11284,7 +11208,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -11304,7 +11228,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -11327,4 +11251,1303 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F25" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F28" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" t="s">
+        <v>232</v>
+      </c>
+      <c r="F31" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" t="s">
+        <v>239</v>
+      </c>
+      <c r="F32" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" t="s">
+        <v>246</v>
+      </c>
+      <c r="F33" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" t="s">
+        <v>252</v>
+      </c>
+      <c r="E34" t="s">
+        <v>253</v>
+      </c>
+      <c r="F34" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" t="s">
+        <v>259</v>
+      </c>
+      <c r="E35" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" t="s">
+        <v>209</v>
+      </c>
+      <c r="D36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E36" t="s">
+        <v>267</v>
+      </c>
+      <c r="F36" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" t="s">
+        <v>209</v>
+      </c>
+      <c r="D37" t="s">
+        <v>273</v>
+      </c>
+      <c r="E37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F37" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D38" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" t="s">
+        <v>281</v>
+      </c>
+      <c r="F38" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E40" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" t="s">
+        <v>209</v>
+      </c>
+      <c r="D41" t="s">
+        <v>301</v>
+      </c>
+      <c r="E41" t="s">
+        <v>302</v>
+      </c>
+      <c r="F41" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" t="s">
+        <v>209</v>
+      </c>
+      <c r="D42" t="s">
+        <v>308</v>
+      </c>
+      <c r="E42" t="s">
+        <v>309</v>
+      </c>
+      <c r="F42" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" t="s">
+        <v>315</v>
+      </c>
+      <c r="E43" t="s">
+        <v>316</v>
+      </c>
+      <c r="F43" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" t="s">
+        <v>209</v>
+      </c>
+      <c r="D44" t="s">
+        <v>322</v>
+      </c>
+      <c r="E44" t="s">
+        <v>323</v>
+      </c>
+      <c r="F44" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>329</v>
+      </c>
+      <c r="C45" t="s">
+        <v>330</v>
+      </c>
+      <c r="D45" t="s">
+        <v>331</v>
+      </c>
+      <c r="E45" t="s">
+        <v>332</v>
+      </c>
+      <c r="F45" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>329</v>
+      </c>
+      <c r="C46" t="s">
+        <v>330</v>
+      </c>
+      <c r="D46" t="s">
+        <v>338</v>
+      </c>
+      <c r="E46" t="s">
+        <v>339</v>
+      </c>
+      <c r="F46" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>329</v>
+      </c>
+      <c r="C47" t="s">
+        <v>330</v>
+      </c>
+      <c r="D47" t="s">
+        <v>345</v>
+      </c>
+      <c r="E47" t="s">
+        <v>346</v>
+      </c>
+      <c r="F47" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D48" t="s">
+        <v>352</v>
+      </c>
+      <c r="E48" t="s">
+        <v>353</v>
+      </c>
+      <c r="F48" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>329</v>
+      </c>
+      <c r="C49" t="s">
+        <v>330</v>
+      </c>
+      <c r="D49" t="s">
+        <v>359</v>
+      </c>
+      <c r="E49" t="s">
+        <v>360</v>
+      </c>
+      <c r="F49" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>329</v>
+      </c>
+      <c r="C50" t="s">
+        <v>330</v>
+      </c>
+      <c r="D50" t="s">
+        <v>366</v>
+      </c>
+      <c r="E50" t="s">
+        <v>367</v>
+      </c>
+      <c r="F50" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>329</v>
+      </c>
+      <c r="C51" t="s">
+        <v>330</v>
+      </c>
+      <c r="D51" t="s">
+        <v>373</v>
+      </c>
+      <c r="E51" t="s">
+        <v>374</v>
+      </c>
+      <c r="F51" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>380</v>
+      </c>
+      <c r="C52" t="s">
+        <v>381</v>
+      </c>
+      <c r="D52" t="s">
+        <v>382</v>
+      </c>
+      <c r="E52" t="s">
+        <v>383</v>
+      </c>
+      <c r="F52" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>380</v>
+      </c>
+      <c r="C53" t="s">
+        <v>381</v>
+      </c>
+      <c r="D53" t="s">
+        <v>389</v>
+      </c>
+      <c r="E53" t="s">
+        <v>390</v>
+      </c>
+      <c r="F53" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>380</v>
+      </c>
+      <c r="C54" t="s">
+        <v>381</v>
+      </c>
+      <c r="D54" t="s">
+        <v>396</v>
+      </c>
+      <c r="E54" t="s">
+        <v>397</v>
+      </c>
+      <c r="F54" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>380</v>
+      </c>
+      <c r="C55" t="s">
+        <v>381</v>
+      </c>
+      <c r="D55" t="s">
+        <v>403</v>
+      </c>
+      <c r="E55" t="s">
+        <v>404</v>
+      </c>
+      <c r="F55" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>410</v>
+      </c>
+      <c r="C56" t="s">
+        <v>411</v>
+      </c>
+      <c r="D56" t="s">
+        <v>412</v>
+      </c>
+      <c r="E56" t="s">
+        <v>413</v>
+      </c>
+      <c r="F56" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" t="s">
+        <v>411</v>
+      </c>
+      <c r="D57" t="s">
+        <v>419</v>
+      </c>
+      <c r="E57" t="s">
+        <v>420</v>
+      </c>
+      <c r="F57" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>410</v>
+      </c>
+      <c r="C58" t="s">
+        <v>411</v>
+      </c>
+      <c r="D58" t="s">
+        <v>426</v>
+      </c>
+      <c r="E58" t="s">
+        <v>427</v>
+      </c>
+      <c r="F58" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>410</v>
+      </c>
+      <c r="C59" t="s">
+        <v>411</v>
+      </c>
+      <c r="D59" t="s">
+        <v>433</v>
+      </c>
+      <c r="E59" t="s">
+        <v>434</v>
+      </c>
+      <c r="F59" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>410</v>
+      </c>
+      <c r="C60" t="s">
+        <v>411</v>
+      </c>
+      <c r="D60" t="s">
+        <v>440</v>
+      </c>
+      <c r="E60" t="s">
+        <v>441</v>
+      </c>
+      <c r="F60" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>410</v>
+      </c>
+      <c r="C61" t="s">
+        <v>411</v>
+      </c>
+      <c r="D61" t="s">
+        <v>447</v>
+      </c>
+      <c r="E61" t="s">
+        <v>448</v>
+      </c>
+      <c r="F61" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>410</v>
+      </c>
+      <c r="C62" t="s">
+        <v>411</v>
+      </c>
+      <c r="D62" t="s">
+        <v>454</v>
+      </c>
+      <c r="E62" t="s">
+        <v>455</v>
+      </c>
+      <c r="F62" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" t="s">
+        <v>411</v>
+      </c>
+      <c r="D63" t="s">
+        <v>461</v>
+      </c>
+      <c r="E63" t="s">
+        <v>462</v>
+      </c>
+      <c r="F63" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" t="s">
+        <v>411</v>
+      </c>
+      <c r="D64" t="s">
+        <v>468</v>
+      </c>
+      <c r="E64" t="s">
+        <v>469</v>
+      </c>
+      <c r="F64" t="s">
+        <v>728</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/sample_data/Knowledge_base_updated.xlsx
+++ b/sample_data/Knowledge_base_updated.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5D2F79-28CD-4B8B-B2E9-272F3062CCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Master" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Recommendations" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="KB Tracker" state="visible" r:id="rId6"/>
+    <sheet name="Master" sheetId="1" r:id="rId1"/>
+    <sheet name="Recommendations" sheetId="2" r:id="rId2"/>
+    <sheet name="KB Tracker" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -81,14 +95,14 @@
     <t>Appointment Scheduling</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;20% of inbound trucks arrive against a pre-booked slot.
+    <t>&lt;20% of inbound trucks arrive against a pre-booked slot.
 &gt;50% of daily volume clusters into a single 2-hour window, causing dock queuing beyond 2 hours.
 No designated driver holding area - drivers and helpers congregate at the security gate causing congestion.
 Dock-in time is not captured, so it cannot feed downstream GRN turnaround-time (TAT) SLAs.
 Slot booking, where it exists, is a manual register entry with no QR/Booking-ID confirmation shared with the vendor ahead of arrival.</t>
   </si>
   <si>
-    <t xml:space="preserve">20-50% slot adherence.
+    <t>20-50% slot adherence.
 Peak-hour concentration still exceeds 40% of daily volume.
 Average vehicle wait time 60-120 minutes.
 An informal holding area exists but is not enforced, so congregation at the gate persists.
@@ -96,7 +110,7 @@
 A digital slot booking exists for under 30% of vendors, without a QR/Booking-ID confirmation shared back to the vendor.</t>
   </si>
   <si>
-    <t xml:space="preserve">50-75% slot adherence via a basic appointment scheduler.
+    <t>50-75% slot adherence via a basic appointment scheduler.
 Peak-hour concentration reduced to 25-40%.
 Average wait time 30-60 minutes.
 A designated driver holding area away from the security gate is marked and used for the majority of vehicles.
@@ -104,7 +118,7 @@
 A digital slot booking with a QR/Booking-ID confirmation (D-2 indent leading to a D-1 slot) is shared with 30-60% of vendors ahead of arrival.</t>
   </si>
   <si>
-    <t xml:space="preserve">75-90% slot adherence with system-enforced windows.
+    <t>75-90% slot adherence with system-enforced windows.
 Peak-hour concentration under 25%.
 Average wait time under 30 minutes.
 Adherence tracked daily.
@@ -113,7 +127,7 @@
 Digital slot booking with a QR/Booking-ID confirmation (D-2 indent to D-1 slot) is shared with 60-90% of vendors, scanned at the gate to authenticate arrival.</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt;90% slot adherence with automated vendor notification.
+    <t>&gt;90% slot adherence with automated vendor notification.
 Load spread within +/-10% across all shift hours.
 Average wait time under 15 minutes.
 The holding area is fully marshalled with real-time occupancy visibility and zero congregation at the security gate.
@@ -130,27 +144,27 @@
     <t>Gate Entry &amp; Documentation Verification</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;50% of gate entries verified against indent/invoice before unloading starts (across the 70:30 vendor:courier vehicle mix, with no differentiated checklist for vendor vs courier vehicles).
+    <t>&lt;50% of gate entries verified against indent/invoice before unloading starts (across the 70:30 vendor:courier vehicle mix, with no differentiated checklist for vendor vs courier vehicles).
 Documentation/invoice mismatch rate above 30%.
 Average gate-in time over 20 min/vehicle.
 There is no driver-ID or vehicle-number authentication against the booked slot, and temperature checks (where done at all) are not scoped to any specific SKU or deviation threshold.</t>
   </si>
   <si>
-    <t xml:space="preserve">50-70% verified pre-unload, using a single generic checklist applied to both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicles.
+    <t>50-70% verified pre-unload, using a single generic checklist applied to both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicles.
 Mismatch rate 20-30%.
 Gate-in time 15-20 min/vehicle.
 Driver-ID and vehicle-number are checked against the slot for under 30% of vehicles.
 A temperature check is performed inconsistently and without a defined deviation threshold, even for 4°C-sensitive SKUs (e.g., mushrooms).</t>
   </si>
   <si>
-    <t xml:space="preserve">70-85% verified against a defined checklist (vendor, invoice, indented qty, reefer temperature), with separate verification steps for vendor trucks (70% of vehicle mix) and courier vans (30% of vehicle mix).
+    <t>70-85% verified against a defined checklist (vendor, invoice, indented qty, reefer temperature), with separate verification steps for vendor trucks (70% of vehicle mix) and courier vans (30% of vehicle mix).
 Mismatch rate 10-20%.
 Gate-in time 10-15 min.
 Driver-ID and vehicle-number are authenticated against the vendor code, PO, and slot for 30-60% of vehicles.
 Temperature is checked specifically for 4°C-sensitive SKUs (e.g., mushrooms) but the reject threshold (e.g., &gt;3°C deviation) is not consistently applied.</t>
   </si>
   <si>
-    <t xml:space="preserve">85-95% verified via system-assisted matching (barcode/OCR) across both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicle streams.
+    <t>85-95% verified via system-assisted matching (barcode/OCR) across both vendor (70% of vehicle mix) and courier (30% of vehicle mix) vehicle streams.
 Mismatch rate 5-10%.
 Gate-in time 5-10 min.
 100% of reefer vehicles temperature-logged.
@@ -158,7 +172,7 @@
 A defined temperature-reject rule (&gt;3°C deviation for 4°C-sensitive SKUs such as mushrooms only, not the full FnV range) is applied consistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt;95% verified end-to-end digitally with zero manual entry, with vendor (70% of vehicle mix) and courier (30% of vehicle mix) streams tracked and matched separately.
+    <t>&gt;95% verified end-to-end digitally with zero manual entry, with vendor (70% of vehicle mix) and courier (30% of vehicle mix) streams tracked and matched separately.
 Mismatch rate under 5%.
 Gate-in time under 5 min.
 Full audit trail with automated exception flags.
@@ -172,28 +186,28 @@
     <t>Manpower Entry Management</t>
   </si>
   <si>
-    <t xml:space="preserve">0% biometric/facial recognition coverage at shift changeovers.
+    <t>0% biometric/facial recognition coverage at shift changeovers.
 Manual register only, with no zone-wise capturing of manpower entries (e.g., S&amp;G, packing, put-away, dispatch) against warehouse-sizing-based headcount norms.
 Unauthorized-entry incidents exceed 60 per month.</t>
   </si>
   <si>
-    <t xml:space="preserve">Under 30% biometric coverage.
+    <t>Under 30% biometric coverage.
 Manual plus partial physical checks.
 Zone-wise entry counts recorded ad hoc for under 30% of zones, not benchmarked against a sizing-based manpower plan.
 Unauthorized-entry incidents 30-60 per month.</t>
   </si>
   <si>
-    <t xml:space="preserve">30-60% facial recognition coverage at main shift changeovers.
+    <t>30-60% facial recognition coverage at main shift changeovers.
 Zone-wise manpower entry tracked for 30-60% of zones (e.g., S&amp;G, packing, put-away) against a defined warehouse-sizing-based headcount norm (illustrative only - e.g., ~10 for S&amp;G, ~25 for packing), reviewed periodically rather than daily.
 Unauthorized-entry incidents 10-30 per month.</t>
   </si>
   <si>
-    <t xml:space="preserve">60-90% coverage across all shifts and gates.
+    <t>60-90% coverage across all shifts and gates.
 Zone-wise entry captured and reconciled daily for 60-90% of zones against the warehouse-sizing-based manpower plan, integrated with the attendance system.
 Unauthorized-entry incidents under 10 per month, zero incidents in the last quarter.</t>
   </si>
   <si>
-    <t xml:space="preserve">100% facial recognition and physical-check coverage across all shifts and gates.
+    <t>100% facial recognition and physical-check coverage across all shifts and gates.
 Zone-wise manpower entry captured in real time for 100% of zones, with automated variance alerts against the warehouse-sizing-based headcount plan.
 Zero unauthorized-entry incidents in the last 12 months.
 Real-time anomaly alerts.</t>
@@ -205,27 +219,27 @@
     <t>Dock Management System</t>
   </si>
   <si>
-    <t xml:space="preserve">No formal dock allocation.
+    <t>No formal dock allocation.
 Dock utilization under 50%.
 Docks unnumbered or inconsistently numbered.</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual dock allocation sheet.
+    <t>Manual dock allocation sheet.
 Utilization 50-65%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Defined dock allocation by vehicle size with numbered docks.
+    <t>Defined dock allocation by vehicle size with numbered docks.
 Utilization 65-80%.
 FIFO followed for over 70% of vehicles.</t>
   </si>
   <si>
-    <t xml:space="preserve">System-based dock scheduling with size-matched allocation.
+    <t>System-based dock scheduling with size-matched allocation.
 Utilization 80-90%.
 FIFO adherence above 90%.
 Green-channel vehicles unloaded within 15 minutes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully automated dock-vehicle matching with real-time queuing.
+    <t>Fully automated dock-vehicle matching with real-time queuing.
 Utilization above 90%.
 FIFO adherence 100%.
 Green-channel wait time under 10 minutes.</t>
@@ -237,32 +251,32 @@
     <t>Dock Buffers</t>
   </si>
   <si>
-    <t xml:space="preserve">Under 25% of docks fitted with buffers.
+    <t>Under 25% of docks fitted with buffers.
 More than 1 dock-damage incident per week.
 No penalty framework for drivers causing repeat dock damage.
 Physical damage to dock structures (bumpers, levelers, shelters, columns) not tracked or inspected separately from buffer coverage.</t>
   </si>
   <si>
-    <t xml:space="preserve">25-50% buffer coverage.
+    <t>25-50% buffer coverage.
 1 dock-damage incident per week on average.
 Repeat-offender drivers flagged informally but no defined penalty applied.
 Physical dock-structure damage noted only when reported by staff, with no periodic inspection.</t>
   </si>
   <si>
-    <t xml:space="preserve">50-75% buffer coverage.
+    <t>50-75% buffer coverage.
 1 dock-damage incident every 2 weeks.
 A defined penalty (e.g., warning/fine) applied to drivers on a repeat incident.
 Physical dock-structure damage inspected monthly and logged separately from buffer-related damage.</t>
   </si>
   <si>
-    <t xml:space="preserve">75-95% buffer coverage.
+    <t>75-95% buffer coverage.
 Fewer than 1 dock-damage incident every 4 weeks.
 A graded penalty scale (warning, fine, vendor/transporter review) enforced for repeat-offender drivers.
 Periodic buffer-condition audits in place.
 Physical dock-structure damage inspected weekly with defects tracked to closure.</t>
   </si>
   <si>
-    <t xml:space="preserve">100% dock buffer coverage.
+    <t>100% dock buffer coverage.
 Zero damage incidents in the last 12 months.
 Graded penalty scale for repeat-offender drivers strictly enforced with under 2% repeat-offense rate.
 Preventive maintenance schedule tracked.
@@ -275,7 +289,7 @@
     <t>Unloading Operations &amp; Floor Management</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined/target unloading SLA.
+    <t>No defined/target unloading SLA.
 No dock-wise dedicated workforce assigned.
 No defined palletisation zone (material is palletized wherever space is available, creating space constraints at the inbound gate).
 No crate-stacking pattern defined (poor vertical space utilization).
@@ -284,7 +298,7 @@
 No bypass-routing flag exists for vendor pre-packed material, so pre-packed loads are routed through S&amp;G by default regardless of need.</t>
   </si>
   <si>
-    <t xml:space="preserve">An unloading SLA is defined but tracked for under 30% of docks (benchmark: ~500 units/person/hour for pre-packed material).
+    <t>An unloading SLA is defined but tracked for under 30% of docks (benchmark: ~500 units/person/hour for pre-packed material).
 Dock-wise workforce assignment is informal.
 A palletisation zone is nominally marked but frequently encroached upon.
 Crate stacking has no defined SOP.
@@ -292,7 +306,7 @@
 A bypass flag for vendor pre-packed material is used informally for under 30% of eligible loads.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unloading SLA (~500 units/person/hour pre-packed) is tracked for 30-60% of docks with a dock-wise supervisor-led team.
+    <t>Unloading SLA (~500 units/person/hour pre-packed) is tracked for 30-60% of docks with a dock-wise supervisor-led team.
 A visibly marked palletisation zone and sorting/grading area are maintained on most days.
 A crate-stacking SOP (max stack height, brick/inline pattern) is defined but followed inconsistently.
 A green channel exists for some reliable vendors.
@@ -300,7 +314,7 @@
 A bypass-routing flag for vendor pre-packed material, skipping S&amp;G and routing straight to packing/staging, is applied for 30-60% of eligible loads.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unloading SLA is tracked for 60-90% of docks against benchmark, with a dock-wise supervisor-led team on every shift.
+    <t>Unloading SLA is tracked for 60-90% of docks against benchmark, with a dock-wise supervisor-led team on every shift.
 Palletisation zone, unloading area, and S&amp;G area are marked and adhered to.
 Crate-stacking SOP is followed on 70-95% of pallets.
 A green channel is consistently used for reliable vendors.
@@ -309,7 +323,7 @@
 The bypass-routing flag for vendor pre-packed material is applied for 60-90% of eligible loads, tracked as part of the load-declaration step at gate/weighment.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unloading SLA is tracked for over 90% of docks and consistently meets/exceeds the ~500 units/person/hour benchmark, with a dock-wise supervisor-led team at all times.
+    <t>Unloading SLA is tracked for over 90% of docks and consistently meets/exceeds the ~500 units/person/hour benchmark, with a dock-wise supervisor-led team at all times.
 Palletisation zone, unloading area, and S&amp;G area are marked, audited, and adhered to with zero space-constraint incidents.
 Crate-stacking SOP compliance exceeds 95%.
 Green-channel and dry-category lanes operate with zero cross-flow incidents.
@@ -323,32 +337,32 @@
     <t>Weighment &amp; GRN Digitization</t>
   </si>
   <si>
-    <t xml:space="preserve">Weighment data is logged manually for GRN/PO creation - error-prone and slow.
+    <t>Weighment data is logged manually for GRN/PO creation - error-prone and slow.
 Weighment occurs downstream of S&amp;G, increasing vendor wait time and delaying PO closure.
 The weighment area sits hard against the staging area with no clear aisle, creating a choke point.
 Scale calibration is untracked.</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual logging accounts for over 70% of weighment transactions.
+    <t>Manual logging accounts for over 70% of weighment transactions.
 Weighment is still performed post-S&amp;G for the majority of vehicles.
 The clear aisle between weighment and staging is under 1.5m or undefined.
 Scale calibration is done ad hoc with no fixed schedule.</t>
   </si>
   <si>
-    <t xml:space="preserve">Digital weighment is integrated with the WMS/GRN system for 30-60% of transactions.
+    <t>Digital weighment is integrated with the WMS/GRN system for 30-60% of transactions.
 Weighment has been shifted to the unloading stage for some vendor categories, reducing PO-closure delay.
 A minimum 1.5m clear aisle between weighment and staging is maintained on most days.
 Scales are calibrated on a defined but not strictly daily schedule.</t>
   </si>
   <si>
-    <t xml:space="preserve">Digital weighment integrated with WMS/GRN covers 60-90% of transactions.
+    <t>Digital weighment integrated with WMS/GRN covers 60-90% of transactions.
 Weighment is performed at the unloading stage for the majority of vendors, ahead of S&amp;G.
 The 1.5m clear-aisle buffer between weighment and staging is consistently maintained.
 Calibrated scales with tare memory per packaging type are recalibrated on a defined schedule (daily recommended).
 Digital weight logs are retained as an audit trail.</t>
   </si>
   <si>
-    <t xml:space="preserve">Over 90% of weighment transactions are digitally integrated with WMS/GRN with zero manual entry.
+    <t>Over 90% of weighment transactions are digitally integrated with WMS/GRN with zero manual entry.
 Weighment is performed at the unloading stage for all applicable vendors, enabling same-day PO closure.
 The 1.5m clear-aisle buffer is maintained with zero choke-point incidents.
 Scales are recalibrated daily with tare memory per packaging type.
@@ -361,27 +375,27 @@
     <t>Gate Release Decision &amp; Capacity Gating</t>
   </si>
   <si>
-    <t xml:space="preserve">Gate operates as a security checkpoint, not a capacity-gated release valve: trucks are waved onto the dock/yard regardless of whether a dock bay or staging space is available, with no reject / temp-reject / hold / bypass decision rule (checks vary guard-to-guard).
+    <t>Gate operates as a security checkpoint, not a capacity-gated release valve: trucks are waved onto the dock/yard regardless of whether a dock bay or staging space is available, with no reject / temp-reject / hold / bypass decision rule (checks vary guard-to-guard).
 Gate-out has no exit slip or outbound-seal verification. Vehicles routinely block the dock and back up into S&amp;G congestion.</t>
   </si>
   <si>
-    <t xml:space="preserve">A capacity check is attempted informally for under 30% of gate-ins (e.g., a phone call to the dock supervisor) with no defined time window, so vehicles sent to hold still cause dock-blocking regularly.
+    <t>A capacity check is attempted informally for under 30% of gate-ins (e.g., a phone call to the dock supervisor) with no defined time window, so vehicles sent to hold still cause dock-blocking regularly.
 Reject/hold decisions depend on individual guard judgment.
 Gate-out has no formal exit slip or seal check.</t>
   </si>
   <si>
-    <t xml:space="preserve">A defined capacity check (dock bay + staging pallet positions available within a stated window, e.g., 15 minutes) gates 30-60% of gate-ins, routing 'no' decisions to the holding area.
+    <t>A defined capacity check (dock bay + staging pallet positions available within a stated window, e.g., 15 minutes) gates 30-60% of gate-ins, routing 'no' decisions to the holding area.
 A basic reject-vs-hold rule exists, but temp-reject (scoped to 4°C SKUs) and bypass-routing (pre-packed vendors) are not yet part of the same decision rule.
 Gate-out issues an exit slip for the majority of dispatches but outbound-seal verification is inconsistent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacity-gated release (dock bay + staging space confirmed within 15 minutes) governs 60-90% of gate-ins.
+    <t>Capacity-gated release (dock bay + staging space confirmed within 15 minutes) governs 60-90% of gate-ins.
 The full reject / temp-reject / hold / bypass decision taxonomy is defined and applied consistently, with 'hold' vehicles routed to the designated holding area.
 Gate-out issues an exit slip and verifies the outbound vehicle seal for the majority of dispatches.
 Physical enablers (multi-lane entry, boom barrier, CCTV/tablet at the gate) are in place.</t>
   </si>
   <si>
-    <t xml:space="preserve">Over 90% of gate-ins are capacity-gated in real time (dock bay + staging space confirmed within 15 minutes, tied live to the dock-management and staging systems), with zero blind releases and zero dock-blocking incidents.
+    <t>Over 90% of gate-ins are capacity-gated in real time (dock bay + staging space confirmed within 15 minutes, tied live to the dock-management and staging systems), with zero blind releases and zero dock-blocking incidents.
 The full reject / temp-reject / hold / bypass decision taxonomy is applied with a complete audit trail.
 Gate-out is fully controlled (exit slip plus outbound-seal verification on 100% of dispatches).
 Physical enablers (multi-lane entry with boom barrier, CCTV/tablet, and weighbridge where applicable) are fully deployed.</t>
@@ -465,11 +479,11 @@
     <t>0-2 of the 9 core QMS elements (policy, objectives, SOPs, exception handling, responsibility matrix, escalation matrix, risk analysis, complaints/feedback loop, documentation control) are documented.</t>
   </si>
   <si>
-    <t xml:space="preserve">3-4 elements documented.
+    <t>3-4 elements documented.
 No formal review cycle in place.</t>
   </si>
   <si>
-    <t xml:space="preserve">5-6 elements documented and in active use.
+    <t>5-6 elements documented and in active use.
 Reviewed annually.</t>
   </si>
   <si>
@@ -485,32 +499,32 @@
     <t>Inbound Quality Check Norms</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined sampling percentage or rejection threshold.
+    <t>No defined sampling percentage or rejection threshold.
 Inspection is ad hoc, covering under 5% of inbound lots.
 GRN is raised and approved without any dependency on a quality-check procedure or quality-team clearance.
 Acceptance/rejection is based purely on visual inspection with no structured Arrival Quality Report (AQR) or fixed cutoff defined before unloading begins, and QC/vehicle rejection rates are not tracked by vendor or SKU.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling done on 5-10% of lots, but rejection threshold undefined or inconsistently applied.
+    <t>Sampling done on 5-10% of lots, but rejection threshold undefined or inconsistently applied.
 GRN approval nominally requires quality-team sign-off, but this is often obtained after goods are already put away, not before GRN posting.
 A written AQR format exists but fixed sampling/defect cutoffs are not consistently applied before unloading starts.
 Rejection data is recorded but not segmented by vendor or SKU.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling fixed at approximately 10% of received quantity.
+    <t>Sampling fixed at approximately 10% of received quantity.
 Rejection threshold set at 20% defect rate for full-lot rejection, but not segmented by SKU/category.
 GRN approval is procedurally linked to quality-team clearance, but clearance is manual/paper-based and not enforced as a system hold.
 A defined AQR is used for the majority of lots (e.g., 10% sampling, reject lot if defect &gt;20%), completed before unloading begins.
 QC reject % and vehicle rejection % are tracked in aggregate but not yet split by vendor/SKU for a supplier scorecard.</t>
   </si>
   <si>
-    <t xml:space="preserve">10% sampling and 20% rejection threshold applied and segmented by category (FnV vs dry), with batch/expiry and 70-80% shelf-life checks enforced.
+    <t>10% sampling and 20% rejection threshold applied and segmented by category (FnV vs dry), with batch/expiry and 70-80% shelf-life checks enforced.
 GRN cannot be posted until the quality team records clearance against the defined inspection procedure.
 AQR with fixed sampling/defect cutoffs is completed before unloading starts for 85-95% of lots.
 QC reject % and vehicle rejection % are tracked by vendor and SKU and feed a periodic supplier scorecard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling and rejection norms (10%/20%) defined per SKU category, digitally logged, with under 2% inspection-error rate and monthly trend analysis on rejection causes.
+    <t>Sampling and rejection norms (10%/20%) defined per SKU category, digitally logged, with under 2% inspection-error rate and monthly trend analysis on rejection causes.
 GRN approval is system-enforced with zero exceptions, released only on digital quality-team clearance against the defined procedure, with a full audit trail of inspector sign-off.
 AQR is completed before unloading begins for over 95% of lots with zero exceptions.
 QC reject % and vehicle rejection % by vendor and SKU are tracked in real time and drive an automated, continuously updated supplier scorecard used in vendor review.</t>
@@ -522,24 +536,24 @@
     <t>Return to Vendor Policy</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined return-to-vendor (RTV) policy.
+    <t>No defined return-to-vendor (RTV) policy.
 Under 30% of returns closed same-day.</t>
   </si>
   <si>
-    <t xml:space="preserve">Informal RTV process.
+    <t>Informal RTV process.
 30-50% same-day closure.</t>
   </si>
   <si>
-    <t xml:space="preserve">RTV policy defined by SKU category (hard/soft).
+    <t>RTV policy defined by SKU category (hard/soft).
 50-75% same-day closure.</t>
   </si>
   <si>
-    <t xml:space="preserve">RTV policy defined and tracked.
+    <t>RTV policy defined and tracked.
 75-95% same-day closure.
 Space occupied by pending returns reviewed weekly.</t>
   </si>
   <si>
-    <t xml:space="preserve">RTV fully systemized.
+    <t>RTV fully systemized.
 Over 95% same-day closure.
 Zero aged-return inventory beyond 24 hours.</t>
   </si>
@@ -550,23 +564,23 @@
     <t>Customer Complaint Tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">Complaint rate exceeds 3% of FnV volume handled, or is not tracked at all.
+    <t>Complaint rate exceeds 3% of FnV volume handled, or is not tracked at all.
 Complaint density is not tracked in PPM at all, or exceeds 500 PPM where estimated, so order-level density cannot be benchmarked against a quick-commerce/dark-store standard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complaint rate tracked at 2.5-3%, with no root-cause analysis.
+    <t>Complaint rate tracked at 2.5-3%, with no root-cause analysis.
 Complaints PPM runs at 200-500, calculated only occasionally/retrospectively.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complaint rate at the typical industry band of 2-2.5%, tracked monthly with basic categorization.
+    <t>Complaint rate at the typical industry band of 2-2.5%, tracked monthly with basic categorization.
 Complaints PPM runs at 100-200, tracked monthly alongside the %-of-volume metric.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complaint rate reduced to 1-2%, with root-cause analysis and corrective actions closed within 7 days.
+    <t>Complaint rate reduced to 1-2%, with root-cause analysis and corrective actions closed within 7 days.
 Complaints PPM runs at 50-100, tracked weekly against a defined benchmark band.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complaint rate under 1% (best-in-class), with real-time tracking, root-cause analysis, and closed-loop resolution within 48 hours.
+    <t>Complaint rate under 1% (best-in-class), with real-time tracking, root-cause analysis, and closed-loop resolution within 48 hours.
 Complaints PPM is held under 50 (best-in-class), tracked daily against benchmark, giving both a wholesale (volume-based) and dark-store/quick-commerce (order-based) view of complaint density.</t>
   </si>
   <si>
@@ -624,33 +638,33 @@
     <t>5S Implementation</t>
   </si>
   <si>
-    <t xml:space="preserve">No formal 5S audit.
+    <t>No formal 5S audit.
 Audit score under 40% where measured at all.
 No physical demarcation of aisles, S&amp;G/packing areas, storage space, buffer-pallet staging, packaging-material storage, or tools/machinery locations - floor markings, if any, are inconsistent or absent.
 No designated area/zone name signage, fire extinguisher position signage, or fire exit signage is installed anywhere in the facility.</t>
   </si>
   <si>
-    <t xml:space="preserve">5S introduced in a pilot area only.
+    <t>5S introduced in a pilot area only.
 Audit score 40-55%.
 Floor marking/demarcation done for under 30% of the required zones (aisles, S&amp;G/packing spaces, storage, buffer-pallet staging, packaging material, tools/machinery), and only in the pilot area.
 Signage exists for a few zones and fire extinguisher points only, limited to the pilot area; fire exits are marked but not consistently visible or illuminated.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sort/Set/Shine implemented facility-wide.
+    <t>Sort/Set/Shine implemented facility-wide.
 Audit score 55-70%.
 Audits conducted quarterly.
 Demarcation in place for 30-60% of required zones - e.g., aisles and storage racking are marked, but S&amp;G/packing space, buffer-pallet staging, packaging-material, and tools/machinery locations are only partially marked.
 Designated area signage and fire extinguisher position signage are installed for 30-60% of required zones/points; fire exits are signed and illuminated for the main escape routes only.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standardized across all zones with monthly audits.
+    <t>Standardized across all zones with monthly audits.
 Score 70-85%.
 Training conducted at least twice a year.
 Demarcation covers 60-90% of required zones, including aisles, S&amp;G and packing space boundaries, storage space marking, buffer-pallet staging area, and packaging-material storage, with tools/machinery locations marked but not yet audited on a fixed schedule.
 Area signage, fire extinguisher signage, and fire exit signage cover 60-90% of required zones/points/routes, checked alongside the periodic 5S review.</t>
   </si>
   <si>
-    <t xml:space="preserve">5S sustained for over 12 months.
+    <t>5S sustained for over 12 months.
 Audit score above 85%.
 Daily checks, biannual training, and a documented continuous-improvement (Kaizen) count.
 100% of zones demarcated and colour-coded - aisles, S&amp;G and packing spaces, storage space, buffer-pallet staging, packaging-material storage, and tools/machinery locations - with demarcation adherence audited as part of the daily 5S check.
@@ -663,25 +677,25 @@
     <t>Lean Principles Implementation</t>
   </si>
   <si>
-    <t xml:space="preserve">0-1 of the 5 lean principles (value definition, value stream mapping, flow, pull, continuous improvement) deployed.
+    <t>0-1 of the 5 lean principles (value definition, value stream mapping, flow, pull, continuous improvement) deployed.
 No PDCA or waste tracking.</t>
   </si>
   <si>
-    <t xml:space="preserve">2 principles deployed (e.g., value stream mapping started).
+    <t>2 principles deployed (e.g., value stream mapping started).
 PDCA used in under 20% of processes.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 principles deployed.
+    <t>3 principles deployed.
 PDCA embedded in 20-50% of processes.
 2-3 of the 8 waste types tracked.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 principles deployed with pull/JIT replenishment active.
+    <t>4 principles deployed with pull/JIT replenishment active.
 PDCA in 50-80% of processes.
 5-6 of the 8 waste types tracked with quarterly reduction targets.</t>
   </si>
   <si>
-    <t xml:space="preserve">All 5 principles fully embedded.
+    <t>All 5 principles fully embedded.
 PDCA in over 80% of processes.
 All 8 waste types tracked with measurable year-on-year reduction of over 10%.</t>
   </si>
@@ -695,7 +709,7 @@
     <t>Under 30% of standard and exception scenarios documented in SOPs.</t>
   </si>
   <si>
-    <t xml:space="preserve">30-50% documented.
+    <t>30-50% documented.
 Exception flows largely undocumented.</t>
   </si>
   <si>
@@ -720,28 +734,28 @@
     <t>Sorting &amp; Grading Norms</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined size or quality standards (blemish-free, rot-free, infestation-free) for sorting/grading.
+    <t>No defined size or quality standards (blemish-free, rot-free, infestation-free) for sorting/grading.
 Criteria applied on 0% of SKUs.
 No S&amp;G throughput SLA is defined (benchmark: ~70 units/person/hour for general S&amp;G, 400-500 units/person/shift for leafy cutting).
 Piece-category SKUs (e.g., coconut, watermelon) are staffed randomly, causing significant throughput slowdown.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standards defined for under 30% of SKUs.
+    <t>Standards defined for under 30% of SKUs.
 A throughput SLA is defined but tracked for under 30% of stations, with wide variance against the ~70 units/person/hour / 400-500 units/person/shift benchmarks.
 Piece-category SKUs are not assigned to experienced manpower.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standards defined for 30-60% of SKUs, covering blemish, rot, infestation, and size checks.
+    <t>Standards defined for 30-60% of SKUs, covering blemish, rot, infestation, and size checks.
 Throughput SLA (~70 units/person/hour, 400-500/shift for leafy) is tracked for 30-60% of stations.
 Experienced manpower is assigned to piece-category SKUs (coconut, watermelon) only inconsistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standards defined for 60-90% of SKUs, with grading accuracy audited monthly at over 90% accuracy.
+    <t>Standards defined for 60-90% of SKUs, with grading accuracy audited monthly at over 90% accuracy.
 Throughput SLA is tracked for 60-90% of stations, mostly within benchmark.
 Experienced manpower is consistently assigned to piece-category SKUs, limiting their drag on overall S&amp;G throughput.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standards defined for 100% of SKUs.
+    <t>Standards defined for 100% of SKUs.
 Grading accuracy above 95%, audited weekly with a corrective feedback loop.
 Throughput SLA is tracked for 100% of stations and consistently meets or exceeds benchmark (~70 units/person/hour, 400-500/shift leafy).
 Piece-category SKUs are always staffed with experienced manpower, with throughput impact monitored and minimized.</t>
@@ -753,7 +767,7 @@
     <t>Packing Norms &amp; Productivity</t>
   </si>
   <si>
-    <t xml:space="preserve">Packing productivity under 60 units/person/hour.
+    <t>Packing productivity under 60 units/person/hour.
 Packaging material (nets/boxes/LDP) not defined by SKU.
 No shift-level SLA is tracked against the net/box/shrink packing benchmarks (~900-1,000 net, ~1,100-1,200 box, ~1,000-1,100 shrink units/person/shift).
 Formed boxes are stacked directly on the worktop causing clutter.
@@ -761,7 +775,7 @@
 Chilled-category SKUs (e.g., apples, pears) are packed under ambient conditions with no dedicated chilled station.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity 60-80 units/person/hour.
+    <t>Productivity 60-80 units/person/hour.
 Packaging material defined for under 50% of SKUs.
 Shift-level SLA is tracked for under 30% of lines against the net/box/shrink benchmarks.
 A formed-box staging shelf is used on under 30% of lines.
@@ -769,7 +783,7 @@
 Chilled SKUs are packed ambient on over 70% of shifts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity at the 80-100 units/person/hour benchmark band.
+    <t>Productivity at the 80-100 units/person/hour benchmark band.
 Packaging material defined per SKU.
 Shift-level SLA is tracked for 30-60% of lines and trending toward the net/box/shrink benchmarks.
 A formed-box staging shelf decongests the worktop on 30-60% of lines.
@@ -777,7 +791,7 @@
 A dedicated chilled packing station is used for 30-60% of chilled-SKU shifts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity 100-120 units/person/hour, matching category benchmarks (net roll ~90/hr, pannet ~100/hr, LDP ~100/hr).
+    <t>Productivity 100-120 units/person/hour, matching category benchmarks (net roll ~90/hr, pannet ~100/hr, LDP ~100/hr).
 Gang output tracked daily against a 400-500 packets/person/day target.
 Shift-level SLA is tracked for 60-90% of lines and mostly at benchmark (~900-1,200 units/person/shift by pack type).
 Formed-box staging shelf standard is followed on 60-90% of lines.
@@ -785,7 +799,7 @@
 A dedicated chilled packing station is used for 60-90% of chilled-SKU shifts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity above 120 units/person/hour or consistently at the top of the category benchmark.
+    <t>Productivity above 120 units/person/hour or consistently at the top of the category benchmark.
 A 4-cutter + 6-packer gang achieving 4,000+ packets/day, tracked and improved monthly.
 Shift-level SLA is tracked for over 90% of lines and consistently at or above benchmark.
 Formed-box staging shelf standard is followed on all lines.
@@ -799,28 +813,28 @@
     <t>Manpower Planning for Processing</t>
   </si>
   <si>
-    <t xml:space="preserve">No standard manpower norm for processing tables.
+    <t>No standard manpower norm for processing tables.
 Occupancy varies randomly (under 2 or over 6 people per 8ft x 4ft table).
 No defined ratio of S&amp;G tables to packaging tables - S&amp;G tables are frequently fewer than packing tables, bottlenecking downstream packaging input.
 No cleaning step is enforced between vendors' S&amp;G batches, causing clutter and cross-contamination risk.</t>
   </si>
   <si>
-    <t xml:space="preserve">Norm defined (4 people per 8ft x 4ft table) but followed on under 40% of tables.
+    <t>Norm defined (4 people per 8ft x 4ft table) but followed on under 40% of tables.
 An S&amp;G-to-packing table ratio is loosely followed for under 40% of shifts, with S&amp;G output frequently under-matched to packing input.
 Inter-vendor cleaning is ad hoc.</t>
   </si>
   <si>
-    <t xml:space="preserve">4-person-per-table norm followed on 40-70% of tables.
+    <t>4-person-per-table norm followed on 40-70% of tables.
 S&amp;G-to-packing table ratio is matched to keep S&amp;G output aligned with packing input on 40-70% of shifts.
 Cleaning between vendors' S&amp;G batches is performed inconsistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">Norm followed on 70-95% of tables, monitored via regular floor walks.
+    <t>Norm followed on 70-95% of tables, monitored via regular floor walks.
 S&amp;G-to-packing table ratio and output-input matching is maintained on 70-95% of shifts, monitored via floor walks.
 Cleaning after each vendor's S&amp;G batch is standard practice.</t>
   </si>
   <si>
-    <t xml:space="preserve">Norm followed on over 95% of tables at all times, with real-time floor supervision preventing congestion or under-utilization.
+    <t>Norm followed on over 95% of tables at all times, with real-time floor supervision preventing congestion or under-utilization.
 S&amp;G-to-packing table ratio and output-input matching is maintained on over 95% of shifts with real-time supervision.
 Cleaning after every vendor's S&amp;G batch is enforced with zero cross-contamination incidents.</t>
   </si>
@@ -831,23 +845,23 @@
     <t>Shrinkage &amp; Seasonal Loss Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Shrinkage not tracked by SKU category.
+    <t>Shrinkage not tracked by SKU category.
 Overall loss exceeds 5% with no seasonal breakup.</t>
   </si>
   <si>
-    <t xml:space="preserve">Shrinkage tracked in aggregate only.
+    <t>Shrinkage tracked in aggregate only.
 No category-specific targets (e.g., leafy items vs vegetables like brinjal).</t>
   </si>
   <si>
-    <t xml:space="preserve">Shrinkage tracked by category against benchmark ranges (up to 30-35% for leafy items, 1-2% for vegetables like brinjal).
+    <t>Shrinkage tracked by category against benchmark ranges (up to 30-35% for leafy items, 1-2% for vegetables like brinjal).
 Seasonal RTV loss tracked at a 1.5-3% band (winter to monsoon).</t>
   </si>
   <si>
-    <t xml:space="preserve">Shrinkage within benchmark for over 80% of SKU categories.
+    <t>Shrinkage within benchmark for over 80% of SKU categories.
 Seasonal loss trend reviewed monthly with corrective action for outliers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Shrinkage consistently at or below benchmark for all categories.
+    <t>Shrinkage consistently at or below benchmark for all categories.
 Seasonal loss held at 1.5% or below even during monsoon.
 Monthly root-cause review with documented reduction actions.</t>
   </si>
@@ -858,26 +872,26 @@
     <t>Repacking Reduction Targets</t>
   </si>
   <si>
-    <t xml:space="preserve">Repacking/re-stickering rate not measured.
+    <t>Repacking/re-stickering rate not measured.
 Anecdotally exceeds 8% of units reworked.
 Cause coding does not distinguish avoidable rework such as re-sorting already vendor-packed bananas at the packing stage, ripeness-based segregation (e.g., mango, avocado) being performed late at the packing stage instead of at S&amp;G, or idle organic-table capacity - all of which inflate the repack rate.</t>
   </si>
   <si>
-    <t xml:space="preserve">Measured but no target set.
+    <t>Measured but no target set.
 Rate at 5-8%.
 Rate is measured in aggregate without cause coding for these specific drivers (banana re-sort, late ripeness segregation, idle organic-table capacity).</t>
   </si>
   <si>
-    <t xml:space="preserve">Target set at 5% or below.
+    <t>Target set at 5% or below.
 Actual performance running at 5-6%.
 Cause coding identifies banana re-sort, late ripeness segregation, and idle organic-table time as contributors, but corrective action (stopping banana re-sort, moving ripeness segregation to the S&amp;G stage, converting the organic table to multi-use) is applied inconsistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">Actual rate 2-5%, tracked weekly with cause coding.
+    <t>Actual rate 2-5%, tracked weekly with cause coding.
 Banana re-sort at packing is eliminated, ripeness-based segregation is performed at the S&amp;G stage, and the organic table is run as a time-clustered multi-use table on 70-95% of shifts, reflected in the weekly cause-coded repack trend.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rate under 2%, tracked daily, root cause eliminated at source (labeling/QC), sustained for 2+ consecutive quarters.
+    <t>Rate under 2%, tracked daily, root cause eliminated at source (labeling/QC), sustained for 2+ consecutive quarters.
 Banana re-sort at packing is fully eliminated, ripeness-based segregation is performed at the S&amp;G stage on 100% of shifts, and the organic table is consistently run as a multi-use table in downtime, sustained for 2+ consecutive quarters as a root-cause-eliminated driver of the sub-2% repack rate.</t>
   </si>
   <si>
@@ -914,32 +928,32 @@
     <t>Demand Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">0-1 of the 5 demand-planning layers (baseline/historical, seasonal &amp; festive, event-based/sales, time-of-day, area/hyperlocal behavior) in use.
+    <t>0-1 of the 5 demand-planning layers (baseline/historical, seasonal &amp; festive, event-based/sales, time-of-day, area/hyperlocal behavior) in use.
 Forecast accuracy under 60%.
 Hourly-volatility and SKU-level inaccuracy are not analyzed, and new-store locations run on no meaningful demand data (pure guesswork).</t>
   </si>
   <si>
-    <t xml:space="preserve">2 layers active.
+    <t>2 layers active.
 Forecast accuracy 60-75%.
 Hourly volatility and hyperlocal (area-level) variation are acknowledged but not modeled.
 New stores use a flat citywide/category average with no ramp-up curve.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 layers active (e.g., baseline + seasonal/festive + event-based).
+    <t>3 layers active (e.g., baseline + seasonal/festive + event-based).
 Forecast accuracy 75-85%.
 Time-of-day demand curves are tracked for under 50% of SKUs/stores.
 Hyperlocal (area-behavior) variation is factored in for high-volume stores only.
 New stores follow a defined but generic ramp-up curve.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 of the 5 layers active (typically missing time-of-day or area-behavior).
+    <t>4 of the 5 layers active (typically missing time-of-day or area-behavior).
 Forecast accuracy 85-95%.
 Time-of-day and hyperlocal demand patterns are modeled for 70-90% of stores.
 SKU-level forecast error is tracked and root-caused monthly.
 New-store data gaps are bridged with a comparable-store proxy model for the first 4-6 weeks.</t>
   </si>
   <si>
-    <t xml:space="preserve">All 5 layers active and continuously calibrated against actuals (baseline, seasonal/festive, event-based, time-of-day, hyperlocal/area-behavior).
+    <t>All 5 layers active and continuously calibrated against actuals (baseline, seasonal/festive, event-based, time-of-day, hyperlocal/area-behavior).
 Forecast accuracy above 95%, directly driving the fill-rate KPI.
 Hourly volatility and SKU-level accuracy are tracked in real time with automated recalibration.
 New-store demand gaps are closed within 2-4 weeks via a proxy-to-actual transition model.</t>
@@ -951,29 +965,29 @@
     <t>Inventory Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">0-1 of the 5 inventory-planning components (regular+buffer stock, seasonal buffer of +15-20%, festive buffer of +50-100%, FEFO discipline for fresh/perishable SKUs, SKU assortment) defined.
+    <t>0-1 of the 5 inventory-planning components (regular+buffer stock, seasonal buffer of +15-20%, festive buffer of +50-100%, FEFO discipline for fresh/perishable SKUs, SKU assortment) defined.
 Stockout/excess (waste) incidents affect over 20% of SKUs monthly.
 Batch/expiry tracking is manual or absent, and shelf-life-driven markdowns/write-offs are not visible until after the fact.</t>
   </si>
   <si>
-    <t xml:space="preserve">2 components defined.
+    <t>2 components defined.
 Incidents affect 10-20% of SKUs monthly.
 FEFO is followed inconsistently, with batch mismanagement (wrong batch picked/dispatched) as a regular occurrence.
 Inventory visibility lags actual stock by more than a day.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 components defined (e.g., regular+buffer stock, one of seasonal/festive buffer, and a defined SKU assortment).
+    <t>3 components defined (e.g., regular+buffer stock, one of seasonal/festive buffer, and a defined SKU assortment).
 Incidents affect 5-10% of SKUs monthly.
 FEFO is enforced for the majority of fresh SKUs.
 Batch-level visibility exists but is not real-time, creating an occasional stockout-vs-waste trade-off at the shelf-life boundary.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 of the 5 components defined and reviewed monthly (seasonal +15-20% and festive +50-100% buffers both applied, FEFO enforced for fresh).
+    <t>4 of the 5 components defined and reviewed monthly (seasonal +15-20% and festive +50-100% buffers both applied, FEFO enforced for fresh).
 Incidents affect under 5% of SKUs monthly.
 Batch/expiry data is visible near-real-time, keeping the stockout-vs-waste trade-off and batch mismanagement to isolated exceptions.</t>
   </si>
   <si>
-    <t xml:space="preserve">All 5 components defined, automated, and reviewed weekly (regular+buffer stock, seasonal +15-20% buffer, festive +50-100% buffer, FEFO for fresh, SKU assortment).
+    <t>All 5 components defined, automated, and reviewed weekly (regular+buffer stock, seasonal +15-20% buffer, festive +50-100% buffer, FEFO for fresh, SKU assortment).
 Incidents affect under 2% of SKUs monthly.
 Batch/expiry visibility is real-time and system-enforced, eliminating batch mismanagement and holding the stockout-vs-waste trade-off within a defined tolerance.</t>
   </si>
@@ -984,13 +998,13 @@
     <t>Replenishment Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">Replenishment triggered manually and irregularly.
+    <t>Replenishment triggered manually and irregularly.
 No defined formula (Forecast Demand + Safety Stock - Current Inventory) or wave structure.
 No min-max or reorder-point model is defined, no emergency top-up process exists for stockout risk, and days-of-inventory (DoI) is not tracked.
 Partial fulfillment, dock congestion at replenishment receipt, and storage overflow are common and unmanaged.</t>
   </si>
   <si>
-    <t xml:space="preserve">Formula-based replenishment defined but run less than once a day.
+    <t>Formula-based replenishment defined but run less than once a day.
 Wave split ad hoc.
 A min-max or reorder-point trigger is defined for under 30% of SKUs.
 Emergency top-up is handled ad hoc with no defined SLA.
@@ -998,7 +1012,7 @@
 Partial fulfillment and storage overflow incidents are frequent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Replenishment run once a day using the standard formula.
+    <t>Replenishment run once a day using the standard formula.
 Wave timing not optimized.
 Min-max/reorder-point triggers cover 30-60% of SKUs.
 A defined but manually-invoked emergency top-up process exists.
@@ -1006,14 +1020,14 @@
 Dock congestion from replenishment receipts is reviewed but not systematically avoided.</t>
   </si>
   <si>
-    <t xml:space="preserve">Replenishment run twice a day with a defined wave split (e.g., 70% first wave / 30% second wave).
+    <t>Replenishment run twice a day with a defined wave split (e.g., 70% first wave / 30% second wave).
 Lead time and buffer capacity factored in.
 Min-max/reorder-point triggers cover 60-90% of SKUs with an SLA-bound emergency top-up process.
 DoI is tracked by SKU against a target band.
 Dock-congestion and storage-overflow incidents from replenishment receipt are reduced to isolated exceptions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully automated twice-daily (or more frequent) replenishment cycle with an optimized wave split (e.g., 70/30), lead-time-adjusted safety stock, and under 2% stockout rate at dark stores.
+    <t>Fully automated twice-daily (or more frequent) replenishment cycle with an optimized wave split (e.g., 70/30), lead-time-adjusted safety stock, and under 2% stockout rate at dark stores.
 Min-max/reorder-point triggers cover over 90% of SKUs, integrated with an automated, SLA-bound emergency top-up process (ARS).
 DoI is tracked by SKU in real time against target bands.
 Dock congestion and storage overflow from replenishment receipts are eliminated through slotted receiving.
@@ -1026,13 +1040,13 @@
     <t>Manpower &amp; Capacity Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">0-2 of 6 roles (inbound, outbound/picking, packing, put-away, supervisory, security) have defined manpower planning.
+    <t>0-2 of 6 roles (inbound, outbound/picking, packing, put-away, supervisory, security) have defined manpower planning.
 Staffing variance exceeds 20%.
 No surge-planning mechanism for demand spikes and no defined gig-workforce flexibility strategy.
 Staffing decisions ignore diurnal (hour-of-day) demand variability, and attrition/gig-supply risk are not tracked.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 roles planned.
+    <t>3 roles planned.
 Staffing variance 15-20%.
 Surge planning is reactive (arranged only after a spike is already underway).
 Gig-workforce usage is ad hoc with no defined flex ratio.
@@ -1040,20 +1054,20 @@
 Attrition is tracked but not analyzed.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 roles planned.
+    <t>4 roles planned.
 Variance 10-15%.
 A surge-planning trigger and a defined gig-to-permanent flex ratio exist for under 60% of shifts.
 Shift design accounts for diurnal variability for the main peak window only.
 Attrition and gig-supply risk are tracked monthly without a mitigation plan.</t>
   </si>
   <si>
-    <t xml:space="preserve">5 roles planned with shift-level granularity.
+    <t>5 roles planned with shift-level granularity.
 Variance 5-10%.
 Surge planning and a defined gig-flex ratio are applied on 60-90% of shifts, with shift design built around the full diurnal demand curve.
 Attrition and gig-supply risk are tracked with an active mitigation/backup-pool plan.</t>
   </si>
   <si>
-    <t xml:space="preserve">All 6 roles planned with daily granularity and capacity buffers.
+    <t>All 6 roles planned with daily granularity and capacity buffers.
 Variance under 5%.
 Surge planning and gig-flex ratio are applied on over 90% of shifts with capacity buffers pre-built into the roster.
 Shift design is fully diurnal-curve-driven.
@@ -1066,7 +1080,7 @@
     <t>Network Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">Fewer than 1 planned warehouse-to-dark-store replenishment cycle per day.
+    <t>Fewer than 1 planned warehouse-to-dark-store replenishment cycle per day.
 Dispatch is ad hoc.
 No route optimization or truck-load optimization is applied (vehicles dispatched part-full or on unoptimized routes).
 No formal pick-path design exists, causing inefficient in-warehouse travel.
@@ -1074,7 +1088,7 @@
 Inbound to not-yet-live (pre-live) dark stores is unplanned and causes downstream issues.</t>
   </si>
   <si>
-    <t xml:space="preserve">1 cycle per day.
+    <t>1 cycle per day.
 Wave split not defined.
 Route/truck-load optimization is applied to under 30% of dispatch routes.
 Pick-path design is undefined, with operators walking ad hoc.
@@ -1082,14 +1096,14 @@
 Pre-live-store inward is handled the same as live-store inward with no distinction.</t>
   </si>
   <si>
-    <t xml:space="preserve">1-2 cycles per day with a defined split (approximately 70/30), but adherence under 70%.
+    <t>1-2 cycles per day with a defined split (approximately 70/30), but adherence under 70%.
 Route/truck-load optimization covers 30-60% of dispatch routes.
 A basic pick-path layout exists but is not distance-optimized.
 Freezer/cold-chain capacity is checked before dispatch for temperature-sensitive SKUs only.
 Pre-live dark-store inward follows a separate but informal process.</t>
   </si>
   <si>
-    <t xml:space="preserve">2 cycles per day with a 70/30 (or optimized) split.
+    <t>2 cycles per day with a 70/30 (or optimized) split.
 Adherence 70-90%.
 Route/truck-load optimization covers 60-90% of dispatch routes, holding OPH (orders-per-hour) close to target.
 Pick-path design is distance-optimized and reviewed periodically.
@@ -1097,7 +1111,7 @@
 Pre-live dark-store inward follows a defined, separate SOP.</t>
   </si>
   <si>
-    <t xml:space="preserve">2 or more cycles per day, wave-split adherence above 90%, dynamically adjusted to dark-store stock positions in real time.
+    <t>2 or more cycles per day, wave-split adherence above 90%, dynamically adjusted to dark-store stock positions in real time.
 Route/truck-load optimization covers over 90% of dispatch routes with OPH consistently at or above target.
 Pick-path design is continuously optimized using movement data.
 Freezer/cold-chain capacity is dynamically planned with zero temperature-zone breaches.
@@ -1110,19 +1124,19 @@
     <t>Planning Cycle &amp; Fill Rate Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill rate under 70%.
+    <t>Fill rate under 70%.
 No defined D-minus planning day.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill rate 70-80%.
+    <t>Fill rate 70-80%.
 D-minus planning cycle used inconsistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill rate 80-90%.
+    <t>Fill rate 80-90%.
 D-minus planning day formally defined and followed for FnV/dry categories.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill rate 90-95%.
+    <t>Fill rate 90-95%.
 D-minus cycle followed consistently, with variance root-caused monthly.</t>
   </si>
   <si>
@@ -1135,25 +1149,25 @@
     <t>Supplier Planning &amp; Risk Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplier performance (quality variability, lead-time risk, price volatility, OTIF - on-time-in-full) is not tracked in any structured way.
+    <t>Supplier performance (quality variability, lead-time risk, price volatility, OTIF - on-time-in-full) is not tracked in any structured way.
 Sourcing decisions are made without visibility into any of these four dimensions.
 OTIF is neither defined nor measured.</t>
   </si>
   <si>
-    <t xml:space="preserve">One of the four dimensions (typically OTIF or price) is tracked in aggregate, with no vendor-level or SKU-level breakdown.
+    <t>One of the four dimensions (typically OTIF or price) is tracked in aggregate, with no vendor-level or SKU-level breakdown.
 Quality variability and lead-time risk are known anecdotally but not measured.</t>
   </si>
   <si>
-    <t xml:space="preserve">2-3 of the four dimensions are tracked by vendor (e.g., OTIF % and lead-time variance), reviewed periodically (e.g., quarterly), but not yet linked to sourcing/allocation decisions.
+    <t>2-3 of the four dimensions are tracked by vendor (e.g., OTIF % and lead-time variance), reviewed periodically (e.g., quarterly), but not yet linked to sourcing/allocation decisions.
 Price volatility is monitored but not hedged or contracted against.</t>
   </si>
   <si>
-    <t xml:space="preserve">All four dimensions (quality variability, lead-time risk, price volatility, OTIF) are tracked by vendor and reviewed monthly, feeding a basic supplier scorecard.
+    <t>All four dimensions (quality variability, lead-time risk, price volatility, OTIF) are tracked by vendor and reviewed monthly, feeding a basic supplier scorecard.
 Sourcing allocation is adjusted for chronic OTIF/quality underperformers.
 Price volatility is partially managed via defined contracting/hedging for key SKUs.</t>
   </si>
   <si>
-    <t xml:space="preserve">All four dimensions are tracked by vendor and SKU in real time via an automated supplier scorecard, directly driving sourcing/allocation decisions and vendor tiering.
+    <t>All four dimensions are tracked by vendor and SKU in real time via an automated supplier scorecard, directly driving sourcing/allocation decisions and vendor tiering.
 OTIF is held above a defined benchmark (e.g., 95%+).
 Price volatility is actively hedged/contracted for the majority of high-value categories, with quarterly vendor business reviews closing the loop on quality and lead-time risk.</t>
   </si>
@@ -1389,11 +1403,11 @@
     <t>Throughput at 75-90% of benchmark (approximately 3-3.6 units/sq ft FnV, 17-20 units/sq ft dry).</t>
   </si>
   <si>
-    <t xml:space="preserve">Throughput at 90-100% of benchmark (4 units/sq ft FnV, 22.5-25 units/sq ft dry).
+    <t>Throughput at 90-100% of benchmark (4 units/sq ft FnV, 22.5-25 units/sq ft dry).
 Outbound dispatch capacity validated at approximately 4x warehouse area.</t>
   </si>
   <si>
-    <t xml:space="preserve">Throughput consistently at or above benchmark.
+    <t>Throughput consistently at or above benchmark.
 Dispatch capacity engineered and validated at exactly 4x warehouse area (e.g., a 50,000 sq ft facility supporting 200,000-unit dispatch capacity), reviewed quarterly.</t>
   </si>
   <si>
@@ -1403,19 +1417,19 @@
     <t>Warehouse Layout Design</t>
   </si>
   <si>
-    <t xml:space="preserve">Layout not benchmarked against SPR/MTR design standards.
+    <t>Layout not benchmarked against SPR/MTR design standards.
 Storage-area ratio undefined or deviates over 70% from the 50-60% norm.</t>
   </si>
   <si>
-    <t xml:space="preserve">Partial benchmarking.
+    <t>Partial benchmarking.
 Storage ratio in the 60-70% band (too high, indicating processing-area shortfall) or below 40%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Storage area at 50-60% of total footprint per design norm.
+    <t>Storage area at 50-60% of total footprint per design norm.
 Aisle widths (~10 ft) and beam lengths (~2.4m) mostly conform to standard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Full conformance to SPR/MTR specifications (aisle width, 100mm overhang, 3-4 ft sprinkler clearance) with storage ratio at 50-55%, or up to 60% for high-inventory/smaller-city sites.
+    <t>Full conformance to SPR/MTR specifications (aisle width, 100mm overhang, 3-4 ft sprinkler clearance) with storage ratio at 50-55%, or up to 60% for high-inventory/smaller-city sites.
 Density near 22.5 units/sq ft.</t>
   </si>
   <si>
@@ -1428,19 +1442,19 @@
     <t>Cost per Unit Tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">0-2 of the 6 cost components (manpower, material supply, packaging, electricity, depreciation, rent) tracked.
+    <t>0-2 of the 6 cost components (manpower, material supply, packaging, electricity, depreciation, rent) tracked.
 No periodic review.</t>
   </si>
   <si>
-    <t xml:space="preserve">3 components tracked.
+    <t>3 components tracked.
 Reviewed annually.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 components tracked.
+    <t>4 components tracked.
 Reviewed quarterly.</t>
   </si>
   <si>
-    <t xml:space="preserve">5 components tracked.
+    <t>5 components tracked.
 Reviewed monthly, feeding into cost-per-unit optimization actions.</t>
   </si>
   <si>
@@ -1453,27 +1467,27 @@
     <t>Project Planning &amp; Governance (Charter, Timeline, Cost Control)</t>
   </si>
   <si>
-    <t xml:space="preserve">No formal project charter, scope definition, or Gantt chart is used for planning/execution.
+    <t>No formal project charter, scope definition, or Gantt chart is used for planning/execution.
 Timelines and budgets are not documented.
 Delivery is tracked informally, with over 50% of projects (of any type - warehouse design/expansion, systems rollout, process change, etc.) running behind schedule or over budget with no visibility into the cause.</t>
   </si>
   <si>
-    <t xml:space="preserve">A basic project charter (scope/objective) is drafted for under 40% of projects.
+    <t>A basic project charter (scope/objective) is drafted for under 40% of projects.
 No Gantt chart or formal milestone timeline is maintained.
 Schedule or cost overrun exceeds 30% on the majority of tracked projects.</t>
   </si>
   <si>
-    <t xml:space="preserve">A project charter (scope, objective, stakeholders, budget) and a Gantt chart with defined milestones are used for 40-70% of projects.
+    <t>A project charter (scope, objective, stakeholders, budget) and a Gantt chart with defined milestones are used for 40-70% of projects.
 Milestone/timeline adherence is reviewed periodically (e.g., monthly), but cost tracking against budget is inconsistent.
 Schedule or cost overrun is in the 15-30% band.</t>
   </si>
   <si>
-    <t xml:space="preserve">A project charter and Gantt chart with milestone-level timelines are mandatory and used for 70-95% of projects.
+    <t>A project charter and Gantt chart with milestone-level timelines are mandatory and used for 70-95% of projects.
 Progress and cost are reviewed on a defined cadence (e.g., weekly) against the charter baseline.
 Schedule/cost overrun held under 15%, with variances root-caused.</t>
   </si>
   <si>
-    <t xml:space="preserve">Over 95% of projects (irrespective of type) are governed by a formal charter and Gantt chart with baselined milestones, tracked in real time against a defined ownership/RACI matrix.
+    <t>Over 95% of projects (irrespective of type) are governed by a formal charter and Gantt chart with baselined milestones, tracked in real time against a defined ownership/RACI matrix.
 Over 90% of projects are delivered on time and within the approved budget (schedule/cost overrun under 5%), with lessons-learned closed out post-project.</t>
   </si>
   <si>
@@ -1552,7 +1566,7 @@
     <t>Collection Center Setup &amp; Purpose</t>
   </si>
   <si>
-    <t xml:space="preserve">0% of inbound FnV volume routed through a collection center.
+    <t>0% of inbound FnV volume routed through a collection center.
 All sourcing goes direct to the main warehouse.</t>
   </si>
   <si>
@@ -1565,7 +1579,7 @@
     <t>50-80% of volume via a collection center, with a defined sorting/grading/packing split.</t>
   </si>
   <si>
-    <t xml:space="preserve">Over 80% of volume via a collection center.
+    <t>Over 80% of volume via a collection center.
 A fully optimized first-mile network measurably reducing cost-per-unit quarter-on-quarter.</t>
   </si>
   <si>
@@ -1575,18 +1589,18 @@
     <t>Collection Center Timing &amp; Dispatch Cutoffs</t>
   </si>
   <si>
-    <t xml:space="preserve">Under 50% of collection-center dispatches meet the 3:00 PM cutoff.
+    <t>Under 50% of collection-center dispatches meet the 3:00 PM cutoff.
 Frequent arrivals past 9:00 PM.</t>
   </si>
   <si>
     <t>50-70% adherence to the 3:00 PM dispatch / 9:00 PM arrival cutoffs.</t>
   </si>
   <si>
-    <t xml:space="preserve">70-85% adherence.
+    <t>70-85% adherence.
 Material typically arrives by 8-9 PM, packing completed by 11:30 PM.</t>
   </si>
   <si>
-    <t xml:space="preserve">85-95% adherence.
+    <t>85-95% adherence.
 Arrival consistently by 7-8 PM, enabling processing completion by 12:00 AM and FnV dispatch by 1:00 PM.</t>
   </si>
   <si>
@@ -1599,7 +1613,7 @@
     <t>Collection Center Processing Split</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined processing split between collection center and warehouse.
+    <t>No defined processing split between collection center and warehouse.
 Allocation decided ad hoc daily.</t>
   </si>
   <si>
@@ -1621,18 +1635,18 @@
     <t>Unloading Productivity Norms</t>
   </si>
   <si>
-    <t xml:space="preserve">Unloading productivity not benchmarked by load type (packed vs bulk).
+    <t>Unloading productivity not benchmarked by load type (packed vs bulk).
 No target set.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity tracked in aggregate only, below benchmark (under 400 units/person/hour packed.
+    <t>Productivity tracked in aggregate only, below benchmark (under 400 units/person/hour packed.
 Under 4 pallets/person/hour bulk).</t>
   </si>
   <si>
     <t>Productivity at benchmark for one load type only: 500 units/person/hour for packed material, or 5 pallets (125 crates)/person/hour for bulk - not both.</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity at benchmark for both load types (500 units/person/hour packed.
+    <t>Productivity at benchmark for both load types (500 units/person/hour packed.
 5 pallets or 125 crates/person/hour bulk), tracked daily.</t>
   </si>
   <si>
@@ -1651,32 +1665,32 @@
     <t>Staging &amp; Holding Zone Management</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined/target SLA for picking and allocation (benchmark: ~600 units/person/hour).
+    <t>No defined/target SLA for picking and allocation (benchmark: ~600 units/person/hour).
 No defined physical staging zones, leading to congestion.
 Allocation and holding material share the same physical zone with no clear demarcation.
 No structured stacking/arrangement method for crates.
 No defined dump/reject area within the staging zone.</t>
   </si>
   <si>
-    <t xml:space="preserve">Picking SLA is tracked for under 30% of shifts against the ~600 units/person/hour benchmark.
+    <t>Picking SLA is tracked for under 30% of shifts against the ~600 units/person/hour benchmark.
 Wave Staging, Holding, and Reject/Dump zones are informally identified but frequently overlap.
 Crate stacking in staging has no defined method.
 A dump/reject corner exists but has no clearance routine.</t>
   </si>
   <si>
-    <t xml:space="preserve">Picking SLA is tracked for 30-60% of shifts.
+    <t>Picking SLA is tracked for 30-60% of shifts.
 Wave Staging, Holding, and Reject/Dump zones are marked with reduced but still occasional overlap.
 A dump/reject corner has a clearance routine that is followed inconsistently.
 A maximum days-of-holding (DoH) target for held material is defined but not consistently tracked.</t>
   </si>
   <si>
-    <t xml:space="preserve">Picking SLA is tracked for 60-90% of shifts and mostly at benchmark.
+    <t>Picking SLA is tracked for 60-90% of shifts and mostly at benchmark.
 Wave Staging, Holding, and Reject/Dump zones are distinctly marked with no overlap on 70-95% of days.
 The dump/reject corner follows a timed clearance SOP.
 DoH SLA for holding material is tracked and mostly met.</t>
   </si>
   <si>
-    <t xml:space="preserve">Picking SLA is tracked for over 90% of shifts and consistently meets/exceeds the ~600 units/person/hour benchmark.
+    <t>Picking SLA is tracked for over 90% of shifts and consistently meets/exceeds the ~600 units/person/hour benchmark.
 Wave Staging, Holding, and Reject/Dump zones are distinctly marked with zero overlap.
 The dump/reject corner's timed clearance SOP is followed with zero aged-waste incidents.
 DoH SLA for holding material is met on over 95% of days, reviewed as part of routine floor governance.</t>
@@ -1688,23 +1702,23 @@
     <t>Dispatch &amp; Loading Operations</t>
   </si>
   <si>
-    <t xml:space="preserve">No defined SLA for dispatch/loading.
+    <t>No defined SLA for dispatch/loading.
 System allocation and physical allocation happen independently and out of sync, resulting in inventory mismatches at receiving hubs.</t>
   </si>
   <si>
-    <t xml:space="preserve">A loading SLA is defined (benchmark: ~2,500 units/person/hour) but tracked for under 30% of dispatches.
+    <t>A loading SLA is defined (benchmark: ~2,500 units/person/hour) but tracked for under 30% of dispatches.
 System and physical allocation are reconciled only after the fact, with inventory mismatches at hubs still common.</t>
   </si>
   <si>
-    <t xml:space="preserve">Loading SLA is tracked for 30-60% of dispatches against the ~2,500 units/person/hour benchmark.
+    <t>Loading SLA is tracked for 30-60% of dispatches against the ~2,500 units/person/hour benchmark.
 Scanner-based allocation is used for some dispatches, but system and physical completion are not always simultaneous, leaving residual hub-level mismatches.</t>
   </si>
   <si>
-    <t xml:space="preserve">Loading SLA is tracked for 60-90% of dispatches and mostly at benchmark.
+    <t>Loading SLA is tracked for 60-90% of dispatches and mostly at benchmark.
 Scanner-based allocation with simultaneous system and physical completion is standard for the majority of dispatches, reducing hub-level inventory mismatches to occasional exceptions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Loading SLA is tracked for over 90% of dispatches and consistently meets/exceeds the ~2,500 units/person/hour benchmark.
+    <t>Loading SLA is tracked for over 90% of dispatches and consistently meets/exceeds the ~2,500 units/person/hour benchmark.
 100% of allocations are scanner-based with simultaneous system and physical completion, eliminating hub-level inventory mismatches.
 Evaluated as a standing criterion in every facility diagnostic, not a one-off, site-specific observation.</t>
   </si>
@@ -1874,7 +1888,7 @@
     <t>Standardized</t>
   </si>
   <si>
-    <t xml:space="preserve">Deploy a digital appointment scheduler with defined slot windows.
+    <t>Deploy a digital appointment scheduler with defined slot windows.
  Mark and start enforcing a driver holding area away from the gate.
  Begin manually logging dock-in time.</t>
   </si>
@@ -1882,7 +1896,7 @@
     <t>Managed</t>
   </si>
   <si>
-    <t xml:space="preserve">Enforce system-generated slot windows with daily adherence tracking.
+    <t>Enforce system-generated slot windows with daily adherence tracking.
  Formalize and signpost the holding area.
  Start using dock-in time as the official SLA start-point for GRN TAT.
  Roll out QR/Booking-ID confirmations to the majority of vendors.</t>
@@ -1891,44 +1905,44 @@
     <t>Best-in-class</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate vendor slot notifications and load-spread balancing across shift hours.
+    <t>Automate vendor slot notifications and load-spread balancing across shift hours.
  Give the holding area real-time occupancy visibility.
  Make dock-in time system-captured with automated GRN-TAT breach alerts.
  Push QR/Booking-ID scanning above 90% of vendors with zero manual slot entries.</t>
   </si>
   <si>
-    <t xml:space="preserve">Introduce a single documentation checklist (vendor, invoice, indent qty) applied before unloading, even generic across vendor/courier.
+    <t>Introduce a single documentation checklist (vendor, invoice, indent qty) applied before unloading, even generic across vendor/courier.
  Start logging driver-ID and vehicle-number at the gate.</t>
   </si>
   <si>
-    <t xml:space="preserve">Split the checklist by vehicle type (vendor vs. courier).
+    <t>Split the checklist by vehicle type (vendor vs. courier).
  Check driver-ID/vehicle-number against the slot for a defined share of vehicles.
  Start temperature checks scoped specifically to 4°C SKUs (mushrooms etc.).</t>
   </si>
   <si>
-    <t xml:space="preserve">Introduce barcode/OCR-assisted matching to raise pre-unload verification coverage.
+    <t>Introduce barcode/OCR-assisted matching to raise pre-unload verification coverage.
  Apply the &gt;3°C-deviation temp-reject rule consistently for 4°C SKUs.
  Push driver-ID/vehicle authentication to the majority of vehicles.
  Log 100% of reefer vehicle temperatures.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully digitize gate verification end-to-end with an automated exception-flagging audit trail.
+    <t>Fully digitize gate verification end-to-end with an automated exception-flagging audit trail.
  Extend driver-ID/vehicle authentication and the temp-reject rule to over 90% of vehicles with zero exceptions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Start rolling out biometric/facial-recognition coverage at main shift changeovers.
+    <t>Start rolling out biometric/facial-recognition coverage at main shift changeovers.
  Begin ad hoc zone-wise entry counts for at least the highest-risk zones (S&amp;G, packing).</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend facial-recognition coverage to the main changeover shifts.
+    <t>Extend facial-recognition coverage to the main changeover shifts.
  Define a warehouse-sizing-based headcount norm per zone and track actuals against it periodically.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend biometric coverage to all shifts and gates.
+    <t>Extend biometric coverage to all shifts and gates.
  Integrate zone-wise entry capture with the attendance system and reconcile daily against the sizing-based plan.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push to 100% biometric plus physical-check coverage across all shifts/gates.
+    <t>Push to 100% biometric plus physical-check coverage across all shifts/gates.
  Move zone-wise capture to real time with automated variance alerts against the sizing-based headcount plan.</t>
   </si>
   <si>
@@ -1938,88 +1952,88 @@
     <t>Define dock allocation rules by vehicle size and start enforcing FIFO sequencing at the dock.</t>
   </si>
   <si>
-    <t xml:space="preserve">Move to system-based dock scheduling with size-matched allocation.
+    <t>Move to system-based dock scheduling with size-matched allocation.
  Push FIFO adherence above 90% and guarantee green-channel vehicles unload within 15 minutes.</t>
   </si>
   <si>
     <t>Automate dock-vehicle matching with real-time queuing to push utilization above 90%, FIFO adherence to 100%, and green-channel wait time under 10 minutes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fit buffers on at least a quarter of docks, prioritizing the highest-traffic ones.
+    <t>Fit buffers on at least a quarter of docks, prioritizing the highest-traffic ones.
  Start logging dock-damage incidents (even informally) as they happen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Expand buffer coverage toward the halfway mark.
+    <t>Expand buffer coverage toward the halfway mark.
  Introduce a formal, if basic, penalty (warning/fine) for a driver's repeat dock-damage incident.
  Begin monthly physical dock-structure inspections logged separately from buffer damage.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push buffer coverage into the 75-95% range.
+    <t>Push buffer coverage into the 75-95% range.
  Formalize a graded penalty scale (warning to fine to vendor/transporter review) for repeat offenders.
  Move dock-structure inspection to weekly with defects tracked to closure.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete buffer coverage to 100%.
+    <t>Complete buffer coverage to 100%.
  Enforce the graded penalty scale strictly to hold repeat-offense rate under 2%.
  Run a preventive maintenance schedule and verify zero unresolved structural damage via weekly inspection.</t>
   </si>
   <si>
-    <t xml:space="preserve">Define a target unloading SLA (~500 units/person/hour for pre-packed material) and start marking a palletisation zone, even loosely.
+    <t>Define a target unloading SLA (~500 units/person/hour for pre-packed material) and start marking a palletisation zone, even loosely.
  Introduce an informal pre-packed bypass flag for known vendors.</t>
   </si>
   <si>
-    <t xml:space="preserve">Assign dock-wise supervisor-led unloading teams.
+    <t>Assign dock-wise supervisor-led unloading teams.
  Enforce the crate-stacking SOP and keep the palletisation/S&amp;G zones marked.
  Relocate waste disposal away from the inbound gate.
  Extend the bypass flag to 30-60% of eligible pre-packed loads.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push supervisor-led teams to every shift.
+    <t>Push supervisor-led teams to every shift.
  Mark FIFO lanes for S&amp;G and a separate dry-category lane.
  Raise crate-stacking SOP compliance and bypass-flag usage into the 60-90% range.</t>
   </si>
   <si>
-    <t xml:space="preserve">Drive unloading SLA, crate-stacking, and bypass-flag compliance above 90% with zero space-constraint or cross-flow incidents.
+    <t>Drive unloading SLA, crate-stacking, and bypass-flag compliance above 90% with zero space-constraint or cross-flow incidents.
  Fully integrate the bypass flag into the load-declaration/GRN step.</t>
   </si>
   <si>
-    <t xml:space="preserve">Start piloting digital weighment integration with the WMS/GRN system on a subset of lanes.
+    <t>Start piloting digital weighment integration with the WMS/GRN system on a subset of lanes.
  Establish a minimum 1.5m clear aisle between weighment and staging.
  Put scale calibration on a defined (even if not daily) schedule.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend digital weighment integration to 30-60% of transactions.
+    <t>Extend digital weighment integration to 30-60% of transactions.
  Begin shifting weighment to the unloading stage (ahead of S&amp;G) for some vendor categories to cut PO-closure delay.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push digital weighment coverage to 60-90%.
+    <t>Push digital weighment coverage to 60-90%.
  Make weighment-at-unloading-stage the default for the majority of vendors.
  Move scale recalibration to daily with tare memory per packaging type.
  Retain digital weight logs as an audit trail.</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete digital weighment integration above 90% with zero manual entry.
+    <t>Complete digital weighment integration above 90% with zero manual entry.
  Make same-day PO closure the norm.
  Use the digital weight log routinely for supplier invoice reconciliation and shrinkage analysis.</t>
   </si>
   <si>
-    <t xml:space="preserve">Introduce an informal capacity check (even a phone call to the dock supervisor) before releasing any vehicle.
+    <t>Introduce an informal capacity check (even a phone call to the dock supervisor) before releasing any vehicle.
  Designate (even if unenforced) a waiting/parking zone for held vehicles.
  Start issuing an exit slip on gate-out.</t>
   </si>
   <si>
-    <t xml:space="preserve">Define a formal capacity check with a stated time window (e.g., 15 minutes for dock bay plus staging space) and route 'no' decisions to the holding area.
+    <t>Define a formal capacity check with a stated time window (e.g., 15 minutes for dock bay plus staging space) and route 'no' decisions to the holding area.
  Introduce a basic reject-vs-hold rule.
  Make exit-slip issuance standard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend capacity-gated release to the majority of gate-ins.
+    <t>Extend capacity-gated release to the majority of gate-ins.
  Formalize the full reject/temp-reject/hold/bypass decision taxonomy.
  Add outbound-seal verification to gate-out.
  Install physical enablers (multi-lane entry, boom barrier, CCTV/tablet).</t>
   </si>
   <si>
-    <t xml:space="preserve">Push capacity-gated release above 90% in real time, tied live to the dock-management and staging systems.
+    <t>Push capacity-gated release above 90% in real time, tied live to the dock-management and staging systems.
  Apply the full decision taxonomy with a complete audit trail.
  Make gate-out fully controlled (exit slip plus seal verification on 100% of dispatches).
  Add a weighbridge where applicable.</t>
@@ -2073,21 +2087,21 @@
     <t>Complete all 9 elements, version-control them, and link them to a closed-loop CAPA process with under 5-day average closure time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Define a sampling percentage and a written AQR format, even if not yet consistently applied.
+    <t>Define a sampling percentage and a written AQR format, even if not yet consistently applied.
  Require quality-team sign-off before GRN posting (even if it currently happens late).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fix sampling at ~10% with a 20% defect-rejection threshold.
+    <t>Fix sampling at ~10% with a 20% defect-rejection threshold.
  Make GRN approval procedurally dependent on quality clearance (even if still manual/paper-based).
  Apply the AQR before unloading for the majority of lots.</t>
   </si>
   <si>
-    <t xml:space="preserve">Segment sampling/rejection by category (FnV vs. dry) with batch/expiry and shelf-life checks.
+    <t>Segment sampling/rejection by category (FnV vs. dry) with batch/expiry and shelf-life checks.
  Make GRN posting a hard system hold pending quality clearance.
  Start tracking QC/vehicle rejection by vendor and SKU into a periodic supplier scorecard.</t>
   </si>
   <si>
-    <t xml:space="preserve">Digitize sampling/rejection norms per SKU category with under 2% inspection error.
+    <t>Digitize sampling/rejection norms per SKU category with under 2% inspection error.
  Make GRN release fully system-enforced with zero exceptions and a full sign-off audit trail.
  Run the AQR and supplier scorecard in real time, feeding vendor reviews.</t>
   </si>
@@ -2110,7 +2124,7 @@
     <t>Categorize complaints monthly and benchmark PPM against the industry band.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add root-cause analysis with a 7-day corrective-action closure target.
+    <t>Add root-cause analysis with a 7-day corrective-action closure target.
  Track PPM weekly against a defined benchmark.</t>
   </si>
   <si>
@@ -2144,30 +2158,30 @@
     <t>Run a 5S pilot in one area and start basic floor demarcation there (aisles, storage) to lift the audit score above 40%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend Sort/Set/Shine facility-wide with quarterly audits.
+    <t>Extend Sort/Set/Shine facility-wide with quarterly audits.
  Expand demarcation to include S&amp;G/packing space and storage marking.</t>
   </si>
   <si>
-    <t xml:space="preserve">Standardize 5S across all zones with monthly audits and biannual training.
+    <t>Standardize 5S across all zones with monthly audits and biannual training.
  Extend demarcation to buffer-pallet staging and packaging-material storage.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sustain 5S with daily checks and a documented Kaizen count.
+    <t>Sustain 5S with daily checks and a documented Kaizen count.
  Complete 100% zone demarcation (including tools/machinery) with colour-coding, auditing demarcation adherence as part of the daily check.</t>
   </si>
   <si>
     <t>Deploy a second lean principle (e.g., start value-stream mapping) and introduce PDCA on at least a few processes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deploy a third principle and embed PDCA in 20-50% of processes.
+    <t>Deploy a third principle and embed PDCA in 20-50% of processes.
  Start tracking 2-3 of the 8 waste types.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add pull/JIT replenishment as a fourth principle.
+    <t>Add pull/JIT replenishment as a fourth principle.
  Push PDCA to 50-80% of processes and track 5-6 waste types with quarterly reduction targets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully embed all 5 lean principles with PDCA in over 80% of processes.
+    <t>Fully embed all 5 lean principles with PDCA in over 80% of processes.
  Track all 8 waste types with measurable year-on-year reduction above 10%.</t>
   </si>
   <si>
@@ -2186,11 +2200,11 @@
     <t>Define size/quality standards and a throughput SLA (~70 units/person/hour) for the first 30% of SKUs/stations, even if compliance is uneven.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend standards and throughput-SLA tracking to 30-60% of SKUs/stations.
+    <t>Extend standards and throughput-SLA tracking to 30-60% of SKUs/stations.
  Start assigning experienced manpower to piece-category SKUs, even if inconsistently.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extend to 60-90% of SKUs/stations with monthly grading-accuracy audits above 90%.
+    <t>Extend to 60-90% of SKUs/stations with monthly grading-accuracy audits above 90%.
  Make experienced-manpower assignment for piece-category SKUs consistent.</t>
   </si>
   <si>
@@ -2200,41 +2214,41 @@
     <t>Define packaging material by SKU for the first half of SKUs and start tracking a shift-level SLA on a subset of lines.</t>
   </si>
   <si>
-    <t xml:space="preserve">Define packaging material for all SKUs.
+    <t>Define packaging material for all SKUs.
  Introduce a formed-box staging shelf and begin aligning some vendors to FC pack standards to remove re-packing.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push productivity toward the 100-120 units/person/hour band with daily gang-output tracking.
+    <t>Push productivity toward the 100-120 units/person/hour band with daily gang-output tracking.
  Extend FC-standard vendor alignment and dedicated chilled packing to 60-90% of applicable lines/shifts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sustain productivity above 120 units/person/hour.
+    <t>Sustain productivity above 120 units/person/hour.
  Eliminate the re-pack sub-process for over 90% of applicable vendors and route 100% of chilled SKUs through a dedicated chilled station, tracked and improved monthly.</t>
   </si>
   <si>
     <t>Set the 4-person-per-table norm and start applying an S&amp;G-to-packing table ratio, even if compliance is under 40%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push table-norm and ratio compliance into the 40-70% range.
+    <t>Push table-norm and ratio compliance into the 40-70% range.
  Begin an inter-vendor cleaning step, even if inconsistent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitor table norm and ratio adherence via regular floor walks to reach 70-95%.
+    <t>Monitor table norm and ratio adherence via regular floor walks to reach 70-95%.
  Make inter-vendor cleaning standard practice.</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintain over 95% adherence with real-time floor supervision.
+    <t>Maintain over 95% adherence with real-time floor supervision.
  Enforce inter-vendor cleaning with zero cross-contamination incidents.</t>
   </si>
   <si>
     <t>Start tracking shrinkage in aggregate (even without category splits) to establish a baseline against the 5% ceiling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Split shrinkage tracking by SKU category against benchmark ranges.
+    <t>Split shrinkage tracking by SKU category against benchmark ranges.
  Start tracking seasonal RTV loss by season.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push category-level shrinkage within benchmark for over 80% of categories.
+    <t>Push category-level shrinkage within benchmark for over 80% of categories.
  Review the seasonal-loss trend monthly with corrective action for outliers.</t>
   </si>
   <si>
@@ -2268,16 +2282,16 @@
     <t>Add a second forecasting layer (e.g., seasonal on top of baseline) to lift forecast accuracy above 60%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add a third layer (event-based) and start tracking time-of-day demand curves for at least half of SKUs/stores.
+    <t>Add a third layer (event-based) and start tracking time-of-day demand curves for at least half of SKUs/stores.
  Give new stores a defined generic ramp-up curve instead of guesswork.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the fourth layer (typically time-of-day or hyperlocal) and extend it to 70-90% of stores.
+    <t>Add the fourth layer (typically time-of-day or hyperlocal) and extend it to 70-90% of stores.
  Root-cause SKU-level forecast error monthly.
  Bridge new-store gaps with a comparable-store proxy model.</t>
   </si>
   <si>
-    <t xml:space="preserve">Activate and continuously calibrate all 5 layers against actuals.
+    <t>Activate and continuously calibrate all 5 layers against actuals.
  Automate recalibration for hourly volatility and SKU-level accuracy.
  Cut the new-store proxy-to-actual transition to 2-4 weeks.</t>
   </si>
@@ -2294,21 +2308,21 @@
     <t>Automate all 5 components with weekly review and real-time, system-enforced batch/expiry visibility to hold incidents under 2% of SKUs monthly.</t>
   </si>
   <si>
-    <t xml:space="preserve">Define the replenishment formula (Forecast Demand + Safety Stock - Current Inventory) and run it at least once a day.
+    <t>Define the replenishment formula (Forecast Demand + Safety Stock - Current Inventory) and run it at least once a day.
  Introduce a basic reorder-point trigger for a subset of SKUs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Run replenishment daily on the standard formula.
+    <t>Run replenishment daily on the standard formula.
  Extend the reorder-point trigger to 30-60% of SKUs with a manually-invoked emergency top-up process.
  Start tracking DoI by category.</t>
   </si>
   <si>
-    <t xml:space="preserve">Move to twice-daily replenishment with a defined wave split and lead-time/buffer-capacity factored in.
+    <t>Move to twice-daily replenishment with a defined wave split and lead-time/buffer-capacity factored in.
  Extend reorder-point coverage to 60-90% of SKUs with an SLA-bound emergency top-up.
  Track DoI by SKU against a target band.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully automate the twice-daily-plus cycle with an optimized wave split and lead-time-adjusted safety stock.
+    <t>Fully automate the twice-daily-plus cycle with an optimized wave split and lead-time-adjusted safety stock.
  Extend reorder-point/ARS coverage above 90%.
  Eliminate replenishment-receipt dock congestion and storage overflow via slotted receiving.</t>
   </si>
@@ -2316,33 +2330,33 @@
     <t>Extend defined manpower planning to a third role and start tracking (even without acting on) attrition.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover a fourth role.
+    <t>Cover a fourth role.
  Introduce a surge-planning trigger and a gig-flex ratio for at least some shifts, even if reactive.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover a fifth role with shift-level granularity.
+    <t>Cover a fifth role with shift-level granularity.
  Build shift design around the full diurnal demand curve and put an active attrition/gig-supply mitigation plan in place.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover all 6 roles with daily granularity and pre-built capacity buffers.
+    <t>Cover all 6 roles with daily granularity and pre-built capacity buffers.
  Make surge planning and gig-flex proactive on over 90% of shifts, with attrition and gig-supply risk mitigated via a pre-qualified backup pool.</t>
   </si>
   <si>
-    <t xml:space="preserve">Move to at least 1 planned warehouse-to-dark-store cycle per day (from ad hoc dispatch).
+    <t>Move to at least 1 planned warehouse-to-dark-store cycle per day (from ad hoc dispatch).
  Start applying route/truck-load optimization to at least some routes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Run 1-2 cycles per day with a defined (e.g., 70/30) wave split.
+    <t>Run 1-2 cycles per day with a defined (e.g., 70/30) wave split.
  Extend route/truck-load optimization to 30-60% of routes.
  Check freezer/cold-chain capacity before dispatch for temperature-sensitive SKUs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Push to 2 cycles per day with 70-90% wave-split adherence.
+    <t>Push to 2 cycles per day with 70-90% wave-split adherence.
  Extend route optimization to 60-90% of routes.
  Give pre-live dark stores a defined, separate inward SOP.</t>
   </si>
   <si>
-    <t xml:space="preserve">Run 2+ cycles per day with wave-split adherence above 90%, dynamically adjusted to dark-store stock in real time.
+    <t>Run 2+ cycles per day with wave-split adherence above 90%, dynamically adjusted to dark-store stock in real time.
  Extend route optimization above 90% with OPH at/above target.
  Plan freezer capacity dynamically with zero breaches.</t>
   </si>
@@ -2365,11 +2379,11 @@
     <t>Track 2-3 dimensions by vendor on a periodic (e.g., quarterly) cadence, even without linking to sourcing decisions yet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Track all four dimensions by vendor monthly, feeding a basic scorecard.
+    <t>Track all four dimensions by vendor monthly, feeding a basic scorecard.
  Start adjusting sourcing allocation for chronic underperformers and defining contracting/hedging for key SKUs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Move to real-time, vendor-and-SKU-level tracking via an automated scorecard driving sourcing/tiering decisions.
+    <t>Move to real-time, vendor-and-SKU-level tracking via an automated scorecard driving sourcing/tiering decisions.
  Hold OTIF above 95% and hedge/contract price volatility for the majority of high-value categories.</t>
   </si>
   <si>
@@ -2520,15 +2534,15 @@
     <t>Introduce a basic project charter (scope/objective) for the next project, even without a Gantt chart yet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add a Gantt chart with milestones and a defined budget to the charter.
+    <t>Add a Gantt chart with milestones and a defined budget to the charter.
  Review milestone/timeline adherence monthly.</t>
   </si>
   <si>
-    <t xml:space="preserve">Make the charter and Gantt chart mandatory for all projects.
+    <t>Make the charter and Gantt chart mandatory for all projects.
  Review progress and cost weekly against the baseline, root-causing variances.</t>
   </si>
   <si>
-    <t xml:space="preserve">Track projects in real time against a defined ownership/RACI matrix.
+    <t>Track projects in real time against a defined ownership/RACI matrix.
  Close out lessons-learned post-project to sustain over 90% on-time, in-budget delivery.</t>
   </si>
   <si>
@@ -2613,15 +2627,15 @@
     <t>Mark rough Wave Staging, Holding, and Reject/Dump zones (even with overlap) and start tracking picking SLA against the 600 units/person/hour benchmark for at least some shifts.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduce zone overlap and introduce a (even inconsistent) clearance routine for the dump/reject corner.
+    <t>Reduce zone overlap and introduce a (even inconsistent) clearance routine for the dump/reject corner.
  Define a maximum DoH target for held material.</t>
   </si>
   <si>
-    <t xml:space="preserve">Eliminate zone overlap on 70-95% of days with a timed clearance SOP for the dump/reject corner.
+    <t>Eliminate zone overlap on 70-95% of days with a timed clearance SOP for the dump/reject corner.
  Track and mostly meet the DoH SLA.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sustain zero zone overlap and a fully followed clearance SOP with zero aged-waste incidents.
+    <t>Sustain zero zone overlap and a fully followed clearance SOP with zero aged-waste incidents.
  Meet the DoH SLA on over 95% of days as part of routine floor governance.</t>
   </si>
   <si>
@@ -2733,36 +2747,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <charset val="1"/>
-      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <charset val="1"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3016,9 +3032,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.6328125" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="1" customWidth="1"/>
@@ -3031,10 +3047,11 @@
     <col min="9" max="13" width="42" style="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.6328125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3081,7 +3098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -3106,7 +3123,7 @@
       </c>
       <c r="H2" s="7">
         <f t="shared" ref="H2:H12" si="1">1/11</f>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>21</v>
@@ -3130,7 +3147,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
@@ -3155,7 +3172,7 @@
       </c>
       <c r="H3" s="7">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>29</v>
@@ -3179,7 +3196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
@@ -3204,7 +3221,7 @@
       </c>
       <c r="H4" s="7">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>36</v>
@@ -3228,7 +3245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -3253,7 +3270,7 @@
       </c>
       <c r="H5" s="7">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>43</v>
@@ -3277,7 +3294,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" ht="87.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="87.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -3302,7 +3319,7 @@
       </c>
       <c r="H6" s="7">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>50</v>
@@ -3326,7 +3343,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="217.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3351,7 +3368,7 @@
       </c>
       <c r="H7" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>57</v>
@@ -3375,7 +3392,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="145" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -3400,7 +3417,7 @@
       </c>
       <c r="H8" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>64</v>
@@ -3424,7 +3441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="174" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="174" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -3449,7 +3466,7 @@
       </c>
       <c r="H9" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>71</v>
@@ -3473,7 +3490,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -3498,7 +3515,7 @@
       </c>
       <c r="H10" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>78</v>
@@ -3522,7 +3539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -3547,7 +3564,7 @@
       </c>
       <c r="H11" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>85</v>
@@ -3571,7 +3588,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" ht="72.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="72.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -3596,7 +3613,7 @@
       </c>
       <c r="H12" s="2">
         <f t="shared" si="1"/>
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>92</v>
@@ -3620,7 +3637,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="62.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -3669,7 +3686,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="162.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="162.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
@@ -3718,7 +3735,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
@@ -3767,7 +3784,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" ht="87.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="87.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
@@ -3816,7 +3833,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3865,7 +3882,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -3914,7 +3931,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>15</v>
       </c>
@@ -3939,7 +3956,7 @@
       </c>
       <c r="H19" s="7">
         <f>1/3</f>
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>145</v>
@@ -3963,7 +3980,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>15</v>
       </c>
@@ -3988,7 +4005,7 @@
       </c>
       <c r="H20" s="7">
         <f>1/3</f>
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>152</v>
@@ -4012,7 +4029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
@@ -4037,7 +4054,7 @@
       </c>
       <c r="H21" s="7">
         <f>1/3</f>
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>159</v>
@@ -4061,7 +4078,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
@@ -4110,7 +4127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" ht="137.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="137.55000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
@@ -4159,7 +4176,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>15</v>
       </c>
@@ -4208,7 +4225,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
@@ -4257,7 +4274,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>15</v>
       </c>
@@ -4306,7 +4323,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
@@ -4355,7 +4372,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>15</v>
       </c>
@@ -4380,7 +4397,7 @@
       </c>
       <c r="H28" s="7">
         <f t="shared" ref="H28:H44" si="4">1/17</f>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>212</v>
@@ -4404,7 +4421,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>15</v>
       </c>
@@ -4429,7 +4446,7 @@
       </c>
       <c r="H29" s="7">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>219</v>
@@ -4453,7 +4470,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" ht="112.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>15</v>
       </c>
@@ -4478,7 +4495,7 @@
       </c>
       <c r="H30" s="7">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>226</v>
@@ -4502,7 +4519,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="150" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>15</v>
       </c>
@@ -4527,7 +4544,7 @@
       </c>
       <c r="H31" s="7">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>233</v>
@@ -4551,7 +4568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" ht="100" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>15</v>
       </c>
@@ -4576,7 +4593,7 @@
       </c>
       <c r="H32" s="7">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>240</v>
@@ -4600,7 +4617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" ht="137.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="137.55000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>15</v>
       </c>
@@ -4625,7 +4642,7 @@
       </c>
       <c r="H33" s="7">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>247</v>
@@ -4649,7 +4666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -4674,7 +4691,7 @@
       </c>
       <c r="H34" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>254</v>
@@ -4698,7 +4715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="130.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>15</v>
       </c>
@@ -4723,7 +4740,7 @@
       </c>
       <c r="H35" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>261</v>
@@ -4747,7 +4764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>15</v>
       </c>
@@ -4772,7 +4789,7 @@
       </c>
       <c r="H36" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>268</v>
@@ -4796,7 +4813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>15</v>
       </c>
@@ -4821,7 +4838,7 @@
       </c>
       <c r="H37" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>275</v>
@@ -4845,7 +4862,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -4870,7 +4887,7 @@
       </c>
       <c r="H38" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>282</v>
@@ -4894,7 +4911,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>15</v>
       </c>
@@ -4919,7 +4936,7 @@
       </c>
       <c r="H39" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>289</v>
@@ -4943,7 +4960,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -4968,7 +4985,7 @@
       </c>
       <c r="H40" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>296</v>
@@ -4992,7 +5009,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
@@ -5017,7 +5034,7 @@
       </c>
       <c r="H41" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>303</v>
@@ -5041,7 +5058,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -5066,7 +5083,7 @@
       </c>
       <c r="H42" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>310</v>
@@ -5090,7 +5107,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
@@ -5115,7 +5132,7 @@
       </c>
       <c r="H43" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>317</v>
@@ -5139,7 +5156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -5164,7 +5181,7 @@
       </c>
       <c r="H44" s="2">
         <f t="shared" si="4"/>
-        <v>0.058823529411764705</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>324</v>
@@ -5188,7 +5205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>15</v>
       </c>
@@ -5237,7 +5254,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="62.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>15</v>
       </c>
@@ -5286,7 +5303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" ht="62.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="62.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>15</v>
       </c>
@@ -5335,7 +5352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
@@ -5384,7 +5401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" ht="116" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
@@ -5433,7 +5450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -5482,7 +5499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" ht="58" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
@@ -5531,7 +5548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>15</v>
       </c>
@@ -5580,7 +5597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>15</v>
       </c>
@@ -5629,7 +5646,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>15</v>
       </c>
@@ -5678,7 +5695,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" ht="37.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>15</v>
       </c>
@@ -5727,7 +5744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" ht="50" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>15</v>
       </c>
@@ -5776,7 +5793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" ht="130.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -5825,7 +5842,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" ht="116" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>15</v>
       </c>
@@ -5874,7 +5891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>15</v>
       </c>
@@ -5923,7 +5940,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>15</v>
       </c>
@@ -5972,7 +5989,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" ht="43.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>15</v>
       </c>
@@ -6021,7 +6038,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
@@ -6070,7 +6087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>15</v>
       </c>
@@ -6119,7 +6136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" ht="29" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -6168,17 +6185,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" ht="29" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="28.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F253"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6188,7 +6205,7 @@
     <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6208,7 +6225,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -6228,7 +6245,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="3" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6248,7 +6265,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -6268,7 +6285,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -6288,7 +6305,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="6" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -6308,7 +6325,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="7" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -6328,7 +6345,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -6348,7 +6365,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="9" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -6368,7 +6385,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="10" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -6388,7 +6405,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="11" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -6408,7 +6425,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="12" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6428,7 +6445,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -6448,7 +6465,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="14" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -6468,7 +6485,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -6488,7 +6505,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="16" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6508,7 +6525,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="17" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -6528,7 +6545,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -6548,7 +6565,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="19" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -6568,7 +6585,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="20" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -6588,7 +6605,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -6608,7 +6625,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -6628,7 +6645,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -6648,7 +6665,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="24" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -6668,7 +6685,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="25" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -6688,7 +6705,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="26" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -6708,7 +6725,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="27" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -6728,7 +6745,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -6748,7 +6765,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="29" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -6768,7 +6785,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="30" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -6788,7 +6805,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="31" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -6808,7 +6825,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="32" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -6828,7 +6845,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="33" ht="72.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="72.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -6848,7 +6865,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="34" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -6868,7 +6885,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -6888,7 +6905,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="36" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -6908,7 +6925,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -6928,7 +6945,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="38" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -6948,7 +6965,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -6968,7 +6985,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -6988,7 +7005,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="41" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -7008,7 +7025,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -7028,7 +7045,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -7048,7 +7065,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -7068,7 +7085,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="45" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -7088,7 +7105,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -7108,7 +7125,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="47" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -7128,7 +7145,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -7148,7 +7165,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="49" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -7168,7 +7185,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="50" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -7188,7 +7205,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="51" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -7208,7 +7225,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="52" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -7228,7 +7245,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="53" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -7248,7 +7265,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -7268,7 +7285,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="55" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -7288,7 +7305,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="56" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -7308,7 +7325,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="57" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -7328,7 +7345,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="58" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -7348,7 +7365,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -7368,7 +7385,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="60" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -7388,7 +7405,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="61" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -7408,7 +7425,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -7428,7 +7445,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="63" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -7448,7 +7465,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -7468,7 +7485,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="65" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -7488,7 +7505,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="66" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -7508,7 +7525,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -7528,7 +7545,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -7548,7 +7565,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="69" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -7568,7 +7585,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="70" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -7588,7 +7605,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="71" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -7608,7 +7625,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="72" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -7628,7 +7645,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="73" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -7648,7 +7665,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="74" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -7668,7 +7685,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="75" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -7688,7 +7705,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="76" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -7708,7 +7725,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="77" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -7728,7 +7745,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -7748,7 +7765,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -7768,7 +7785,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -7788,7 +7805,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="81" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -7808,7 +7825,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="82" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -7828,7 +7845,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="83" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -7848,7 +7865,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="84" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -7868,7 +7885,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="85" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -7888,7 +7905,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="86" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -7908,7 +7925,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="87" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -7928,7 +7945,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="88" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -7948,7 +7965,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="89" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -7968,7 +7985,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="90" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -7988,7 +8005,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="91" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -8008,7 +8025,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="92" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -8028,7 +8045,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="93" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -8048,7 +8065,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="94" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -8068,7 +8085,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -8088,7 +8105,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="96" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -8108,7 +8125,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="97" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -8128,7 +8145,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="98" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -8148,7 +8165,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="99" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -8168,7 +8185,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="100" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -8188,7 +8205,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="101" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -8208,7 +8225,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="102" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -8228,7 +8245,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -8248,7 +8265,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>15</v>
       </c>
@@ -8268,7 +8285,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -8288,7 +8305,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -8308,7 +8325,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="107" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -8328,7 +8345,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="108" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -8348,7 +8365,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="109" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>15</v>
       </c>
@@ -8368,7 +8385,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>15</v>
       </c>
@@ -8388,7 +8405,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="111" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>15</v>
       </c>
@@ -8408,7 +8425,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="112" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -8428,7 +8445,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="113" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -8448,7 +8465,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="114" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -8468,7 +8485,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="115" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>15</v>
       </c>
@@ -8488,7 +8505,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="116" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -8508,7 +8525,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="117" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>15</v>
       </c>
@@ -8528,7 +8545,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -8548,7 +8565,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="119" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -8568,7 +8585,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="120" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -8588,7 +8605,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="121" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -8608,7 +8625,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="122" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>15</v>
       </c>
@@ -8628,7 +8645,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="123" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>15</v>
       </c>
@@ -8648,7 +8665,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -8668,7 +8685,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="125" ht="58" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>15</v>
       </c>
@@ -8688,7 +8705,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -8708,7 +8725,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>15</v>
       </c>
@@ -8728,7 +8745,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="128" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>15</v>
       </c>
@@ -8748,7 +8765,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="129" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -8768,7 +8785,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -8788,7 +8805,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="131" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -8808,7 +8825,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="132" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -8828,7 +8845,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="133" ht="43.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -8848,7 +8865,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="134" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -8868,7 +8885,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -8888,7 +8905,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -8908,7 +8925,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="137" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -8928,7 +8945,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -8948,7 +8965,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -8968,7 +8985,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -8988,7 +9005,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -9008,7 +9025,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -9028,7 +9045,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -9048,7 +9065,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -9068,7 +9085,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="145" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>15</v>
       </c>
@@ -9088,7 +9105,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -9108,7 +9125,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -9128,7 +9145,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -9148,7 +9165,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -9168,7 +9185,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -9188,7 +9205,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -9208,7 +9225,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -9228,7 +9245,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -9248,7 +9265,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -9268,7 +9285,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -9288,7 +9305,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -9308,7 +9325,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="157" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -9328,7 +9345,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -9348,7 +9365,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -9368,7 +9385,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -9388,7 +9405,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -9408,7 +9425,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="162" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -9428,7 +9445,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -9448,7 +9465,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -9468,7 +9485,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="165" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -9488,7 +9505,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -9508,7 +9525,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -9528,7 +9545,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -9548,7 +9565,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -9568,7 +9585,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -9588,7 +9605,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -9608,7 +9625,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -9628,7 +9645,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="173" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -9648,7 +9665,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="174" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -9668,7 +9685,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -9688,7 +9705,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="176" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -9708,7 +9725,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="177" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -9728,7 +9745,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="178" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -9748,7 +9765,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -9768,7 +9785,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="180" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -9788,7 +9805,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="181" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -9808,7 +9825,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -9828,7 +9845,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -9848,7 +9865,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>15</v>
       </c>
@@ -9868,7 +9885,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="185" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -9888,7 +9905,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -9908,7 +9925,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="187" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>15</v>
       </c>
@@ -9928,7 +9945,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="188" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>15</v>
       </c>
@@ -9948,7 +9965,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="189" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>15</v>
       </c>
@@ -9968,7 +9985,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>15</v>
       </c>
@@ -9988,7 +10005,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>15</v>
       </c>
@@ -10008,7 +10025,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>15</v>
       </c>
@@ -10028,7 +10045,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>15</v>
       </c>
@@ -10048,7 +10065,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>15</v>
       </c>
@@ -10068,7 +10085,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>15</v>
       </c>
@@ -10088,7 +10105,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>15</v>
       </c>
@@ -10108,7 +10125,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>15</v>
       </c>
@@ -10128,7 +10145,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="198" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>15</v>
       </c>
@@ -10148,7 +10165,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>15</v>
       </c>
@@ -10168,7 +10185,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="200" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>15</v>
       </c>
@@ -10188,7 +10205,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>15</v>
       </c>
@@ -10208,7 +10225,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="202" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>15</v>
       </c>
@@ -10228,7 +10245,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>15</v>
       </c>
@@ -10248,7 +10265,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>15</v>
       </c>
@@ -10268,7 +10285,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="205" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>15</v>
       </c>
@@ -10288,7 +10305,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>15</v>
       </c>
@@ -10308,7 +10325,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="207" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>15</v>
       </c>
@@ -10328,7 +10345,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="208" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>15</v>
       </c>
@@ -10348,7 +10365,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>15</v>
       </c>
@@ -10368,7 +10385,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="210" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>15</v>
       </c>
@@ -10388,7 +10405,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>15</v>
       </c>
@@ -10408,7 +10425,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="212" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -10428,7 +10445,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="213" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>15</v>
       </c>
@@ -10448,7 +10465,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="214" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>15</v>
       </c>
@@ -10468,7 +10485,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -10488,7 +10505,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>15</v>
       </c>
@@ -10508,7 +10525,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -10528,7 +10545,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="218" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>15</v>
       </c>
@@ -10548,7 +10565,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="219" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>15</v>
       </c>
@@ -10568,7 +10585,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="220" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>15</v>
       </c>
@@ -10588,7 +10605,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="221" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>15</v>
       </c>
@@ -10608,7 +10625,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="222" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>15</v>
       </c>
@@ -10628,7 +10645,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="223" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>15</v>
       </c>
@@ -10648,7 +10665,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="224" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>15</v>
       </c>
@@ -10668,7 +10685,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="225" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>15</v>
       </c>
@@ -10688,7 +10705,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>15</v>
       </c>
@@ -10708,7 +10725,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>15</v>
       </c>
@@ -10728,7 +10745,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>15</v>
       </c>
@@ -10748,7 +10765,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>15</v>
       </c>
@@ -10768,7 +10785,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>15</v>
       </c>
@@ -10788,7 +10805,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>15</v>
       </c>
@@ -10808,7 +10825,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>15</v>
       </c>
@@ -10828,7 +10845,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="233" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>15</v>
       </c>
@@ -10848,7 +10865,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>15</v>
       </c>
@@ -10868,7 +10885,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>15</v>
       </c>
@@ -10888,7 +10905,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>15</v>
       </c>
@@ -10908,7 +10925,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="237" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>15</v>
       </c>
@@ -10928,7 +10945,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>15</v>
       </c>
@@ -10948,7 +10965,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="239" ht="29" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>15</v>
       </c>
@@ -10968,7 +10985,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>15</v>
       </c>
@@ -10988,7 +11005,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>15</v>
       </c>
@@ -11008,7 +11025,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>15</v>
       </c>
@@ -11028,7 +11045,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>15</v>
       </c>
@@ -11048,7 +11065,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>15</v>
       </c>
@@ -11068,7 +11085,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>15</v>
       </c>
@@ -11088,7 +11105,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>15</v>
       </c>
@@ -11108,7 +11125,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>15</v>
       </c>
@@ -11128,7 +11145,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>15</v>
       </c>
@@ -11148,7 +11165,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>15</v>
       </c>
@@ -11168,7 +11185,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>15</v>
       </c>
@@ -11188,7 +11205,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>15</v>
       </c>
@@ -11208,7 +11225,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -11228,7 +11245,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -11254,9 +11271,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -11266,7 +11283,7 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -11286,7 +11303,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -11306,7 +11323,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -11326,7 +11343,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -11346,7 +11363,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -11366,7 +11383,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -11386,7 +11403,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -11406,7 +11423,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -11426,7 +11443,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -11446,7 +11463,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -11466,7 +11483,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -11486,7 +11503,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -11506,7 +11523,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -11526,7 +11543,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -11546,7 +11563,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -11566,7 +11583,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -11586,7 +11603,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -11606,7 +11623,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -11626,7 +11643,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -11646,7 +11663,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -11666,7 +11683,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -11686,7 +11703,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -11706,7 +11723,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -11726,7 +11743,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -11746,7 +11763,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -11766,7 +11783,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -11786,7 +11803,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -11806,7 +11823,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -11826,7 +11843,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -11846,7 +11863,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -11866,7 +11883,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -11886,7 +11903,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -11906,7 +11923,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -11926,7 +11943,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -11946,7 +11963,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -11966,7 +11983,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -11986,7 +12003,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -12006,7 +12023,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -12026,7 +12043,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -12046,7 +12063,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -12066,7 +12083,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -12086,7 +12103,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -12106,7 +12123,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -12126,7 +12143,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -12146,7 +12163,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -12166,7 +12183,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -12186,7 +12203,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -12206,7 +12223,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -12226,7 +12243,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -12246,7 +12263,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -12266,7 +12283,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -12286,7 +12303,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -12306,7 +12323,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -12326,7 +12343,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -12346,7 +12363,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -12366,7 +12383,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -12386,7 +12403,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -12406,7 +12423,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -12426,7 +12443,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -12446,7 +12463,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -12466,7 +12483,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -12486,7 +12503,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -12506,7 +12523,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -12526,7 +12543,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -12548,6 +12565,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>